--- a/Financial Analysis/COUR.xlsx
+++ b/Financial Analysis/COUR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF75EFF-FD23-4D1B-A170-EE10FE4F3B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF12F09D-A822-49F4-AA08-C318AD60FB4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{31E8D773-A0F0-4A5C-8306-0B953AC75F07}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{31E8D773-A0F0-4A5C-8306-0B953AC75F07}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -299,7 +299,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -315,7 +315,6 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -763,15 +762,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <f>11.3</f>
-        <v>11.3</v>
+        <v>10.31</v>
       </c>
       <c r="E3" s="4">
-        <v>45902</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45902</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="4">
         <v>45953</v>
@@ -794,7 +792,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>1849.81</v>
+        <v>1687.7470000000001</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -835,7 +833,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>1074.71</v>
+        <v>912.64700000000005</v>
       </c>
     </row>
   </sheetData>
@@ -1184,19 +1182,19 @@
       <c r="AH4" s="5">
         <v>165.8</v>
       </c>
-      <c r="AI4" s="9">
+      <c r="AI4" s="5">
         <f>SUM(O4:R4)</f>
         <v>192.3</v>
       </c>
-      <c r="AJ4" s="9">
+      <c r="AJ4" s="5">
         <f>SUM(S4:V4)</f>
         <v>306.10000000000002</v>
       </c>
-      <c r="AK4" s="9">
+      <c r="AK4" s="5">
         <f>SUM(W4:Z4)</f>
         <v>323.3</v>
       </c>
-      <c r="AL4" s="9">
+      <c r="AL4" s="5">
         <f>SUM(AA4:AD4)</f>
         <v>337.58479999999997</v>
       </c>
@@ -1246,67 +1244,67 @@
         <v>14</v>
       </c>
       <c r="M5" s="8">
-        <f>M3-M4</f>
+        <f t="shared" ref="M5:AB5" si="3">M3-M4</f>
         <v>67.7</v>
       </c>
       <c r="N5" s="8">
-        <f>N3-N4</f>
+        <f t="shared" si="3"/>
         <v>71.3</v>
       </c>
       <c r="O5" s="8">
-        <f>O3-O4</f>
+        <f t="shared" si="3"/>
         <v>77.600000000000009</v>
       </c>
       <c r="P5" s="8">
-        <f>P3-P4</f>
+        <f t="shared" si="3"/>
         <v>78.400000000000006</v>
       </c>
       <c r="Q5" s="8">
-        <f>Q3-Q4</f>
+        <f t="shared" si="3"/>
         <v>87.600000000000009</v>
       </c>
       <c r="R5" s="8">
-        <f>R3-R4</f>
+        <f t="shared" si="3"/>
         <v>87.899999999999991</v>
       </c>
       <c r="S5" s="8">
-        <f>S3-S4</f>
+        <f t="shared" si="3"/>
         <v>77.399999999999991</v>
       </c>
       <c r="T5" s="8">
-        <f>T3-T4</f>
+        <f t="shared" si="3"/>
         <v>79.699999999999989</v>
       </c>
       <c r="U5" s="8">
-        <f>U3-U4</f>
+        <f t="shared" si="3"/>
         <v>83.2</v>
       </c>
       <c r="V5" s="8">
-        <f>V3-V4</f>
+        <f t="shared" si="3"/>
         <v>89.300000000000011</v>
       </c>
       <c r="W5" s="8">
-        <f>W3-W4</f>
+        <f t="shared" si="3"/>
         <v>89.5</v>
       </c>
       <c r="X5" s="8">
-        <f>X3-X4</f>
+        <f t="shared" si="3"/>
         <v>90.200000000000017</v>
       </c>
       <c r="Y5" s="8">
-        <f>Y3-Y4</f>
+        <f t="shared" si="3"/>
         <v>96.199999999999989</v>
       </c>
       <c r="Z5" s="8">
-        <f>Z3-Z4</f>
+        <f t="shared" si="3"/>
         <v>95.499999999999986</v>
       </c>
       <c r="AA5" s="8">
-        <f>AA3-AA4</f>
+        <f t="shared" si="3"/>
         <v>97.9</v>
       </c>
       <c r="AB5" s="8">
-        <f>AB3-AB4</f>
+        <f t="shared" si="3"/>
         <v>102.69999999999999</v>
       </c>
       <c r="AC5" s="8">
@@ -1314,35 +1312,35 @@
         <v>104.50000000000001</v>
       </c>
       <c r="AD5" s="8">
-        <f t="shared" ref="AD5" si="3">AD3*0.55</f>
+        <f t="shared" ref="AD5" si="4">AD3*0.55</f>
         <v>105.45920000000001</v>
       </c>
       <c r="AF5" s="8">
-        <f>AF3-AF4</f>
+        <f t="shared" ref="AF5:AL5" si="5">AF3-AF4</f>
         <v>94.800000000000011</v>
       </c>
       <c r="AG5" s="8">
-        <f>AG3-AG4</f>
+        <f t="shared" si="5"/>
         <v>154.69999999999999</v>
       </c>
       <c r="AH5" s="8">
-        <f>AH3-AH4</f>
+        <f t="shared" si="5"/>
         <v>249.5</v>
       </c>
       <c r="AI5" s="8">
-        <f>AI3-AI4</f>
+        <f t="shared" si="5"/>
         <v>331.49999999999994</v>
       </c>
       <c r="AJ5" s="8">
-        <f>AJ3-AJ4</f>
+        <f t="shared" si="5"/>
         <v>329.59999999999991</v>
       </c>
       <c r="AK5" s="8">
-        <f>AK3-AK4</f>
+        <f t="shared" si="5"/>
         <v>371.40000000000003</v>
       </c>
       <c r="AL5" s="8">
-        <f>AL3-AL4</f>
+        <f t="shared" si="5"/>
         <v>410.55920000000003</v>
       </c>
       <c r="AM5" s="8">
@@ -1358,31 +1356,31 @@
         <v>488.05981835519998</v>
       </c>
       <c r="AP5" s="8">
-        <f t="shared" ref="AP5:AV5" si="4">AP3*0.58</f>
+        <f t="shared" ref="AP5:AV5" si="6">AP3*0.58</f>
         <v>497.82101472230397</v>
       </c>
       <c r="AQ5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>507.77743501675002</v>
       </c>
       <c r="AR5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>517.93298371708499</v>
       </c>
       <c r="AS5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>523.11231355425582</v>
       </c>
       <c r="AT5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>528.34343668979841</v>
       </c>
       <c r="AU5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>533.62687105669647</v>
       </c>
       <c r="AV5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>538.96313976726344</v>
       </c>
     </row>
@@ -1455,20 +1453,20 @@
       <c r="AH6" s="5">
         <v>135.4</v>
       </c>
-      <c r="AI6" s="9">
-        <f t="shared" ref="AI6:AI9" si="5">SUM(O6:R6)</f>
+      <c r="AI6" s="5">
+        <f t="shared" ref="AI6:AI9" si="7">SUM(O6:R6)</f>
         <v>165.10000000000002</v>
       </c>
-      <c r="AJ6" s="9">
-        <f t="shared" ref="AI6:AJ9" si="6">SUM(S6:V6)</f>
+      <c r="AJ6" s="5">
+        <f t="shared" ref="AJ6:AJ9" si="8">SUM(S6:V6)</f>
         <v>160.1</v>
       </c>
-      <c r="AK6" s="9">
-        <f t="shared" ref="AJ6:AL9" si="7">SUM(W6:Z6)</f>
+      <c r="AK6" s="5">
+        <f t="shared" ref="AK6:AK9" si="9">SUM(W6:Z6)</f>
         <v>132</v>
       </c>
-      <c r="AL6" s="9">
-        <f t="shared" ref="AL6:AL9" si="8">SUM(AA6:AD6)</f>
+      <c r="AL6" s="5">
+        <f t="shared" ref="AL6:AL9" si="10">SUM(AA6:AD6)</f>
         <v>114.85600000000001</v>
       </c>
       <c r="AM6" s="5">
@@ -1476,39 +1474,39 @@
         <v>107.96464</v>
       </c>
       <c r="AN6" s="5">
-        <f t="shared" ref="AN6:AV6" si="9">AM6*1.01</f>
+        <f t="shared" ref="AN6:AV6" si="11">AM6*1.01</f>
         <v>109.0442864</v>
       </c>
       <c r="AO6" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>110.134729264</v>
       </c>
       <c r="AP6" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>111.23607655664</v>
       </c>
       <c r="AQ6" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>112.34843732220641</v>
       </c>
       <c r="AR6" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>113.47192169542848</v>
       </c>
       <c r="AS6" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>114.60664091238276</v>
       </c>
       <c r="AT6" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>115.75270732150659</v>
       </c>
       <c r="AU6" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>116.91023439472166</v>
       </c>
       <c r="AV6" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>118.07933673866887</v>
       </c>
     </row>
@@ -1569,7 +1567,7 @@
         <v>64.600000000000009</v>
       </c>
       <c r="AD7" s="5">
-        <f t="shared" ref="AD7" si="10">AD3*0.34</f>
+        <f t="shared" ref="AD7" si="12">AD3*0.34</f>
         <v>65.192959999999999</v>
       </c>
       <c r="AF7" s="5">
@@ -1581,20 +1579,20 @@
       <c r="AH7" s="5">
         <v>179.3</v>
       </c>
-      <c r="AI7" s="9">
-        <f t="shared" si="5"/>
+      <c r="AI7" s="5">
+        <f t="shared" si="7"/>
         <v>227.70000000000002</v>
       </c>
-      <c r="AJ7" s="9">
-        <f t="shared" si="6"/>
+      <c r="AJ7" s="5">
+        <f t="shared" si="8"/>
         <v>222.79999999999998</v>
       </c>
-      <c r="AK7" s="9">
-        <f t="shared" si="7"/>
+      <c r="AK7" s="5">
+        <f t="shared" si="9"/>
         <v>234.89999999999998</v>
       </c>
-      <c r="AL7" s="9">
-        <f t="shared" si="8"/>
+      <c r="AL7" s="5">
+        <f t="shared" si="10"/>
         <v>250.19296</v>
       </c>
       <c r="AM7" s="5">
@@ -1610,31 +1608,31 @@
         <v>260.8595580864</v>
       </c>
       <c r="AP7" s="5">
-        <f t="shared" ref="AP7:AV7" si="11">AP3*0.31</f>
+        <f t="shared" ref="AP7:AV7" si="13">AP3*0.31</f>
         <v>266.07674924812801</v>
       </c>
       <c r="AQ7" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>271.39828423309052</v>
       </c>
       <c r="AR7" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>276.82624991775236</v>
       </c>
       <c r="AS7" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>279.59451241692989</v>
       </c>
       <c r="AT7" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>282.39045754109918</v>
       </c>
       <c r="AU7" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>285.21436211651019</v>
       </c>
       <c r="AV7" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>288.0665057376753</v>
       </c>
     </row>
@@ -1707,20 +1705,20 @@
       <c r="AH8" s="5">
         <v>77.8</v>
       </c>
-      <c r="AI8" s="9">
-        <f t="shared" si="5"/>
+      <c r="AI8" s="5">
+        <f t="shared" si="7"/>
         <v>105.9</v>
       </c>
-      <c r="AJ8" s="9">
-        <f t="shared" si="6"/>
+      <c r="AJ8" s="5">
+        <f t="shared" si="8"/>
         <v>98.199999999999989</v>
       </c>
-      <c r="AK8" s="9">
-        <f t="shared" si="7"/>
+      <c r="AK8" s="5">
+        <f t="shared" si="9"/>
         <v>108.9</v>
       </c>
-      <c r="AL8" s="9">
-        <f t="shared" si="8"/>
+      <c r="AL8" s="5">
+        <f t="shared" si="10"/>
         <v>102.29899999999999</v>
       </c>
       <c r="AM8" s="5">
@@ -1732,35 +1730,35 @@
         <v>98.155890499999984</v>
       </c>
       <c r="AO8" s="5">
-        <f t="shared" ref="AO8:AV8" si="12">AN8*1.01</f>
+        <f t="shared" ref="AO8:AV8" si="14">AN8*1.01</f>
         <v>99.137449404999984</v>
       </c>
       <c r="AP8" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>100.12882389904999</v>
       </c>
       <c r="AQ8" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>101.13011213804049</v>
       </c>
       <c r="AR8" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>102.1414132594209</v>
       </c>
       <c r="AS8" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>103.16282739201512</v>
       </c>
       <c r="AT8" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>104.19445566593527</v>
       </c>
       <c r="AU8" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>105.23640022259463</v>
       </c>
       <c r="AV8" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>106.28876422482057</v>
       </c>
     </row>
@@ -1831,20 +1829,20 @@
       <c r="AH9" s="5">
         <v>0</v>
       </c>
-      <c r="AI9" s="9">
-        <f t="shared" si="5"/>
+      <c r="AI9" s="5">
+        <f t="shared" si="7"/>
         <v>10.1</v>
       </c>
-      <c r="AJ9" s="9">
-        <f t="shared" si="6"/>
+      <c r="AJ9" s="5">
+        <f t="shared" si="8"/>
         <v>-5.6000000000000005</v>
       </c>
-      <c r="AK9" s="9">
-        <f t="shared" si="7"/>
+      <c r="AK9" s="5">
+        <f t="shared" si="9"/>
         <v>8.9</v>
       </c>
-      <c r="AL9" s="9">
-        <f t="shared" si="8"/>
+      <c r="AL9" s="5">
+        <f t="shared" si="10"/>
         <v>-0.9</v>
       </c>
       <c r="AM9" s="5">
@@ -1883,143 +1881,143 @@
         <v>18</v>
       </c>
       <c r="M10" s="5">
-        <f>SUM(M6:M9)</f>
+        <f t="shared" ref="M10:AB10" si="15">SUM(M6:M9)</f>
         <v>99.1</v>
       </c>
       <c r="N10" s="5">
-        <f>SUM(N6:N9)</f>
+        <f t="shared" si="15"/>
         <v>118.80000000000001</v>
       </c>
       <c r="O10" s="5">
-        <f>SUM(O6:O9)</f>
+        <f t="shared" si="15"/>
         <v>114.9</v>
       </c>
       <c r="P10" s="5">
-        <f>SUM(P6:P9)</f>
+        <f t="shared" si="15"/>
         <v>126.2</v>
       </c>
       <c r="Q10" s="5">
-        <f>SUM(Q6:Q9)</f>
+        <f t="shared" si="15"/>
         <v>123.9</v>
       </c>
       <c r="R10" s="5">
-        <f>SUM(R6:R9)</f>
+        <f t="shared" si="15"/>
         <v>143.79999999999998</v>
       </c>
       <c r="S10" s="5">
-        <f>SUM(S6:S9)</f>
+        <f t="shared" si="15"/>
         <v>116.49999999999999</v>
       </c>
       <c r="T10" s="5">
-        <f>SUM(T6:T9)</f>
+        <f t="shared" si="15"/>
         <v>118.29999999999998</v>
       </c>
       <c r="U10" s="5">
-        <f>SUM(U6:U9)</f>
+        <f t="shared" si="15"/>
         <v>122.80000000000001</v>
       </c>
       <c r="V10" s="5">
-        <f>SUM(V6:V9)</f>
+        <f t="shared" si="15"/>
         <v>117.9</v>
       </c>
       <c r="W10" s="5">
-        <f>SUM(W6:W9)</f>
+        <f t="shared" si="15"/>
         <v>119.3</v>
       </c>
       <c r="X10" s="5">
-        <f>SUM(X6:X9)</f>
+        <f t="shared" si="15"/>
         <v>121.4</v>
       </c>
       <c r="Y10" s="5">
-        <f>SUM(Y6:Y9)</f>
+        <f t="shared" si="15"/>
         <v>118</v>
       </c>
       <c r="Z10" s="5">
-        <f>SUM(Z6:Z9)</f>
+        <f t="shared" si="15"/>
         <v>126.00000000000001</v>
       </c>
       <c r="AA10" s="5">
-        <f>SUM(AA6:AA9)</f>
+        <f t="shared" si="15"/>
         <v>112.29999999999998</v>
       </c>
       <c r="AB10" s="5">
-        <f>SUM(AB6:AB9)</f>
+        <f t="shared" si="15"/>
         <v>117.80000000000001</v>
       </c>
       <c r="AC10" s="5">
-        <f t="shared" ref="AC10:AD10" si="13">SUM(AC6:AC9)</f>
+        <f t="shared" ref="AC10:AD10" si="16">SUM(AC6:AC9)</f>
         <v>117.89000000000001</v>
       </c>
       <c r="AD10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>118.45796</v>
       </c>
       <c r="AF10" s="5">
-        <f>SUM(AF6:AF9)</f>
+        <f t="shared" ref="AF10:AL10" si="17">SUM(AF6:AF9)</f>
         <v>143.20000000000002</v>
       </c>
       <c r="AG10" s="5">
-        <f>SUM(AG6:AG9)</f>
+        <f t="shared" si="17"/>
         <v>221.2</v>
       </c>
       <c r="AH10" s="5">
-        <f>SUM(AH6:AH9)</f>
+        <f t="shared" si="17"/>
         <v>392.50000000000006</v>
       </c>
       <c r="AI10" s="5">
-        <f>SUM(AI6:AI9)</f>
+        <f t="shared" si="17"/>
         <v>508.80000000000007</v>
       </c>
       <c r="AJ10" s="5">
-        <f>SUM(AJ6:AJ9)</f>
+        <f t="shared" si="17"/>
         <v>475.49999999999994</v>
       </c>
       <c r="AK10" s="5">
-        <f>SUM(AK6:AK9)</f>
+        <f t="shared" si="17"/>
         <v>484.69999999999993</v>
       </c>
       <c r="AL10" s="5">
-        <f>SUM(AL6:AL9)</f>
+        <f t="shared" si="17"/>
         <v>466.44796000000002</v>
       </c>
       <c r="AM10" s="5">
-        <f t="shared" ref="AM10:AN10" si="14">SUM(AM6:AM9)</f>
+        <f t="shared" ref="AM10:AN10" si="18">SUM(AM6:AM9)</f>
         <v>464.38058599999999</v>
       </c>
       <c r="AN10" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>468.63161626000004</v>
       </c>
       <c r="AO10" s="5">
-        <f t="shared" ref="AO10" si="15">SUM(AO6:AO9)</f>
+        <f t="shared" ref="AO10" si="19">SUM(AO6:AO9)</f>
         <v>470.13173675539997</v>
       </c>
       <c r="AP10" s="5">
-        <f t="shared" ref="AP10" si="16">SUM(AP6:AP9)</f>
+        <f t="shared" ref="AP10" si="20">SUM(AP6:AP9)</f>
         <v>477.44164970381803</v>
       </c>
       <c r="AQ10" s="5">
-        <f t="shared" ref="AQ10" si="17">SUM(AQ6:AQ9)</f>
+        <f t="shared" ref="AQ10" si="21">SUM(AQ6:AQ9)</f>
         <v>484.8768336933374</v>
       </c>
       <c r="AR10" s="5">
-        <f t="shared" ref="AR10" si="18">SUM(AR6:AR9)</f>
+        <f t="shared" ref="AR10" si="22">SUM(AR6:AR9)</f>
         <v>492.43958487260176</v>
       </c>
       <c r="AS10" s="5">
-        <f t="shared" ref="AS10" si="19">SUM(AS6:AS9)</f>
+        <f t="shared" ref="AS10" si="23">SUM(AS6:AS9)</f>
         <v>497.36398072132778</v>
       </c>
       <c r="AT10" s="5">
-        <f t="shared" ref="AT10" si="20">SUM(AT6:AT9)</f>
+        <f t="shared" ref="AT10" si="24">SUM(AT6:AT9)</f>
         <v>502.33762052854104</v>
       </c>
       <c r="AU10" s="5">
-        <f t="shared" ref="AU10" si="21">SUM(AU6:AU9)</f>
+        <f t="shared" ref="AU10" si="25">SUM(AU6:AU9)</f>
         <v>507.36099673382648</v>
       </c>
       <c r="AV10" s="5">
-        <f t="shared" ref="AV10" si="22">SUM(AV6:AV9)</f>
+        <f t="shared" ref="AV10" si="26">SUM(AV6:AV9)</f>
         <v>512.43460670116474</v>
       </c>
     </row>
@@ -2028,143 +2026,143 @@
         <v>20</v>
       </c>
       <c r="M11" s="8">
-        <f>M5-M10</f>
+        <f t="shared" ref="M11:AB11" si="27">M5-M10</f>
         <v>-31.399999999999991</v>
       </c>
       <c r="N11" s="8">
-        <f>N5-N10</f>
+        <f t="shared" si="27"/>
         <v>-47.500000000000014</v>
       </c>
       <c r="O11" s="8">
-        <f>O5-O10</f>
+        <f t="shared" si="27"/>
         <v>-37.299999999999997</v>
       </c>
       <c r="P11" s="8">
-        <f>P5-P10</f>
+        <f t="shared" si="27"/>
         <v>-47.8</v>
       </c>
       <c r="Q11" s="8">
-        <f>Q5-Q10</f>
+        <f t="shared" si="27"/>
         <v>-36.299999999999997</v>
       </c>
       <c r="R11" s="8">
-        <f>R5-R10</f>
+        <f t="shared" si="27"/>
         <v>-55.899999999999991</v>
       </c>
       <c r="S11" s="8">
-        <f>S5-S10</f>
+        <f t="shared" si="27"/>
         <v>-39.099999999999994</v>
       </c>
       <c r="T11" s="8">
-        <f>T5-T10</f>
+        <f t="shared" si="27"/>
         <v>-38.599999999999994</v>
       </c>
       <c r="U11" s="8">
-        <f>U5-U10</f>
+        <f t="shared" si="27"/>
         <v>-39.600000000000009</v>
       </c>
       <c r="V11" s="8">
-        <f>V5-V10</f>
+        <f t="shared" si="27"/>
         <v>-28.599999999999994</v>
       </c>
       <c r="W11" s="8">
-        <f>W5-W10</f>
+        <f t="shared" si="27"/>
         <v>-29.799999999999997</v>
       </c>
       <c r="X11" s="8">
-        <f>X5-X10</f>
+        <f t="shared" si="27"/>
         <v>-31.199999999999989</v>
       </c>
       <c r="Y11" s="8">
-        <f>Y5-Y10</f>
+        <f t="shared" si="27"/>
         <v>-21.800000000000011</v>
       </c>
       <c r="Z11" s="8">
-        <f>Z5-Z10</f>
+        <f t="shared" si="27"/>
         <v>-30.500000000000028</v>
       </c>
       <c r="AA11" s="8">
-        <f>AA5-AA10</f>
+        <f t="shared" si="27"/>
         <v>-14.399999999999977</v>
       </c>
       <c r="AB11" s="8">
-        <f>AB5-AB10</f>
+        <f t="shared" si="27"/>
         <v>-15.100000000000023</v>
       </c>
       <c r="AC11" s="8">
-        <f t="shared" ref="AC11:AD11" si="23">AC5-AC10</f>
+        <f t="shared" ref="AC11:AD11" si="28">AC5-AC10</f>
         <v>-13.39</v>
       </c>
       <c r="AD11" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>-12.99875999999999</v>
       </c>
       <c r="AF11" s="8">
-        <f>AF5-AF10</f>
+        <f t="shared" ref="AF11:AL11" si="29">AF5-AF10</f>
         <v>-48.400000000000006</v>
       </c>
       <c r="AG11" s="8">
-        <f>AG5-AG10</f>
+        <f t="shared" si="29"/>
         <v>-66.5</v>
       </c>
       <c r="AH11" s="8">
-        <f>AH5-AH10</f>
+        <f t="shared" si="29"/>
         <v>-143.00000000000006</v>
       </c>
       <c r="AI11" s="8">
-        <f>AI5-AI10</f>
+        <f t="shared" si="29"/>
         <v>-177.30000000000013</v>
       </c>
       <c r="AJ11" s="8">
-        <f>AJ5-AJ10</f>
+        <f t="shared" si="29"/>
         <v>-145.90000000000003</v>
       </c>
       <c r="AK11" s="8">
-        <f>AK5-AK10</f>
+        <f t="shared" si="29"/>
         <v>-113.2999999999999</v>
       </c>
       <c r="AL11" s="8">
-        <f>AL5-AL10</f>
+        <f t="shared" si="29"/>
         <v>-55.888759999999991</v>
       </c>
       <c r="AM11" s="8">
-        <f t="shared" ref="AM11:AN11" si="24">AM5-AM10</f>
+        <f t="shared" ref="AM11:AN11" si="30">AM5-AM10</f>
         <v>-24.47191399999997</v>
       </c>
       <c r="AN11" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>-2.9568649000000846</v>
       </c>
       <c r="AO11" s="8">
-        <f t="shared" ref="AO11" si="25">AO5-AO10</f>
+        <f t="shared" ref="AO11" si="31">AO5-AO10</f>
         <v>17.928081599800009</v>
       </c>
       <c r="AP11" s="8">
-        <f t="shared" ref="AP11" si="26">AP5-AP10</f>
+        <f t="shared" ref="AP11" si="32">AP5-AP10</f>
         <v>20.379365018485942</v>
       </c>
       <c r="AQ11" s="8">
-        <f t="shared" ref="AQ11" si="27">AQ5-AQ10</f>
+        <f t="shared" ref="AQ11" si="33">AQ5-AQ10</f>
         <v>22.900601323412616</v>
       </c>
       <c r="AR11" s="8">
-        <f t="shared" ref="AR11" si="28">AR5-AR10</f>
+        <f t="shared" ref="AR11" si="34">AR5-AR10</f>
         <v>25.493398844483238</v>
       </c>
       <c r="AS11" s="8">
-        <f t="shared" ref="AS11" si="29">AS5-AS10</f>
+        <f t="shared" ref="AS11" si="35">AS5-AS10</f>
         <v>25.748332832928043</v>
       </c>
       <c r="AT11" s="8">
-        <f t="shared" ref="AT11" si="30">AT5-AT10</f>
+        <f t="shared" ref="AT11" si="36">AT5-AT10</f>
         <v>26.005816161257371</v>
       </c>
       <c r="AU11" s="8">
-        <f t="shared" ref="AU11" si="31">AU5-AU10</f>
+        <f t="shared" ref="AU11" si="37">AU5-AU10</f>
         <v>26.26587432286999</v>
       </c>
       <c r="AV11" s="8">
-        <f t="shared" ref="AV11" si="32">AV5-AV10</f>
+        <f t="shared" ref="AV11" si="38">AV5-AV10</f>
         <v>26.528533066098703</v>
       </c>
     </row>
@@ -2235,20 +2233,20 @@
       <c r="AH12" s="5">
         <v>-0.3</v>
       </c>
-      <c r="AI12" s="9">
-        <f t="shared" ref="AI12:AI13" si="33">SUM(O12:R12)</f>
+      <c r="AI12" s="5">
+        <f t="shared" ref="AI12:AI13" si="39">SUM(O12:R12)</f>
         <v>-9.1</v>
       </c>
-      <c r="AJ12" s="9">
-        <f t="shared" ref="AI12:AJ13" si="34">SUM(S12:V12)</f>
+      <c r="AJ12" s="5">
+        <f t="shared" ref="AJ12:AJ13" si="40">SUM(S12:V12)</f>
         <v>-34.400000000000006</v>
       </c>
-      <c r="AK12" s="9">
-        <f t="shared" ref="AJ12:AL13" si="35">SUM(W12:Z12)</f>
+      <c r="AK12" s="5">
+        <f t="shared" ref="AK12:AK13" si="41">SUM(W12:Z12)</f>
         <v>-36.799999999999997</v>
       </c>
-      <c r="AL12" s="9">
-        <f t="shared" ref="AL12:AL13" si="36">SUM(AA12:AD12)</f>
+      <c r="AL12" s="5">
+        <f t="shared" ref="AL12:AL13" si="42">SUM(AA12:AD12)</f>
         <v>-31.8</v>
       </c>
       <c r="AM12" s="5">
@@ -2260,35 +2258,35 @@
         <v>-32.43918</v>
       </c>
       <c r="AO12" s="5">
-        <f t="shared" ref="AO12:AV12" si="37">AN12*1.01</f>
+        <f t="shared" ref="AO12:AV12" si="43">AN12*1.01</f>
         <v>-32.763571800000001</v>
       </c>
       <c r="AP12" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>-33.091207518000004</v>
       </c>
       <c r="AQ12" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>-33.422119593180007</v>
       </c>
       <c r="AR12" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>-33.75634078911181</v>
       </c>
       <c r="AS12" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>-34.093904197002928</v>
       </c>
       <c r="AT12" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>-34.43484323897296</v>
       </c>
       <c r="AU12" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>-34.779191671362689</v>
       </c>
       <c r="AV12" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>-35.126983588076314</v>
       </c>
     </row>
@@ -2360,20 +2358,20 @@
       <c r="AH13" s="5">
         <v>0.3</v>
       </c>
-      <c r="AI13" s="9">
-        <f t="shared" si="33"/>
+      <c r="AI13" s="5">
+        <f t="shared" si="39"/>
         <v>2.4</v>
       </c>
-      <c r="AJ13" s="9">
-        <f t="shared" si="34"/>
+      <c r="AJ13" s="5">
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="AK13" s="9">
-        <f t="shared" si="35"/>
+      <c r="AK13" s="5">
+        <f t="shared" si="41"/>
         <v>2</v>
       </c>
-      <c r="AL13" s="9">
-        <f t="shared" si="36"/>
+      <c r="AL13" s="5">
+        <f t="shared" si="42"/>
         <v>-0.4</v>
       </c>
       <c r="AM13" s="5">
@@ -2412,143 +2410,143 @@
         <v>23</v>
       </c>
       <c r="M14" s="8">
-        <f>M11-M12-M13</f>
+        <f t="shared" ref="M14:AB14" si="44">M11-M12-M13</f>
         <v>-31.599999999999991</v>
       </c>
       <c r="N14" s="8">
-        <f>N11-N12-N13</f>
+        <f t="shared" si="44"/>
         <v>-47.500000000000014</v>
       </c>
       <c r="O14" s="8">
-        <f>O11-O12-O13</f>
+        <f t="shared" si="44"/>
         <v>-37.4</v>
       </c>
       <c r="P14" s="8">
-        <f>P11-P12-P13</f>
+        <f t="shared" si="44"/>
         <v>-48.2</v>
       </c>
       <c r="Q14" s="8">
-        <f>Q11-Q12-Q13</f>
+        <f t="shared" si="44"/>
         <v>-35</v>
       </c>
       <c r="R14" s="8">
-        <f>R11-R12-R13</f>
+        <f t="shared" si="44"/>
         <v>-49.999999999999986</v>
       </c>
       <c r="S14" s="8">
-        <f>S11-S12-S13</f>
+        <f t="shared" si="44"/>
         <v>-30.999999999999993</v>
       </c>
       <c r="T14" s="8">
-        <f>T11-T12-T13</f>
+        <f t="shared" si="44"/>
         <v>-30.399999999999995</v>
       </c>
       <c r="U14" s="8">
-        <f>U11-U12-U13</f>
+        <f t="shared" si="44"/>
         <v>-31.000000000000011</v>
       </c>
       <c r="V14" s="8">
-        <f>V11-V12-V13</f>
+        <f t="shared" si="44"/>
         <v>-19.099999999999994</v>
       </c>
       <c r="W14" s="8">
-        <f>W11-W12-W13</f>
+        <f t="shared" si="44"/>
         <v>-20.499999999999996</v>
       </c>
       <c r="X14" s="8">
-        <f>X11-X12-X13</f>
+        <f t="shared" si="44"/>
         <v>-21.899999999999988</v>
       </c>
       <c r="Y14" s="8">
-        <f>Y11-Y12-Y13</f>
+        <f t="shared" si="44"/>
         <v>-12.200000000000012</v>
       </c>
       <c r="Z14" s="8">
-        <f>Z11-Z12-Z13</f>
+        <f t="shared" si="44"/>
         <v>-23.900000000000027</v>
       </c>
       <c r="AA14" s="8">
-        <f>AA11-AA12-AA13</f>
+        <f t="shared" si="44"/>
         <v>-6.2999999999999776</v>
       </c>
       <c r="AB14" s="8">
-        <f>AB11-AB12-AB13</f>
+        <f t="shared" si="44"/>
         <v>-7.0000000000000231</v>
       </c>
       <c r="AC14" s="8">
-        <f t="shared" ref="AC14:AD14" si="38">AC11-AC12-AC13</f>
+        <f t="shared" ref="AC14:AD14" si="45">AC11-AC12-AC13</f>
         <v>-5.3900000000000006</v>
       </c>
       <c r="AD14" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="45"/>
         <v>-4.9987599999999901</v>
       </c>
       <c r="AF14" s="8">
-        <f>AF11-AF12-AF13</f>
+        <f t="shared" ref="AF14:AL14" si="46">AF11-AF12-AF13</f>
         <v>-46.000000000000007</v>
       </c>
       <c r="AG14" s="8">
-        <f>AG11-AG12-AG13</f>
+        <f t="shared" si="46"/>
         <v>-65.2</v>
       </c>
       <c r="AH14" s="8">
-        <f>AH11-AH12-AH13</f>
+        <f t="shared" si="46"/>
         <v>-143.00000000000006</v>
       </c>
       <c r="AI14" s="8">
-        <f>AI11-AI12-AI13</f>
+        <f t="shared" si="46"/>
         <v>-170.60000000000014</v>
       </c>
       <c r="AJ14" s="8">
-        <f>AJ11-AJ12-AJ13</f>
+        <f t="shared" si="46"/>
         <v>-111.50000000000003</v>
       </c>
       <c r="AK14" s="8">
-        <f>AK11-AK12-AK13</f>
+        <f t="shared" si="46"/>
         <v>-78.499999999999901</v>
       </c>
       <c r="AL14" s="8">
-        <f>AL11-AL12-AL13</f>
+        <f t="shared" si="46"/>
         <v>-23.688759999999991</v>
       </c>
       <c r="AM14" s="8">
-        <f t="shared" ref="AM14:AN14" si="39">AM11-AM12-AM13</f>
+        <f t="shared" ref="AM14:AN14" si="47">AM11-AM12-AM13</f>
         <v>7.6460860000000324</v>
       </c>
       <c r="AN14" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="47"/>
         <v>29.482315099999916</v>
       </c>
       <c r="AO14" s="8">
-        <f t="shared" ref="AO14" si="40">AO11-AO12-AO13</f>
+        <f t="shared" ref="AO14" si="48">AO11-AO12-AO13</f>
         <v>50.691653399800011</v>
       </c>
       <c r="AP14" s="8">
-        <f t="shared" ref="AP14" si="41">AP11-AP12-AP13</f>
+        <f t="shared" ref="AP14" si="49">AP11-AP12-AP13</f>
         <v>53.470572536485946</v>
       </c>
       <c r="AQ14" s="8">
-        <f t="shared" ref="AQ14" si="42">AQ11-AQ12-AQ13</f>
+        <f t="shared" ref="AQ14" si="50">AQ11-AQ12-AQ13</f>
         <v>56.322720916592623</v>
       </c>
       <c r="AR14" s="8">
-        <f t="shared" ref="AR14" si="43">AR11-AR12-AR13</f>
+        <f t="shared" ref="AR14" si="51">AR11-AR12-AR13</f>
         <v>59.249739633595048</v>
       </c>
       <c r="AS14" s="8">
-        <f t="shared" ref="AS14" si="44">AS11-AS12-AS13</f>
+        <f t="shared" ref="AS14" si="52">AS11-AS12-AS13</f>
         <v>59.84223702993097</v>
       </c>
       <c r="AT14" s="8">
-        <f t="shared" ref="AT14" si="45">AT11-AT12-AT13</f>
+        <f t="shared" ref="AT14" si="53">AT11-AT12-AT13</f>
         <v>60.440659400230331</v>
       </c>
       <c r="AU14" s="8">
-        <f t="shared" ref="AU14" si="46">AU11-AU12-AU13</f>
+        <f t="shared" ref="AU14" si="54">AU11-AU12-AU13</f>
         <v>61.045065994232679</v>
       </c>
       <c r="AV14" s="8">
-        <f t="shared" ref="AV14" si="47">AV11-AV12-AV13</f>
+        <f t="shared" ref="AV14" si="55">AV11-AV12-AV13</f>
         <v>61.655516654175017</v>
       </c>
     </row>
@@ -2619,19 +2617,19 @@
       <c r="AH15" s="5">
         <v>2.1</v>
       </c>
-      <c r="AI15" s="9">
+      <c r="AI15" s="5">
         <f>SUM(O15:R15)</f>
         <v>4.7</v>
       </c>
-      <c r="AJ15" s="9">
+      <c r="AJ15" s="5">
         <f>SUM(S15:V15)</f>
         <v>5.3</v>
       </c>
-      <c r="AK15" s="9">
+      <c r="AK15" s="5">
         <f>SUM(W15:Z15)</f>
         <v>1</v>
       </c>
-      <c r="AL15" s="9">
+      <c r="AL15" s="5">
         <f>SUM(AA15:AD15)</f>
         <v>4.3</v>
       </c>
@@ -2644,35 +2642,35 @@
         <v>2.9482315099999918</v>
       </c>
       <c r="AO15" s="5">
-        <f t="shared" ref="AO15:AV15" si="48">AO14*0.1</f>
+        <f t="shared" ref="AO15:AV15" si="56">AO14*0.1</f>
         <v>5.0691653399800014</v>
       </c>
       <c r="AP15" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>5.347057253648595</v>
       </c>
       <c r="AQ15" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>5.6322720916592628</v>
       </c>
       <c r="AR15" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>5.9249739633595055</v>
       </c>
       <c r="AS15" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>5.9842237029930976</v>
       </c>
       <c r="AT15" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>6.0440659400230334</v>
       </c>
       <c r="AU15" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>6.1045065994232681</v>
       </c>
       <c r="AV15" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>6.1655516654175022</v>
       </c>
     </row>
@@ -2681,143 +2679,143 @@
         <v>25</v>
       </c>
       <c r="M16" s="8">
-        <f>M14-M15</f>
+        <f t="shared" ref="M16:AB16" si="57">M14-M15</f>
         <v>-32.399999999999991</v>
       </c>
       <c r="N16" s="8">
-        <f>N14-N15</f>
+        <f t="shared" si="57"/>
         <v>-47.700000000000017</v>
       </c>
       <c r="O16" s="8">
-        <f>O14-O15</f>
+        <f t="shared" si="57"/>
         <v>-38.4</v>
       </c>
       <c r="P16" s="8">
-        <f>P14-P15</f>
+        <f t="shared" si="57"/>
         <v>-49.400000000000006</v>
       </c>
       <c r="Q16" s="8">
-        <f>Q14-Q15</f>
+        <f t="shared" si="57"/>
         <v>-36</v>
       </c>
       <c r="R16" s="8">
-        <f>R14-R15</f>
+        <f t="shared" si="57"/>
         <v>-51.499999999999986</v>
       </c>
       <c r="S16" s="8">
-        <f>S14-S15</f>
+        <f t="shared" si="57"/>
         <v>-32.399999999999991</v>
       </c>
       <c r="T16" s="8">
-        <f>T14-T15</f>
+        <f t="shared" si="57"/>
         <v>-31.999999999999996</v>
       </c>
       <c r="U16" s="8">
-        <f>U14-U15</f>
+        <f t="shared" si="57"/>
         <v>-32.000000000000014</v>
       </c>
       <c r="V16" s="8">
-        <f>V14-V15</f>
+        <f t="shared" si="57"/>
         <v>-20.399999999999995</v>
       </c>
       <c r="W16" s="8">
-        <f>W14-W15</f>
+        <f t="shared" si="57"/>
         <v>-21.299999999999997</v>
       </c>
       <c r="X16" s="8">
-        <f>X14-X15</f>
+        <f t="shared" si="57"/>
         <v>-22.899999999999988</v>
       </c>
       <c r="Y16" s="8">
-        <f>Y14-Y15</f>
+        <f t="shared" si="57"/>
         <v>-13.700000000000012</v>
       </c>
       <c r="Z16" s="8">
-        <f>Z14-Z15</f>
+        <f t="shared" si="57"/>
         <v>-21.600000000000026</v>
       </c>
       <c r="AA16" s="8">
-        <f>AA14-AA15</f>
+        <f t="shared" si="57"/>
         <v>-7.7999999999999776</v>
       </c>
       <c r="AB16" s="8">
-        <f>AB14-AB15</f>
+        <f t="shared" si="57"/>
         <v>-7.8000000000000229</v>
       </c>
       <c r="AC16" s="8">
-        <f t="shared" ref="AC16:AD16" si="49">AC14-AC15</f>
+        <f t="shared" ref="AC16:AD16" si="58">AC14-AC15</f>
         <v>-6.3900000000000006</v>
       </c>
       <c r="AD16" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="58"/>
         <v>-5.9987599999999901</v>
       </c>
       <c r="AF16" s="8">
-        <f>AF14-AF15</f>
+        <f t="shared" ref="AF16:AL16" si="59">AF14-AF15</f>
         <v>-46.70000000000001</v>
       </c>
       <c r="AG16" s="8">
-        <f>AG14-AG15</f>
+        <f t="shared" si="59"/>
         <v>-66.7</v>
       </c>
       <c r="AH16" s="8">
-        <f>AH14-AH15</f>
+        <f t="shared" si="59"/>
         <v>-145.10000000000005</v>
       </c>
       <c r="AI16" s="8">
-        <f>AI14-AI15</f>
+        <f t="shared" si="59"/>
         <v>-175.30000000000013</v>
       </c>
       <c r="AJ16" s="8">
-        <f>AJ14-AJ15</f>
+        <f t="shared" si="59"/>
         <v>-116.80000000000003</v>
       </c>
       <c r="AK16" s="8">
-        <f>AK14-AK15</f>
+        <f t="shared" si="59"/>
         <v>-79.499999999999901</v>
       </c>
       <c r="AL16" s="8">
-        <f>AL14-AL15</f>
+        <f t="shared" si="59"/>
         <v>-27.988759999999992</v>
       </c>
       <c r="AM16" s="8">
-        <f t="shared" ref="AM16:AN16" si="50">AM14-AM15</f>
+        <f t="shared" ref="AM16:AN16" si="60">AM14-AM15</f>
         <v>6.8814774000000289</v>
       </c>
       <c r="AN16" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v>26.534083589999923</v>
       </c>
       <c r="AO16" s="8">
-        <f t="shared" ref="AO16" si="51">AO14-AO15</f>
+        <f t="shared" ref="AO16" si="61">AO14-AO15</f>
         <v>45.622488059820007</v>
       </c>
       <c r="AP16" s="8">
-        <f t="shared" ref="AP16" si="52">AP14-AP15</f>
+        <f t="shared" ref="AP16" si="62">AP14-AP15</f>
         <v>48.123515282837353</v>
       </c>
       <c r="AQ16" s="8">
-        <f t="shared" ref="AQ16" si="53">AQ14-AQ15</f>
+        <f t="shared" ref="AQ16" si="63">AQ14-AQ15</f>
         <v>50.690448824933362</v>
       </c>
       <c r="AR16" s="8">
-        <f t="shared" ref="AR16" si="54">AR14-AR15</f>
+        <f t="shared" ref="AR16" si="64">AR14-AR15</f>
         <v>53.324765670235543</v>
       </c>
       <c r="AS16" s="8">
-        <f t="shared" ref="AS16" si="55">AS14-AS15</f>
+        <f t="shared" ref="AS16" si="65">AS14-AS15</f>
         <v>53.858013326937872</v>
       </c>
       <c r="AT16" s="8">
-        <f t="shared" ref="AT16" si="56">AT14-AT15</f>
+        <f t="shared" ref="AT16" si="66">AT14-AT15</f>
         <v>54.396593460207299</v>
       </c>
       <c r="AU16" s="8">
-        <f t="shared" ref="AU16" si="57">AU14-AU15</f>
+        <f t="shared" ref="AU16" si="67">AU14-AU15</f>
         <v>54.940559394809412</v>
       </c>
       <c r="AV16" s="8">
-        <f t="shared" ref="AV16" si="58">AV14-AV15</f>
+        <f t="shared" ref="AV16" si="68">AV14-AV15</f>
         <v>55.489964988757514</v>
       </c>
       <c r="AW16" s="1">
@@ -2825,383 +2823,383 @@
         <v>54.93506533886994</v>
       </c>
       <c r="AX16" s="1">
-        <f t="shared" ref="AX16:DI16" si="59">AW16*(1+$AY$21)</f>
+        <f t="shared" ref="AX16:DI16" si="69">AW16*(1+$AY$21)</f>
         <v>54.38571468548124</v>
       </c>
       <c r="AY16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>53.841857538626428</v>
       </c>
       <c r="AZ16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>53.303438963240161</v>
       </c>
       <c r="BA16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>52.770404573607756</v>
       </c>
       <c r="BB16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>52.242700527871676</v>
       </c>
       <c r="BC16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>51.720273522592962</v>
       </c>
       <c r="BD16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>51.203070787367032</v>
       </c>
       <c r="BE16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>50.691040079493362</v>
       </c>
       <c r="BF16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>50.184129678698426</v>
       </c>
       <c r="BG16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>49.682288381911441</v>
       </c>
       <c r="BH16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>49.185465498092327</v>
       </c>
       <c r="BI16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>48.693610843111401</v>
       </c>
       <c r="BJ16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>48.206674734680284</v>
       </c>
       <c r="BK16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>47.724607987333478</v>
       </c>
       <c r="BL16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>47.247361907460146</v>
       </c>
       <c r="BM16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>46.774888288385547</v>
       </c>
       <c r="BN16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>46.307139405501694</v>
       </c>
       <c r="BO16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>45.844068011446673</v>
       </c>
       <c r="BP16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>45.385627331332209</v>
       </c>
       <c r="BQ16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>44.931771058018889</v>
       </c>
       <c r="BR16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>44.4824533474387</v>
       </c>
       <c r="BS16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>44.037628813964311</v>
       </c>
       <c r="BT16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>43.597252525824665</v>
       </c>
       <c r="BU16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>43.161280000566421</v>
       </c>
       <c r="BV16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>42.729667200560755</v>
       </c>
       <c r="BW16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>42.302370528555144</v>
       </c>
       <c r="BX16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>41.879346823269593</v>
       </c>
       <c r="BY16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>41.460553355036893</v>
       </c>
       <c r="BZ16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>41.045947821486521</v>
       </c>
       <c r="CA16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>40.635488343271653</v>
       </c>
       <c r="CB16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>40.229133459838934</v>
       </c>
       <c r="CC16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>39.826842125240546</v>
       </c>
       <c r="CD16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>39.428573703988143</v>
       </c>
       <c r="CE16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>39.034287966948263</v>
       </c>
       <c r="CF16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>38.64394508727878</v>
       </c>
       <c r="CG16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>38.257505636405995</v>
       </c>
       <c r="CH16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>37.874930580041934</v>
       </c>
       <c r="CI16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>37.496181274241515</v>
       </c>
       <c r="CJ16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>37.121219461499102</v>
       </c>
       <c r="CK16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>36.750007266884111</v>
       </c>
       <c r="CL16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>36.382507194215272</v>
       </c>
       <c r="CM16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>36.01868212227312</v>
       </c>
       <c r="CN16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>35.658495301050387</v>
       </c>
       <c r="CO16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>35.301910348039883</v>
       </c>
       <c r="CP16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>34.948891244559483</v>
       </c>
       <c r="CQ16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>34.59940233211389</v>
       </c>
       <c r="CR16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>34.25340830879275</v>
       </c>
       <c r="CS16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>33.910874225704823</v>
       </c>
       <c r="CT16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>33.571765483447777</v>
       </c>
       <c r="CU16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>33.236047828613302</v>
       </c>
       <c r="CV16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>32.903687350327168</v>
       </c>
       <c r="CW16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>32.574650476823898</v>
       </c>
       <c r="CX16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>32.248903972055658</v>
       </c>
       <c r="CY16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>31.926414932335099</v>
       </c>
       <c r="CZ16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>31.607150783011747</v>
       </c>
       <c r="DA16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>31.29107927518163</v>
       </c>
       <c r="DB16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>30.978168482429815</v>
       </c>
       <c r="DC16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>30.668386797605518</v>
       </c>
       <c r="DD16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>30.361702929629462</v>
       </c>
       <c r="DE16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>30.058085900333168</v>
       </c>
       <c r="DF16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>29.757505041329836</v>
       </c>
       <c r="DG16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>29.459929990916535</v>
       </c>
       <c r="DH16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>29.16533069100737</v>
       </c>
       <c r="DI16" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>28.873677384097295</v>
       </c>
       <c r="DJ16" s="1">
-        <f t="shared" ref="DJ16:EN16" si="60">DI16*(1+$AY$21)</f>
+        <f t="shared" ref="DJ16:EN16" si="70">DI16*(1+$AY$21)</f>
         <v>28.584940610256321</v>
       </c>
       <c r="DK16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>28.299091204153758</v>
       </c>
       <c r="DL16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>28.01610029211222</v>
       </c>
       <c r="DM16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>27.735939289191098</v>
       </c>
       <c r="DN16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>27.458579896299188</v>
       </c>
       <c r="DO16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>27.183994097336196</v>
       </c>
       <c r="DP16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>26.912154156362835</v>
       </c>
       <c r="DQ16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>26.643032614799207</v>
       </c>
       <c r="DR16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>26.376602288651213</v>
       </c>
       <c r="DS16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>26.112836265764702</v>
       </c>
       <c r="DT16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>25.851707903107055</v>
       </c>
       <c r="DU16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>25.593190824075986</v>
       </c>
       <c r="DV16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>25.337258915835225</v>
       </c>
       <c r="DW16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>25.083886326676872</v>
       </c>
       <c r="DX16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>24.833047463410104</v>
       </c>
       <c r="DY16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>24.584716988776002</v>
       </c>
       <c r="DZ16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>24.338869818888242</v>
       </c>
       <c r="EA16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>24.095481120699358</v>
       </c>
       <c r="EB16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>23.854526309492364</v>
       </c>
       <c r="EC16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>23.61598104639744</v>
       </c>
       <c r="ED16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>23.379821235933466</v>
       </c>
       <c r="EE16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>23.146023023574131</v>
       </c>
       <c r="EF16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>22.914562793338391</v>
       </c>
       <c r="EG16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>22.685417165405006</v>
       </c>
       <c r="EH16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>22.458562993750956</v>
       </c>
       <c r="EI16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>22.233977363813445</v>
       </c>
       <c r="EJ16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>22.011637590175312</v>
       </c>
       <c r="EK16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>21.791521214273558</v>
       </c>
       <c r="EL16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>21.573606002130823</v>
       </c>
       <c r="EM16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>21.357869942109517</v>
       </c>
       <c r="EN16" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>21.144291242688421</v>
       </c>
     </row>
@@ -3320,143 +3318,143 @@
         <v>26</v>
       </c>
       <c r="M18" s="7">
-        <f>M16/M17</f>
+        <f t="shared" ref="M18:AB18" si="71">M16/M17</f>
         <v>-0.19792302993280386</v>
       </c>
       <c r="N18" s="7">
-        <f>N16/N17</f>
+        <f t="shared" si="71"/>
         <v>-0.29138668295662812</v>
       </c>
       <c r="O18" s="7">
-        <f>O16/O17</f>
+        <f t="shared" si="71"/>
         <v>-0.23457544288332316</v>
       </c>
       <c r="P18" s="7">
-        <f>P16/P17</f>
+        <f t="shared" si="71"/>
         <v>-0.30177153329260847</v>
       </c>
       <c r="Q18" s="7">
-        <f>Q16/Q17</f>
+        <f t="shared" si="71"/>
         <v>-0.21991447770311548</v>
       </c>
       <c r="R18" s="7">
-        <f>R16/R17</f>
+        <f t="shared" si="71"/>
         <v>-0.31459987782529009</v>
       </c>
       <c r="S18" s="7">
-        <f>S16/S17</f>
+        <f t="shared" si="71"/>
         <v>-0.19792302993280386</v>
       </c>
       <c r="T18" s="7">
-        <f>T16/T17</f>
+        <f t="shared" si="71"/>
         <v>-0.19547953573610261</v>
       </c>
       <c r="U18" s="7">
-        <f>U16/U17</f>
+        <f t="shared" si="71"/>
         <v>-0.19547953573610272</v>
       </c>
       <c r="V18" s="7">
-        <f>V16/V17</f>
+        <f t="shared" si="71"/>
         <v>-0.12461820403176541</v>
       </c>
       <c r="W18" s="7">
-        <f>W16/W17</f>
+        <f t="shared" si="71"/>
         <v>-0.1301160659743433</v>
       </c>
       <c r="X18" s="7">
-        <f>X16/X17</f>
+        <f t="shared" si="71"/>
         <v>-0.13989004276114839</v>
       </c>
       <c r="Y18" s="7">
-        <f>Y16/Y17</f>
+        <f t="shared" si="71"/>
         <v>-8.368967623701902E-2</v>
       </c>
       <c r="Z18" s="7">
-        <f>Z16/Z17</f>
+        <f t="shared" si="71"/>
         <v>-0.13194868662186945</v>
       </c>
       <c r="AA18" s="7">
-        <f>AA16/AA17</f>
+        <f t="shared" si="71"/>
         <v>-4.7648136835674884E-2</v>
       </c>
       <c r="AB18" s="7">
-        <f>AB16/AB17</f>
+        <f t="shared" si="71"/>
         <v>-4.7648136835675162E-2</v>
       </c>
       <c r="AC18" s="7">
-        <f t="shared" ref="AC18:AD18" si="61">AC16/AC17</f>
+        <f t="shared" ref="AC18:AD18" si="72">AC16/AC17</f>
         <v>-3.9034819792302999E-2</v>
       </c>
       <c r="AD18" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="72"/>
         <v>-3.664483811850941E-2</v>
       </c>
       <c r="AF18" s="7">
-        <f>AF16/AF17</f>
+        <f t="shared" ref="AF18:AL18" si="73">AF16/AF17</f>
         <v>-0.28527794746487484</v>
       </c>
       <c r="AG18" s="7">
-        <f>AG16/AG17</f>
+        <f t="shared" si="73"/>
         <v>-0.40745265729993896</v>
       </c>
       <c r="AH18" s="7">
-        <f>AH16/AH17</f>
+        <f t="shared" si="73"/>
         <v>-0.88637751985339075</v>
       </c>
       <c r="AI18" s="7">
-        <f>AI16/AI17</f>
+        <f t="shared" si="73"/>
         <v>-1.0708613317043381</v>
       </c>
       <c r="AJ18" s="7">
-        <f>AJ16/AJ17</f>
+        <f t="shared" si="73"/>
         <v>-0.71350030543677478</v>
       </c>
       <c r="AK18" s="7">
-        <f>AK16/AK17</f>
+        <f t="shared" si="73"/>
         <v>-0.4856444715943794</v>
       </c>
       <c r="AL18" s="7">
-        <f>AL16/AL17</f>
+        <f t="shared" si="73"/>
         <v>-0.17097593158216245</v>
       </c>
       <c r="AM18" s="7">
-        <f t="shared" ref="AM18:AN18" si="62">AM16/AM17</f>
+        <f t="shared" ref="AM18:AN18" si="74">AM16/AM17</f>
         <v>4.2037125229077758E-2</v>
       </c>
       <c r="AN18" s="7">
-        <f t="shared" si="62"/>
+        <f t="shared" si="74"/>
         <v>0.16208969816737889</v>
       </c>
       <c r="AO18" s="7">
-        <f t="shared" ref="AO18" si="63">AO16/AO17</f>
+        <f t="shared" ref="AO18" si="75">AO16/AO17</f>
         <v>0.27869571203310939</v>
       </c>
       <c r="AP18" s="7">
-        <f t="shared" ref="AP18" si="64">AP16/AP17</f>
+        <f t="shared" ref="AP18" si="76">AP16/AP17</f>
         <v>0.29397382579619641</v>
       </c>
       <c r="AQ18" s="7">
-        <f t="shared" ref="AQ18" si="65">AQ16/AQ17</f>
+        <f t="shared" ref="AQ18" si="77">AQ16/AQ17</f>
         <v>0.30965454382977009</v>
       </c>
       <c r="AR18" s="7">
-        <f t="shared" ref="AR18" si="66">AR16/AR17</f>
+        <f t="shared" ref="AR18" si="78">AR16/AR17</f>
         <v>0.32574688863919088</v>
       </c>
       <c r="AS18" s="7">
-        <f t="shared" ref="AS18" si="67">AS16/AS17</f>
+        <f t="shared" ref="AS18" si="79">AS16/AS17</f>
         <v>0.3290043575255826</v>
       </c>
       <c r="AT18" s="7">
-        <f t="shared" ref="AT18" si="68">AT16/AT17</f>
+        <f t="shared" ref="AT18" si="80">AT16/AT17</f>
         <v>0.33229440110083874</v>
       </c>
       <c r="AU18" s="7">
-        <f t="shared" ref="AU18" si="69">AU16/AU17</f>
+        <f t="shared" ref="AU18" si="81">AU16/AU17</f>
         <v>0.33561734511184738</v>
       </c>
       <c r="AV18" s="7">
-        <f t="shared" ref="AV18" si="70">AV16/AV17</f>
+        <f t="shared" ref="AV18" si="82">AV16/AV17</f>
         <v>0.33897351856296593</v>
       </c>
     </row>
@@ -3464,129 +3462,129 @@
       <c r="B20" t="s">
         <v>55</v>
       </c>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10">
-        <f t="shared" ref="M20:AA20" si="71">Q3/M3-1</f>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9">
+        <f t="shared" ref="Q20:AA20" si="83">Q3/M3-1</f>
         <v>0.2411282984531391</v>
       </c>
-      <c r="R20" s="10">
-        <f t="shared" si="71"/>
+      <c r="R20" s="9">
+        <f t="shared" si="83"/>
         <v>0.23652173913043462</v>
       </c>
-      <c r="S20" s="10">
-        <f t="shared" si="71"/>
+      <c r="S20" s="9">
+        <f t="shared" si="83"/>
         <v>0.2259136212624584</v>
       </c>
-      <c r="T20" s="10">
-        <f t="shared" si="71"/>
+      <c r="T20" s="9">
+        <f t="shared" si="83"/>
         <v>0.23157051282051277</v>
       </c>
-      <c r="U20" s="10">
-        <f t="shared" si="71"/>
+      <c r="U20" s="9">
+        <f t="shared" si="83"/>
         <v>0.21334310850439886</v>
       </c>
-      <c r="V20" s="10">
-        <f t="shared" si="71"/>
+      <c r="V20" s="9">
+        <f t="shared" si="83"/>
         <v>0.18776371308016881</v>
       </c>
-      <c r="W20" s="10">
-        <f t="shared" si="71"/>
+      <c r="W20" s="9">
+        <f t="shared" si="83"/>
         <v>0.14566395663956633</v>
       </c>
-      <c r="X20" s="10">
-        <f t="shared" si="71"/>
+      <c r="X20" s="9">
+        <f t="shared" si="83"/>
         <v>0.10800260247234883</v>
       </c>
-      <c r="Y20" s="10">
-        <f t="shared" si="71"/>
+      <c r="Y20" s="9">
+        <f t="shared" si="83"/>
         <v>6.4048338368579927E-2</v>
       </c>
-      <c r="Z20" s="10">
-        <f t="shared" si="71"/>
+      <c r="Z20" s="9">
+        <f t="shared" si="83"/>
         <v>6.0982830076968586E-2</v>
       </c>
-      <c r="AA20" s="10">
-        <f t="shared" si="71"/>
+      <c r="AA20" s="9">
+        <f t="shared" si="83"/>
         <v>6.0319337670017736E-2</v>
       </c>
-      <c r="AB20" s="10">
+      <c r="AB20" s="9">
         <f>AB3/X3-1</f>
         <v>9.8649442160892331E-2</v>
       </c>
-      <c r="AC20" s="10">
-        <f t="shared" ref="AC20:AD20" si="72">AC3/Y3-1</f>
+      <c r="AC20" s="9">
+        <f t="shared" ref="AC20:AD20" si="84">AC3/Y3-1</f>
         <v>7.8932424758659803E-2</v>
       </c>
-      <c r="AD20" s="10">
-        <f t="shared" si="72"/>
+      <c r="AD20" s="9">
+        <f t="shared" si="84"/>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="AF20" s="10"/>
-      <c r="AG20" s="10">
-        <f t="shared" ref="AF20:AK20" si="73">AG3/AF3-1</f>
+      <c r="AF20" s="9"/>
+      <c r="AG20" s="9">
+        <f t="shared" ref="AG20:AJ20" si="85">AG3/AF3-1</f>
         <v>0.5916485900216919</v>
       </c>
-      <c r="AH20" s="10">
-        <f t="shared" si="73"/>
+      <c r="AH20" s="9">
+        <f t="shared" si="85"/>
         <v>0.41499148211243608</v>
       </c>
-      <c r="AI20" s="10">
-        <f t="shared" si="73"/>
+      <c r="AI20" s="9">
+        <f t="shared" si="85"/>
         <v>0.26125692270647716</v>
       </c>
-      <c r="AJ20" s="10">
-        <f t="shared" si="73"/>
+      <c r="AJ20" s="9">
+        <f t="shared" si="85"/>
         <v>0.21363115693012591</v>
       </c>
-      <c r="AK20" s="10">
+      <c r="AK20" s="9">
         <f>AK3/AJ3-1</f>
         <v>9.2811074406166538E-2</v>
       </c>
-      <c r="AL20" s="10">
-        <f t="shared" ref="AL20:AV20" si="74">AL3/AK3-1</f>
+      <c r="AL20" s="9">
+        <f t="shared" ref="AL20:AV20" si="86">AL3/AK3-1</f>
         <v>7.693104937383044E-2</v>
       </c>
-      <c r="AM20" s="10">
-        <f t="shared" si="74"/>
+      <c r="AM20" s="9">
+        <f t="shared" si="86"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AN20" s="10">
-        <f t="shared" si="74"/>
+      <c r="AN20" s="9">
+        <f t="shared" si="86"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AO20" s="10">
-        <f t="shared" si="74"/>
+      <c r="AO20" s="9">
+        <f t="shared" si="86"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AP20" s="10">
-        <f t="shared" si="74"/>
+      <c r="AP20" s="9">
+        <f t="shared" si="86"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AQ20" s="10">
-        <f t="shared" si="74"/>
+      <c r="AQ20" s="9">
+        <f t="shared" si="86"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AR20" s="10">
-        <f t="shared" si="74"/>
+      <c r="AR20" s="9">
+        <f t="shared" si="86"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AS20" s="10">
-        <f t="shared" si="74"/>
+      <c r="AS20" s="9">
+        <f t="shared" si="86"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AT20" s="10">
-        <f t="shared" si="74"/>
+      <c r="AT20" s="9">
+        <f t="shared" si="86"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AU20" s="10">
-        <f t="shared" si="74"/>
+      <c r="AU20" s="9">
+        <f t="shared" si="86"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AV20" s="10">
-        <f t="shared" si="74"/>
+      <c r="AV20" s="9">
+        <f t="shared" si="86"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -3594,150 +3592,150 @@
       <c r="B21" t="s">
         <v>54</v>
       </c>
-      <c r="M21" s="10">
-        <f t="shared" ref="M21:AB21" si="75">M5/M3</f>
+      <c r="M21" s="9">
+        <f t="shared" ref="M21:AA21" si="87">M5/M3</f>
         <v>0.61601455868971788</v>
       </c>
-      <c r="N21" s="10">
-        <f t="shared" si="75"/>
+      <c r="N21" s="9">
+        <f t="shared" si="87"/>
         <v>0.62</v>
       </c>
-      <c r="O21" s="10">
-        <f t="shared" si="75"/>
+      <c r="O21" s="9">
+        <f t="shared" si="87"/>
         <v>0.64451827242524917</v>
       </c>
-      <c r="P21" s="10">
-        <f t="shared" si="75"/>
+      <c r="P21" s="9">
+        <f t="shared" si="87"/>
         <v>0.6282051282051283</v>
       </c>
-      <c r="Q21" s="10">
-        <f t="shared" si="75"/>
+      <c r="Q21" s="9">
+        <f t="shared" si="87"/>
         <v>0.64222873900293254</v>
       </c>
-      <c r="R21" s="10">
-        <f t="shared" si="75"/>
+      <c r="R21" s="9">
+        <f t="shared" si="87"/>
         <v>0.61814345991561181</v>
       </c>
-      <c r="S21" s="10">
-        <f t="shared" si="75"/>
+      <c r="S21" s="9">
+        <f t="shared" si="87"/>
         <v>0.52439024390243894</v>
       </c>
-      <c r="T21" s="10">
-        <f t="shared" si="75"/>
+      <c r="T21" s="9">
+        <f t="shared" si="87"/>
         <v>0.51854261548471048</v>
       </c>
-      <c r="U21" s="10">
-        <f t="shared" si="75"/>
+      <c r="U21" s="9">
+        <f t="shared" si="87"/>
         <v>0.50271903323262845</v>
       </c>
-      <c r="V21" s="10">
-        <f t="shared" si="75"/>
+      <c r="V21" s="9">
+        <f t="shared" si="87"/>
         <v>0.52871521610420369</v>
       </c>
-      <c r="W21" s="10">
-        <f t="shared" si="75"/>
+      <c r="W21" s="9">
+        <f t="shared" si="87"/>
         <v>0.52927261975162632</v>
       </c>
-      <c r="X21" s="10">
-        <f t="shared" si="75"/>
+      <c r="X21" s="9">
+        <f t="shared" si="87"/>
         <v>0.52965355255431601</v>
       </c>
-      <c r="Y21" s="10">
-        <f t="shared" si="75"/>
+      <c r="Y21" s="9">
+        <f t="shared" si="87"/>
         <v>0.54628052243043723</v>
       </c>
-      <c r="Z21" s="10">
-        <f t="shared" si="75"/>
+      <c r="Z21" s="9">
+        <f t="shared" si="87"/>
         <v>0.5329241071428571</v>
       </c>
-      <c r="AA21" s="10">
-        <f t="shared" si="75"/>
+      <c r="AA21" s="9">
+        <f t="shared" si="87"/>
         <v>0.54601226993865026</v>
       </c>
-      <c r="AB21" s="10">
+      <c r="AB21" s="9">
         <f>AB5/AB3</f>
         <v>0.54890432923570276</v>
       </c>
-      <c r="AC21" s="10">
-        <f t="shared" ref="AC21:AD21" si="76">AC5/AC3</f>
+      <c r="AC21" s="9">
+        <f t="shared" ref="AC21:AD21" si="88">AC5/AC3</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="AD21" s="10">
-        <f t="shared" si="76"/>
+      <c r="AD21" s="9">
+        <f t="shared" si="88"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="AF21" s="10">
-        <f t="shared" ref="AF21:AK21" si="77">AF5/AF3</f>
+      <c r="AF21" s="9">
+        <f t="shared" ref="AF21:AJ21" si="89">AF5/AF3</f>
         <v>0.51409978308026039</v>
       </c>
-      <c r="AG21" s="10">
-        <f t="shared" si="77"/>
+      <c r="AG21" s="9">
+        <f t="shared" si="89"/>
         <v>0.52708688245315161</v>
       </c>
-      <c r="AH21" s="10">
-        <f t="shared" si="77"/>
+      <c r="AH21" s="9">
+        <f t="shared" si="89"/>
         <v>0.6007705273296412</v>
       </c>
-      <c r="AI21" s="10">
-        <f t="shared" si="77"/>
+      <c r="AI21" s="9">
+        <f t="shared" si="89"/>
         <v>0.63287514318442151</v>
       </c>
-      <c r="AJ21" s="10">
-        <f t="shared" si="77"/>
+      <c r="AJ21" s="9">
+        <f t="shared" si="89"/>
         <v>0.51848356142834662</v>
       </c>
-      <c r="AK21" s="10">
-        <f t="shared" ref="AK21:AV21" si="78">AK5/AK3</f>
+      <c r="AK21" s="9">
+        <f t="shared" ref="AK21:AV21" si="90">AK5/AK3</f>
         <v>0.53461926011227867</v>
       </c>
-      <c r="AL21" s="10">
-        <f t="shared" si="78"/>
+      <c r="AL21" s="9">
+        <f t="shared" si="90"/>
         <v>0.54877029021151014</v>
       </c>
-      <c r="AM21" s="10">
-        <f t="shared" si="78"/>
+      <c r="AM21" s="9">
+        <f t="shared" si="90"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="AN21" s="10">
-        <f t="shared" si="78"/>
+      <c r="AN21" s="9">
+        <f t="shared" si="90"/>
         <v>0.56999999999999995</v>
       </c>
-      <c r="AO21" s="10">
-        <f t="shared" si="78"/>
+      <c r="AO21" s="9">
+        <f t="shared" si="90"/>
         <v>0.57999999999999996</v>
       </c>
-      <c r="AP21" s="10">
-        <f t="shared" si="78"/>
+      <c r="AP21" s="9">
+        <f t="shared" si="90"/>
         <v>0.57999999999999996</v>
       </c>
-      <c r="AQ21" s="10">
-        <f t="shared" si="78"/>
+      <c r="AQ21" s="9">
+        <f t="shared" si="90"/>
         <v>0.57999999999999996</v>
       </c>
-      <c r="AR21" s="10">
-        <f t="shared" si="78"/>
+      <c r="AR21" s="9">
+        <f t="shared" si="90"/>
         <v>0.57999999999999996</v>
       </c>
-      <c r="AS21" s="10">
-        <f t="shared" si="78"/>
+      <c r="AS21" s="9">
+        <f t="shared" si="90"/>
         <v>0.57999999999999996</v>
       </c>
-      <c r="AT21" s="10">
-        <f t="shared" si="78"/>
+      <c r="AT21" s="9">
+        <f t="shared" si="90"/>
         <v>0.57999999999999996</v>
       </c>
-      <c r="AU21" s="10">
-        <f t="shared" si="78"/>
+      <c r="AU21" s="9">
+        <f t="shared" si="90"/>
         <v>0.58000000000000007</v>
       </c>
-      <c r="AV21" s="10">
-        <f t="shared" si="78"/>
+      <c r="AV21" s="9">
+        <f t="shared" si="90"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="AX21" t="s">
         <v>61</v>
       </c>
-      <c r="AY21" s="10">
+      <c r="AY21" s="9">
         <v>-0.01</v>
       </c>
     </row>
@@ -3745,135 +3743,135 @@
       <c r="B22" t="s">
         <v>56</v>
       </c>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10">
-        <f t="shared" ref="M22:AA22" si="79">Q6/M6-1</f>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9">
+        <f t="shared" ref="Q22:AA22" si="91">Q6/M6-1</f>
         <v>0.16224188790560468</v>
       </c>
-      <c r="R22" s="10">
-        <f t="shared" si="79"/>
+      <c r="R22" s="9">
+        <f t="shared" si="91"/>
         <v>0.11749347258485643</v>
       </c>
-      <c r="S22" s="10">
-        <f t="shared" si="79"/>
+      <c r="S22" s="9">
+        <f t="shared" si="91"/>
         <v>0.15263157894736845</v>
       </c>
-      <c r="T22" s="10">
-        <f t="shared" si="79"/>
+      <c r="T22" s="9">
+        <f t="shared" si="91"/>
         <v>-8.0178173719376411E-2</v>
       </c>
-      <c r="U22" s="10">
-        <f t="shared" si="79"/>
+      <c r="U22" s="9">
+        <f t="shared" si="91"/>
         <v>-4.5685279187817174E-2</v>
       </c>
-      <c r="V22" s="10">
-        <f t="shared" si="79"/>
+      <c r="V22" s="9">
+        <f t="shared" si="91"/>
         <v>-0.12616822429906538</v>
       </c>
-      <c r="W22" s="10">
-        <f t="shared" si="79"/>
+      <c r="W22" s="9">
+        <f t="shared" si="91"/>
         <v>-0.2100456621004565</v>
       </c>
-      <c r="X22" s="10">
-        <f t="shared" si="79"/>
+      <c r="X22" s="9">
+        <f t="shared" si="91"/>
         <v>-0.18401937046004835</v>
       </c>
-      <c r="Y22" s="10">
-        <f t="shared" si="79"/>
+      <c r="Y22" s="9">
+        <f t="shared" si="91"/>
         <v>-0.15957446808510634</v>
       </c>
-      <c r="Z22" s="10">
-        <f t="shared" si="79"/>
+      <c r="Z22" s="9">
+        <f t="shared" si="91"/>
         <v>-0.14171122994652396</v>
       </c>
-      <c r="AA22" s="10">
-        <f t="shared" si="79"/>
+      <c r="AA22" s="9">
+        <f t="shared" si="91"/>
         <v>-0.14739884393063585</v>
       </c>
-      <c r="AB22" s="10">
+      <c r="AB22" s="9">
         <f>AB6/X6-1</f>
         <v>-0.13056379821958464</v>
       </c>
-      <c r="AC22" s="10">
-        <f t="shared" ref="AC22:AD22" si="80">AC6/Y6-1</f>
+      <c r="AC22" s="9">
+        <f t="shared" ref="AC22:AD22" si="92">AC6/Y6-1</f>
         <v>-0.12</v>
       </c>
-      <c r="AD22" s="10">
-        <f t="shared" si="80"/>
+      <c r="AD22" s="9">
+        <f t="shared" si="92"/>
         <v>-0.12</v>
       </c>
-      <c r="AF22" s="10"/>
-      <c r="AG22" s="10">
-        <f t="shared" ref="AF22:AK22" si="81">AG6/AF6-1</f>
+      <c r="AF22" s="9"/>
+      <c r="AG22" s="9">
+        <f t="shared" ref="AG22:AJ22" si="93">AG6/AF6-1</f>
         <v>0.36170212765957444</v>
       </c>
-      <c r="AH22" s="10">
-        <f t="shared" si="81"/>
+      <c r="AH22" s="9">
+        <f t="shared" si="93"/>
         <v>0.76302083333333348</v>
       </c>
-      <c r="AI22" s="10">
-        <f t="shared" si="81"/>
+      <c r="AI22" s="9">
+        <f t="shared" si="93"/>
         <v>0.21935007385524385</v>
       </c>
-      <c r="AJ22" s="10">
-        <f t="shared" si="81"/>
+      <c r="AJ22" s="9">
+        <f t="shared" si="93"/>
         <v>-3.0284675953967444E-2</v>
       </c>
-      <c r="AK22" s="10">
+      <c r="AK22" s="9">
         <f>AK6/AJ6-1</f>
         <v>-0.1755153029356652</v>
       </c>
-      <c r="AL22" s="10">
-        <f t="shared" ref="AL22:AV22" si="82">AL6/AK6-1</f>
+      <c r="AL22" s="9">
+        <f t="shared" ref="AL22:AV22" si="94">AL6/AK6-1</f>
         <v>-0.12987878787878782</v>
       </c>
-      <c r="AM22" s="10">
-        <f t="shared" si="82"/>
+      <c r="AM22" s="9">
+        <f t="shared" si="94"/>
         <v>-6.0000000000000053E-2</v>
       </c>
-      <c r="AN22" s="10">
-        <f t="shared" si="82"/>
+      <c r="AN22" s="9">
+        <f t="shared" si="94"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AO22" s="10">
-        <f t="shared" si="82"/>
+      <c r="AO22" s="9">
+        <f t="shared" si="94"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AP22" s="10">
-        <f t="shared" si="82"/>
+      <c r="AP22" s="9">
+        <f t="shared" si="94"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AQ22" s="10">
-        <f t="shared" si="82"/>
+      <c r="AQ22" s="9">
+        <f t="shared" si="94"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AR22" s="10">
-        <f t="shared" si="82"/>
+      <c r="AR22" s="9">
+        <f t="shared" si="94"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AS22" s="10">
-        <f t="shared" si="82"/>
+      <c r="AS22" s="9">
+        <f t="shared" si="94"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AT22" s="10">
-        <f t="shared" si="82"/>
+      <c r="AT22" s="9">
+        <f t="shared" si="94"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AU22" s="10">
-        <f t="shared" si="82"/>
+      <c r="AU22" s="9">
+        <f t="shared" si="94"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AV22" s="10">
-        <f t="shared" si="82"/>
+      <c r="AV22" s="9">
+        <f t="shared" si="94"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX22" t="s">
         <v>62</v>
       </c>
-      <c r="AY22" s="10">
+      <c r="AY22" s="9">
         <v>0.1</v>
       </c>
     </row>
@@ -3881,144 +3879,144 @@
       <c r="B23" t="s">
         <v>57</v>
       </c>
-      <c r="M23" s="10">
-        <f t="shared" ref="M23:AB23" si="83">M7/M3</f>
+      <c r="M23" s="9">
+        <f t="shared" ref="M23:AA23" si="95">M7/M3</f>
         <v>0.41219290263876246</v>
       </c>
-      <c r="N23" s="10">
-        <f t="shared" si="83"/>
+      <c r="N23" s="9">
+        <f t="shared" si="95"/>
         <v>0.50086956521739134</v>
       </c>
-      <c r="O23" s="10">
-        <f t="shared" si="83"/>
+      <c r="O23" s="9">
+        <f t="shared" si="95"/>
         <v>0.42940199335548174</v>
       </c>
-      <c r="P23" s="10">
-        <f t="shared" si="83"/>
+      <c r="P23" s="9">
+        <f t="shared" si="95"/>
         <v>0.44551282051282054</v>
       </c>
-      <c r="Q23" s="10">
-        <f t="shared" si="83"/>
+      <c r="Q23" s="9">
+        <f t="shared" si="95"/>
         <v>0.42888563049853373</v>
       </c>
-      <c r="R23" s="10">
-        <f t="shared" si="83"/>
+      <c r="R23" s="9">
+        <f t="shared" si="95"/>
         <v>0.43530239099859358</v>
       </c>
-      <c r="S23" s="10">
-        <f t="shared" si="83"/>
+      <c r="S23" s="9">
+        <f t="shared" si="95"/>
         <v>0.35840108401084009</v>
       </c>
-      <c r="T23" s="10">
-        <f t="shared" si="83"/>
+      <c r="T23" s="9">
+        <f t="shared" si="95"/>
         <v>0.33832140533506833</v>
       </c>
-      <c r="U23" s="10">
-        <f t="shared" si="83"/>
+      <c r="U23" s="9">
+        <f t="shared" si="95"/>
         <v>0.36132930513595163</v>
       </c>
-      <c r="V23" s="10">
-        <f t="shared" si="83"/>
+      <c r="V23" s="9">
+        <f t="shared" si="95"/>
         <v>0.34399052693901716</v>
       </c>
-      <c r="W23" s="10">
-        <f t="shared" si="83"/>
+      <c r="W23" s="9">
+        <f t="shared" si="95"/>
         <v>0.34062684801892373</v>
       </c>
-      <c r="X23" s="10">
-        <f t="shared" si="83"/>
+      <c r="X23" s="9">
+        <f t="shared" si="95"/>
         <v>0.34116265413975339</v>
       </c>
-      <c r="Y23" s="10">
-        <f t="shared" si="83"/>
+      <c r="Y23" s="9">
+        <f t="shared" si="95"/>
         <v>0.3350369108461102</v>
       </c>
-      <c r="Z23" s="10">
-        <f t="shared" si="83"/>
+      <c r="Z23" s="9">
+        <f t="shared" si="95"/>
         <v>0.33593750000000006</v>
       </c>
-      <c r="AA23" s="10">
-        <f t="shared" si="83"/>
+      <c r="AA23" s="9">
+        <f t="shared" si="95"/>
         <v>0.316787506971556</v>
       </c>
-      <c r="AB23" s="10">
+      <c r="AB23" s="9">
         <f>AB7/AB3</f>
         <v>0.33992517370390168</v>
       </c>
-      <c r="AC23" s="10">
-        <f t="shared" ref="AC23:AD23" si="84">AC7/AC3</f>
+      <c r="AC23" s="9">
+        <f t="shared" ref="AC23:AD23" si="96">AC7/AC3</f>
         <v>0.34</v>
       </c>
-      <c r="AD23" s="10">
-        <f t="shared" si="84"/>
+      <c r="AD23" s="9">
+        <f t="shared" si="96"/>
         <v>0.34</v>
       </c>
-      <c r="AF23" s="10">
-        <f t="shared" ref="AF23:AK23" si="85">AF7/AF3</f>
+      <c r="AF23" s="9">
+        <f t="shared" ref="AF23:AJ23" si="97">AF7/AF3</f>
         <v>0.30911062906724512</v>
       </c>
-      <c r="AG23" s="10">
-        <f t="shared" si="85"/>
+      <c r="AG23" s="9">
+        <f t="shared" si="97"/>
         <v>0.36524701873935267</v>
       </c>
-      <c r="AH23" s="10">
-        <f t="shared" si="85"/>
+      <c r="AH23" s="9">
+        <f t="shared" si="97"/>
         <v>0.43173609438959792</v>
       </c>
-      <c r="AI23" s="10">
-        <f t="shared" si="85"/>
+      <c r="AI23" s="9">
+        <f t="shared" si="97"/>
         <v>0.43470790378006879</v>
       </c>
-      <c r="AJ23" s="10">
-        <f t="shared" si="85"/>
+      <c r="AJ23" s="9">
+        <f t="shared" si="97"/>
         <v>0.35047978606260816</v>
       </c>
-      <c r="AK23" s="10">
-        <f t="shared" ref="AK23:AV23" si="86">AK7/AK3</f>
+      <c r="AK23" s="9">
+        <f t="shared" ref="AK23:AV23" si="98">AK7/AK3</f>
         <v>0.33813156758312934</v>
       </c>
-      <c r="AL23" s="10">
-        <f t="shared" si="86"/>
+      <c r="AL23" s="9">
+        <f t="shared" si="98"/>
         <v>0.33441818687311531</v>
       </c>
-      <c r="AM23" s="10">
-        <f t="shared" si="86"/>
+      <c r="AM23" s="9">
+        <f t="shared" si="98"/>
         <v>0.33</v>
       </c>
-      <c r="AN23" s="10">
-        <f t="shared" si="86"/>
+      <c r="AN23" s="9">
+        <f t="shared" si="98"/>
         <v>0.32</v>
       </c>
-      <c r="AO23" s="10">
-        <f t="shared" si="86"/>
+      <c r="AO23" s="9">
+        <f t="shared" si="98"/>
         <v>0.31</v>
       </c>
-      <c r="AP23" s="10">
-        <f t="shared" si="86"/>
+      <c r="AP23" s="9">
+        <f t="shared" si="98"/>
         <v>0.31</v>
       </c>
-      <c r="AQ23" s="10">
-        <f t="shared" si="86"/>
+      <c r="AQ23" s="9">
+        <f t="shared" si="98"/>
         <v>0.31</v>
       </c>
-      <c r="AR23" s="10">
-        <f t="shared" si="86"/>
+      <c r="AR23" s="9">
+        <f t="shared" si="98"/>
         <v>0.31</v>
       </c>
-      <c r="AS23" s="10">
-        <f t="shared" si="86"/>
+      <c r="AS23" s="9">
+        <f t="shared" si="98"/>
         <v>0.31</v>
       </c>
-      <c r="AT23" s="10">
-        <f t="shared" si="86"/>
+      <c r="AT23" s="9">
+        <f t="shared" si="98"/>
         <v>0.31</v>
       </c>
-      <c r="AU23" s="10">
-        <f t="shared" si="86"/>
+      <c r="AU23" s="9">
+        <f t="shared" si="98"/>
         <v>0.31</v>
       </c>
-      <c r="AV23" s="10">
-        <f t="shared" si="86"/>
+      <c r="AV23" s="9">
+        <f t="shared" si="98"/>
         <v>0.31</v>
       </c>
       <c r="AX23" t="s">
@@ -4033,129 +4031,129 @@
       <c r="B24" t="s">
         <v>58</v>
       </c>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="10">
-        <f t="shared" ref="M24:AA24" si="87">Q8/M8-1</f>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9">
+        <f t="shared" ref="Q24:AA24" si="99">Q8/M8-1</f>
         <v>0.30653266331658302</v>
       </c>
-      <c r="R24" s="10">
-        <f t="shared" si="87"/>
+      <c r="R24" s="9">
+        <f t="shared" si="99"/>
         <v>0.26637554585152845</v>
       </c>
-      <c r="S24" s="10">
-        <f t="shared" si="87"/>
+      <c r="S24" s="9">
+        <f t="shared" si="99"/>
         <v>1.1904761904761862E-2</v>
       </c>
-      <c r="T24" s="10">
-        <f t="shared" si="87"/>
+      <c r="T24" s="9">
+        <f t="shared" si="99"/>
         <v>-3.1128404669260701E-2</v>
       </c>
-      <c r="U24" s="10">
-        <f t="shared" si="87"/>
+      <c r="U24" s="9">
+        <f t="shared" si="99"/>
         <v>-2.3076923076923106E-2</v>
       </c>
-      <c r="V24" s="10">
-        <f t="shared" si="87"/>
+      <c r="V24" s="9">
+        <f t="shared" si="99"/>
         <v>-0.22758620689655173</v>
       </c>
-      <c r="W24" s="10">
-        <f t="shared" si="87"/>
+      <c r="W24" s="9">
+        <f t="shared" si="99"/>
         <v>-1.9607843137254943E-2</v>
       </c>
-      <c r="X24" s="10">
-        <f t="shared" si="87"/>
+      <c r="X24" s="9">
+        <f t="shared" si="99"/>
         <v>0.18875502008032141</v>
       </c>
-      <c r="Y24" s="10">
-        <f t="shared" si="87"/>
+      <c r="Y24" s="9">
+        <f t="shared" si="99"/>
         <v>7.8740157480315043E-2</v>
       </c>
-      <c r="Z24" s="10">
-        <f t="shared" si="87"/>
+      <c r="Z24" s="9">
+        <f t="shared" si="99"/>
         <v>0.20089285714285721</v>
       </c>
-      <c r="AA24" s="10">
-        <f t="shared" si="87"/>
+      <c r="AA24" s="9">
+        <f t="shared" si="99"/>
         <v>7.5999999999999845E-2</v>
       </c>
-      <c r="AB24" s="10">
+      <c r="AB24" s="9">
         <f>AB8/X8-1</f>
         <v>-0.15878378378378388</v>
       </c>
-      <c r="AC24" s="10">
-        <f t="shared" ref="AC24:AD24" si="88">AC8/Y8-1</f>
+      <c r="AC24" s="9">
+        <f t="shared" ref="AC24:AD24" si="100">AC8/Y8-1</f>
         <v>-6.9999999999999951E-2</v>
       </c>
-      <c r="AD24" s="10">
-        <f t="shared" si="88"/>
+      <c r="AD24" s="9">
+        <f t="shared" si="100"/>
         <v>-6.9999999999999951E-2</v>
       </c>
-      <c r="AF24" s="10"/>
-      <c r="AG24" s="10">
-        <f t="shared" ref="AF24:AK24" si="89">AG8/AF8-1</f>
+      <c r="AF24" s="9"/>
+      <c r="AG24" s="9">
+        <f t="shared" ref="AG24:AJ24" si="101">AG8/AF8-1</f>
         <v>0.24832214765100669</v>
       </c>
-      <c r="AH24" s="10">
-        <f t="shared" si="89"/>
+      <c r="AH24" s="9">
+        <f t="shared" si="101"/>
         <v>1.0913978494623655</v>
       </c>
-      <c r="AI24" s="10">
-        <f t="shared" si="89"/>
+      <c r="AI24" s="9">
+        <f t="shared" si="101"/>
         <v>0.36118251928020584</v>
       </c>
-      <c r="AJ24" s="10">
-        <f t="shared" si="89"/>
+      <c r="AJ24" s="9">
+        <f t="shared" si="101"/>
         <v>-7.271010387157717E-2</v>
       </c>
-      <c r="AK24" s="10">
+      <c r="AK24" s="9">
         <f>AK8/AJ8-1</f>
         <v>0.10896130346232202</v>
       </c>
-      <c r="AL24" s="10">
-        <f t="shared" ref="AL24:AV24" si="90">AL8/AK8-1</f>
+      <c r="AL24" s="9">
+        <f t="shared" ref="AL24:AV24" si="102">AL8/AK8-1</f>
         <v>-6.0615243342516223E-2</v>
       </c>
-      <c r="AM24" s="10">
-        <f t="shared" si="90"/>
+      <c r="AM24" s="9">
+        <f t="shared" si="102"/>
         <v>-5.0000000000000044E-2</v>
       </c>
-      <c r="AN24" s="10">
-        <f t="shared" si="90"/>
+      <c r="AN24" s="9">
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AO24" s="10">
-        <f t="shared" si="90"/>
+      <c r="AO24" s="9">
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AP24" s="10">
-        <f t="shared" si="90"/>
+      <c r="AP24" s="9">
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AQ24" s="10">
-        <f t="shared" si="90"/>
+      <c r="AQ24" s="9">
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AR24" s="10">
-        <f t="shared" si="90"/>
+      <c r="AR24" s="9">
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AS24" s="10">
-        <f t="shared" si="90"/>
+      <c r="AS24" s="9">
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AT24" s="10">
-        <f t="shared" si="90"/>
+      <c r="AT24" s="9">
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AU24" s="10">
-        <f t="shared" si="90"/>
+      <c r="AU24" s="9">
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AV24" s="10">
-        <f t="shared" si="90"/>
+      <c r="AV24" s="9">
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX24" t="s">
@@ -4170,144 +4168,144 @@
       <c r="B25" t="s">
         <v>59</v>
       </c>
-      <c r="M25" s="10">
-        <f t="shared" ref="M25:AB25" si="91">M11/M3</f>
+      <c r="M25" s="9">
+        <f t="shared" ref="M25:AA25" si="103">M11/M3</f>
         <v>-0.28571428571428564</v>
       </c>
-      <c r="N25" s="10">
-        <f t="shared" si="91"/>
+      <c r="N25" s="9">
+        <f t="shared" si="103"/>
         <v>-0.41304347826086968</v>
       </c>
-      <c r="O25" s="10">
-        <f t="shared" si="91"/>
+      <c r="O25" s="9">
+        <f t="shared" si="103"/>
         <v>-0.30980066445182719</v>
       </c>
-      <c r="P25" s="10">
-        <f t="shared" si="91"/>
+      <c r="P25" s="9">
+        <f t="shared" si="103"/>
         <v>-0.38301282051282048</v>
       </c>
-      <c r="Q25" s="10">
-        <f t="shared" si="91"/>
+      <c r="Q25" s="9">
+        <f t="shared" si="103"/>
         <v>-0.2661290322580645</v>
       </c>
-      <c r="R25" s="10">
-        <f t="shared" si="91"/>
+      <c r="R25" s="9">
+        <f t="shared" si="103"/>
         <v>-0.39310829817158927</v>
       </c>
-      <c r="S25" s="10">
-        <f t="shared" si="91"/>
+      <c r="S25" s="9">
+        <f t="shared" si="103"/>
         <v>-0.26490514905149048</v>
       </c>
-      <c r="T25" s="10">
-        <f t="shared" si="91"/>
+      <c r="T25" s="9">
+        <f t="shared" si="103"/>
         <v>-0.25113858165256991</v>
       </c>
-      <c r="U25" s="10">
-        <f t="shared" si="91"/>
+      <c r="U25" s="9">
+        <f t="shared" si="103"/>
         <v>-0.23927492447129914</v>
       </c>
-      <c r="V25" s="10">
-        <f t="shared" si="91"/>
+      <c r="V25" s="9">
+        <f t="shared" si="103"/>
         <v>-0.16933096506808759</v>
       </c>
-      <c r="W25" s="10">
-        <f t="shared" si="91"/>
+      <c r="W25" s="9">
+        <f t="shared" si="103"/>
         <v>-0.17622708456534594</v>
       </c>
-      <c r="X25" s="10">
-        <f t="shared" si="91"/>
+      <c r="X25" s="9">
+        <f t="shared" si="103"/>
         <v>-0.18320610687022892</v>
       </c>
-      <c r="Y25" s="10">
-        <f t="shared" si="91"/>
+      <c r="Y25" s="9">
+        <f t="shared" si="103"/>
         <v>-0.12379329926178315</v>
       </c>
-      <c r="Z25" s="10">
-        <f t="shared" si="91"/>
+      <c r="Z25" s="9">
+        <f t="shared" si="103"/>
         <v>-0.17020089285714302</v>
       </c>
-      <c r="AA25" s="10">
-        <f t="shared" si="91"/>
+      <c r="AA25" s="9">
+        <f t="shared" si="103"/>
         <v>-8.0312325711098587E-2</v>
       </c>
-      <c r="AB25" s="10">
+      <c r="AB25" s="9">
         <f>AB11/AB3</f>
         <v>-8.0705505077498782E-2</v>
       </c>
-      <c r="AC25" s="10">
-        <f t="shared" ref="AC25:AD25" si="92">AC11/AC3</f>
+      <c r="AC25" s="9">
+        <f t="shared" ref="AC25:AD25" si="104">AC11/AC3</f>
         <v>-7.0473684210526313E-2</v>
       </c>
-      <c r="AD25" s="10">
-        <f t="shared" si="92"/>
+      <c r="AD25" s="9">
+        <f t="shared" si="104"/>
         <v>-6.7792264686248285E-2</v>
       </c>
-      <c r="AF25" s="10">
-        <f t="shared" ref="AF25:AK25" si="93">AF11/AF3</f>
+      <c r="AF25" s="9">
+        <f t="shared" ref="AF25:AJ25" si="105">AF11/AF3</f>
         <v>-0.26247288503253796</v>
       </c>
-      <c r="AG25" s="10">
-        <f t="shared" si="93"/>
+      <c r="AG25" s="9">
+        <f t="shared" si="105"/>
         <v>-0.22657580919931858</v>
       </c>
-      <c r="AH25" s="10">
-        <f t="shared" si="93"/>
+      <c r="AH25" s="9">
+        <f t="shared" si="105"/>
         <v>-0.34432940043342175</v>
       </c>
-      <c r="AI25" s="10">
-        <f t="shared" si="93"/>
+      <c r="AI25" s="9">
+        <f t="shared" si="105"/>
         <v>-0.33848797250859131</v>
       </c>
-      <c r="AJ25" s="10">
-        <f t="shared" si="93"/>
+      <c r="AJ25" s="9">
+        <f t="shared" si="105"/>
         <v>-0.22951077552304555</v>
       </c>
-      <c r="AK25" s="10">
-        <f t="shared" ref="AK25:AV25" si="94">AK11/AK3</f>
+      <c r="AK25" s="9">
+        <f t="shared" ref="AK25:AV25" si="106">AK11/AK3</f>
         <v>-0.16309198215056844</v>
       </c>
-      <c r="AL25" s="10">
-        <f t="shared" si="94"/>
+      <c r="AL25" s="9">
+        <f t="shared" si="106"/>
         <v>-7.4703212215830095E-2</v>
       </c>
-      <c r="AM25" s="10">
-        <f t="shared" si="94"/>
+      <c r="AM25" s="9">
+        <f t="shared" si="106"/>
         <v>-3.1152538497808888E-2</v>
       </c>
-      <c r="AN25" s="10">
-        <f t="shared" si="94"/>
+      <c r="AN25" s="9">
+        <f t="shared" si="106"/>
         <v>-3.619292194987619E-3</v>
       </c>
-      <c r="AO25" s="10">
-        <f t="shared" si="94"/>
+      <c r="AO25" s="9">
+        <f t="shared" si="106"/>
         <v>2.1305354255400602E-2</v>
       </c>
-      <c r="AP25" s="10">
-        <f t="shared" si="94"/>
+      <c r="AP25" s="9">
+        <f t="shared" si="106"/>
         <v>2.3743537056818167E-2</v>
       </c>
-      <c r="AQ25" s="10">
-        <f t="shared" si="94"/>
+      <c r="AQ25" s="9">
+        <f t="shared" si="106"/>
         <v>2.6157816105280795E-2</v>
       </c>
-      <c r="AR25" s="10">
-        <f t="shared" si="94"/>
+      <c r="AR25" s="9">
+        <f t="shared" si="106"/>
         <v>2.8548425751307342E-2</v>
       </c>
-      <c r="AS25" s="10">
-        <f t="shared" si="94"/>
+      <c r="AS25" s="9">
+        <f t="shared" si="106"/>
         <v>2.8548425751307314E-2</v>
       </c>
-      <c r="AT25" s="10">
-        <f t="shared" si="94"/>
+      <c r="AT25" s="9">
+        <f t="shared" si="106"/>
         <v>2.8548425751307366E-2</v>
       </c>
-      <c r="AU25" s="10">
-        <f t="shared" si="94"/>
+      <c r="AU25" s="9">
+        <f t="shared" si="106"/>
         <v>2.8548425751307414E-2</v>
       </c>
-      <c r="AV25" s="10">
-        <f t="shared" si="94"/>
+      <c r="AV25" s="9">
+        <f t="shared" si="106"/>
         <v>2.8548425751307425E-2</v>
       </c>
       <c r="AX25" t="s">
@@ -4322,144 +4320,144 @@
       <c r="B26" t="s">
         <v>24</v>
       </c>
-      <c r="M26" s="10">
-        <f t="shared" ref="M26:AB26" si="95">M15/M14</f>
+      <c r="M26" s="9">
+        <f t="shared" ref="M26:AA26" si="107">M15/M14</f>
         <v>-2.5316455696202542E-2</v>
       </c>
-      <c r="N26" s="10">
-        <f t="shared" si="95"/>
+      <c r="N26" s="9">
+        <f t="shared" si="107"/>
         <v>-4.2105263157894727E-3</v>
       </c>
-      <c r="O26" s="10">
-        <f t="shared" si="95"/>
+      <c r="O26" s="9">
+        <f t="shared" si="107"/>
         <v>-2.6737967914438502E-2</v>
       </c>
-      <c r="P26" s="10">
-        <f t="shared" si="95"/>
+      <c r="P26" s="9">
+        <f t="shared" si="107"/>
         <v>-2.4896265560165973E-2</v>
       </c>
-      <c r="Q26" s="10">
-        <f t="shared" si="95"/>
+      <c r="Q26" s="9">
+        <f t="shared" si="107"/>
         <v>-2.8571428571428571E-2</v>
       </c>
-      <c r="R26" s="10">
-        <f t="shared" si="95"/>
+      <c r="R26" s="9">
+        <f t="shared" si="107"/>
         <v>-3.0000000000000009E-2</v>
       </c>
-      <c r="S26" s="10">
-        <f t="shared" si="95"/>
+      <c r="S26" s="9">
+        <f t="shared" si="107"/>
         <v>-4.5161290322580649E-2</v>
       </c>
-      <c r="T26" s="10">
-        <f t="shared" si="95"/>
+      <c r="T26" s="9">
+        <f t="shared" si="107"/>
         <v>-5.2631578947368432E-2</v>
       </c>
-      <c r="U26" s="10">
-        <f t="shared" si="95"/>
+      <c r="U26" s="9">
+        <f t="shared" si="107"/>
         <v>-3.2258064516129024E-2</v>
       </c>
-      <c r="V26" s="10">
-        <f t="shared" si="95"/>
+      <c r="V26" s="9">
+        <f t="shared" si="107"/>
         <v>-6.8062827225130906E-2</v>
       </c>
-      <c r="W26" s="10">
-        <f t="shared" si="95"/>
+      <c r="W26" s="9">
+        <f t="shared" si="107"/>
         <v>-3.9024390243902446E-2</v>
       </c>
-      <c r="X26" s="10">
-        <f t="shared" si="95"/>
+      <c r="X26" s="9">
+        <f t="shared" si="107"/>
         <v>-4.566210045662103E-2</v>
       </c>
-      <c r="Y26" s="10">
-        <f t="shared" si="95"/>
+      <c r="Y26" s="9">
+        <f t="shared" si="107"/>
         <v>-0.12295081967213103</v>
       </c>
-      <c r="Z26" s="10">
-        <f t="shared" si="95"/>
+      <c r="Z26" s="9">
+        <f t="shared" si="107"/>
         <v>9.6234309623430853E-2</v>
       </c>
-      <c r="AA26" s="10">
-        <f t="shared" si="95"/>
+      <c r="AA26" s="9">
+        <f t="shared" si="107"/>
         <v>-0.23809523809523894</v>
       </c>
-      <c r="AB26" s="10">
+      <c r="AB26" s="9">
         <f>AB15/AB14</f>
         <v>-0.11428571428571392</v>
       </c>
-      <c r="AC26" s="10">
-        <f t="shared" ref="AC26:AD26" si="96">AC15/AC14</f>
+      <c r="AC26" s="9">
+        <f t="shared" ref="AC26:AD26" si="108">AC15/AC14</f>
         <v>-0.18552875695732837</v>
       </c>
-      <c r="AD26" s="10">
-        <f t="shared" si="96"/>
+      <c r="AD26" s="9">
+        <f t="shared" si="108"/>
         <v>-0.20004961230385176</v>
       </c>
-      <c r="AF26" s="10">
-        <f t="shared" ref="AF26:AK26" si="97">AF15/AF14</f>
+      <c r="AF26" s="9">
+        <f t="shared" ref="AF26:AJ26" si="109">AF15/AF14</f>
         <v>-1.5217391304347823E-2</v>
       </c>
-      <c r="AG26" s="10">
-        <f t="shared" si="97"/>
+      <c r="AG26" s="9">
+        <f t="shared" si="109"/>
         <v>-2.3006134969325152E-2</v>
       </c>
-      <c r="AH26" s="10">
-        <f t="shared" si="97"/>
+      <c r="AH26" s="9">
+        <f t="shared" si="109"/>
         <v>-1.468531468531468E-2</v>
       </c>
-      <c r="AI26" s="10">
-        <f t="shared" si="97"/>
+      <c r="AI26" s="9">
+        <f t="shared" si="109"/>
         <v>-2.7549824150058595E-2</v>
       </c>
-      <c r="AJ26" s="10">
-        <f t="shared" si="97"/>
+      <c r="AJ26" s="9">
+        <f t="shared" si="109"/>
         <v>-4.7533632286995503E-2</v>
       </c>
-      <c r="AK26" s="10">
-        <f t="shared" ref="AK26:AV26" si="98">AK15/AK14</f>
+      <c r="AK26" s="9">
+        <f t="shared" ref="AK26:AV26" si="110">AK15/AK14</f>
         <v>-1.273885350318473E-2</v>
       </c>
-      <c r="AL26" s="10">
-        <f t="shared" si="98"/>
+      <c r="AL26" s="9">
+        <f t="shared" si="110"/>
         <v>-0.18152068744839331</v>
       </c>
-      <c r="AM26" s="10">
-        <f t="shared" si="98"/>
+      <c r="AM26" s="9">
+        <f t="shared" si="110"/>
         <v>0.1</v>
       </c>
-      <c r="AN26" s="10">
-        <f t="shared" si="98"/>
+      <c r="AN26" s="9">
+        <f t="shared" si="110"/>
         <v>0.1</v>
       </c>
-      <c r="AO26" s="10">
-        <f t="shared" si="98"/>
+      <c r="AO26" s="9">
+        <f t="shared" si="110"/>
         <v>0.1</v>
       </c>
-      <c r="AP26" s="10">
-        <f t="shared" si="98"/>
+      <c r="AP26" s="9">
+        <f t="shared" si="110"/>
         <v>0.1</v>
       </c>
-      <c r="AQ26" s="10">
-        <f t="shared" si="98"/>
+      <c r="AQ26" s="9">
+        <f t="shared" si="110"/>
         <v>0.1</v>
       </c>
-      <c r="AR26" s="10">
-        <f t="shared" si="98"/>
+      <c r="AR26" s="9">
+        <f t="shared" si="110"/>
         <v>0.1</v>
       </c>
-      <c r="AS26" s="10">
-        <f t="shared" si="98"/>
+      <c r="AS26" s="9">
+        <f t="shared" si="110"/>
         <v>0.1</v>
       </c>
-      <c r="AT26" s="10">
-        <f t="shared" si="98"/>
+      <c r="AT26" s="9">
+        <f t="shared" si="110"/>
         <v>0.1</v>
       </c>
-      <c r="AU26" s="10">
-        <f t="shared" si="98"/>
+      <c r="AU26" s="9">
+        <f t="shared" si="110"/>
         <v>0.1</v>
       </c>
-      <c r="AV26" s="10">
-        <f t="shared" si="98"/>
+      <c r="AV26" s="9">
+        <f t="shared" si="110"/>
         <v>0.1</v>
       </c>
       <c r="AX26" t="s">
@@ -4474,144 +4472,144 @@
       <c r="B27" t="s">
         <v>60</v>
       </c>
-      <c r="M27" s="10">
-        <f t="shared" ref="M27:AB27" si="99">M16/M3</f>
+      <c r="M27" s="9">
+        <f t="shared" ref="M27:AA27" si="111">M16/M3</f>
         <v>-0.29481346678798898</v>
       </c>
-      <c r="N27" s="10">
-        <f t="shared" si="99"/>
+      <c r="N27" s="9">
+        <f t="shared" si="111"/>
         <v>-0.41478260869565231</v>
       </c>
-      <c r="O27" s="10">
-        <f t="shared" si="99"/>
+      <c r="O27" s="9">
+        <f t="shared" si="111"/>
         <v>-0.31893687707641194</v>
       </c>
-      <c r="P27" s="10">
-        <f t="shared" si="99"/>
+      <c r="P27" s="9">
+        <f t="shared" si="111"/>
         <v>-0.39583333333333337</v>
       </c>
-      <c r="Q27" s="10">
-        <f t="shared" si="99"/>
+      <c r="Q27" s="9">
+        <f t="shared" si="111"/>
         <v>-0.26392961876832843</v>
       </c>
-      <c r="R27" s="10">
-        <f t="shared" si="99"/>
+      <c r="R27" s="9">
+        <f t="shared" si="111"/>
         <v>-0.36216596343178614</v>
       </c>
-      <c r="S27" s="10">
-        <f t="shared" si="99"/>
+      <c r="S27" s="9">
+        <f t="shared" si="111"/>
         <v>-0.21951219512195116</v>
       </c>
-      <c r="T27" s="10">
-        <f t="shared" si="99"/>
+      <c r="T27" s="9">
+        <f t="shared" si="111"/>
         <v>-0.20819778789850357</v>
       </c>
-      <c r="U27" s="10">
-        <f t="shared" si="99"/>
+      <c r="U27" s="9">
+        <f t="shared" si="111"/>
         <v>-0.19335347432024177</v>
       </c>
-      <c r="V27" s="10">
-        <f t="shared" si="99"/>
+      <c r="V27" s="9">
+        <f t="shared" si="111"/>
         <v>-0.12078152753108345</v>
       </c>
-      <c r="W27" s="10">
-        <f t="shared" si="99"/>
+      <c r="W27" s="9">
+        <f t="shared" si="111"/>
         <v>-0.12596096984033114</v>
       </c>
-      <c r="X27" s="10">
-        <f t="shared" si="99"/>
+      <c r="X27" s="9">
+        <f t="shared" si="111"/>
         <v>-0.13446858485026417</v>
       </c>
-      <c r="Y27" s="10">
-        <f t="shared" si="99"/>
+      <c r="Y27" s="9">
+        <f t="shared" si="111"/>
         <v>-7.7796706416808706E-2</v>
       </c>
-      <c r="Z27" s="10">
-        <f t="shared" si="99"/>
+      <c r="Z27" s="9">
+        <f t="shared" si="111"/>
         <v>-0.12053571428571444</v>
       </c>
-      <c r="AA27" s="10">
-        <f t="shared" si="99"/>
+      <c r="AA27" s="9">
+        <f t="shared" si="111"/>
         <v>-4.3502509760178346E-2</v>
       </c>
-      <c r="AB27" s="10">
+      <c r="AB27" s="9">
         <f>AB16/AB3</f>
         <v>-4.1688936397648438E-2</v>
       </c>
-      <c r="AC27" s="10">
-        <f t="shared" ref="AC27:AD27" si="100">AC16/AC3</f>
+      <c r="AC27" s="9">
+        <f t="shared" ref="AC27:AD27" si="112">AC16/AC3</f>
         <v>-3.3631578947368422E-2</v>
       </c>
-      <c r="AD27" s="10">
-        <f t="shared" si="100"/>
+      <c r="AD27" s="9">
+        <f t="shared" si="112"/>
         <v>-3.1285255340453885E-2</v>
       </c>
-      <c r="AF27" s="10">
-        <f t="shared" ref="AF27:AK27" si="101">AF16/AF3</f>
+      <c r="AF27" s="9">
+        <f t="shared" ref="AF27:AJ27" si="113">AF16/AF3</f>
         <v>-0.25325379609544474</v>
       </c>
-      <c r="AG27" s="10">
-        <f t="shared" si="101"/>
+      <c r="AG27" s="9">
+        <f t="shared" si="113"/>
         <v>-0.22725724020442931</v>
       </c>
-      <c r="AH27" s="10">
-        <f t="shared" si="101"/>
+      <c r="AH27" s="9">
+        <f t="shared" si="113"/>
         <v>-0.34938598603419224</v>
       </c>
-      <c r="AI27" s="10">
-        <f t="shared" si="101"/>
+      <c r="AI27" s="9">
+        <f t="shared" si="113"/>
         <v>-0.3346697212676597</v>
       </c>
-      <c r="AJ27" s="10">
-        <f t="shared" si="101"/>
+      <c r="AJ27" s="9">
+        <f t="shared" si="113"/>
         <v>-0.18373446594305495</v>
       </c>
-      <c r="AK27" s="10">
-        <f t="shared" ref="AK27:AV27" si="102">AK16/AK3</f>
+      <c r="AK27" s="9">
+        <f t="shared" ref="AK27:AV27" si="114">AK16/AK3</f>
         <v>-0.11443788685763624</v>
       </c>
-      <c r="AL27" s="10">
-        <f t="shared" si="102"/>
+      <c r="AL27" s="9">
+        <f t="shared" si="114"/>
         <v>-3.7410926238798936E-2</v>
       </c>
-      <c r="AM27" s="10">
-        <f t="shared" si="102"/>
+      <c r="AM27" s="9">
+        <f t="shared" si="114"/>
         <v>8.7600622340084627E-3</v>
       </c>
-      <c r="AN27" s="10">
-        <f t="shared" si="102"/>
+      <c r="AN27" s="9">
+        <f t="shared" si="114"/>
         <v>3.247852197725809E-2</v>
       </c>
-      <c r="AO27" s="10">
-        <f t="shared" si="102"/>
+      <c r="AO27" s="9">
+        <f t="shared" si="114"/>
         <v>5.4216803103913372E-2</v>
       </c>
-      <c r="AP27" s="10">
-        <f t="shared" si="102"/>
+      <c r="AP27" s="9">
+        <f t="shared" si="114"/>
         <v>5.6067618759757298E-2</v>
       </c>
-      <c r="AQ27" s="10">
-        <f t="shared" si="102"/>
+      <c r="AQ27" s="9">
+        <f t="shared" si="114"/>
         <v>5.7900289164073464E-2</v>
       </c>
-      <c r="AR27" s="10">
-        <f t="shared" si="102"/>
+      <c r="AR27" s="9">
+        <f t="shared" si="114"/>
         <v>5.9714992211484408E-2</v>
       </c>
-      <c r="AS27" s="10">
-        <f t="shared" si="102"/>
+      <c r="AS27" s="9">
+        <f t="shared" si="114"/>
         <v>5.971499221148438E-2</v>
       </c>
-      <c r="AT27" s="10">
-        <f t="shared" si="102"/>
+      <c r="AT27" s="9">
+        <f t="shared" si="114"/>
         <v>5.9714992211484436E-2</v>
       </c>
-      <c r="AU27" s="10">
-        <f t="shared" si="102"/>
+      <c r="AU27" s="9">
+        <f t="shared" si="114"/>
         <v>5.9714992211484477E-2</v>
       </c>
-      <c r="AV27" s="10">
-        <f t="shared" si="102"/>
+      <c r="AV27" s="9">
+        <f t="shared" si="114"/>
         <v>5.9714992211484477E-2</v>
       </c>
       <c r="AX27" t="s">
@@ -4619,23 +4617,23 @@
       </c>
       <c r="AY27" s="2">
         <f>Main!D3</f>
-        <v>11.3</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="28" spans="2:51" x14ac:dyDescent="0.3">
       <c r="AX28" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AY28" s="11">
+      <c r="AY28" s="10">
         <f>AY26/AY27-1</f>
-        <v>-0.37498667247952933</v>
+        <v>-0.31497084374574991</v>
       </c>
     </row>
     <row r="29" spans="2:51" x14ac:dyDescent="0.3">
       <c r="AX29" t="s">
         <v>69</v>
       </c>
-      <c r="AY29" t="s">
+      <c r="AY29" s="6" t="s">
         <v>70</v>
       </c>
     </row>

--- a/Financial Analysis/COUR.xlsx
+++ b/Financial Analysis/COUR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87D2EC3-184D-44CD-BCF0-E104DDC17DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F54242D-6FC6-4BFF-B2CC-0E784211647D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{31E8D773-A0F0-4A5C-8306-0B953AC75F07}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="74">
   <si>
     <t>COUR</t>
   </si>
@@ -244,7 +244,10 @@
     <t>Learners y/y</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
+    <t>Slightly undervalued</t>
+  </si>
+  <si>
+    <t>Q425 8K</t>
   </si>
 </sst>
 </file>
@@ -344,14 +347,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -368,8 +371,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22936200" y="7620"/>
-          <a:ext cx="0" cy="6134100"/>
+          <a:off x="26151840" y="7620"/>
+          <a:ext cx="0" cy="6865620"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -394,13 +397,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
+      <xdr:col>30</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
+      <xdr:col>30</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -418,8 +421,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18127980" y="7620"/>
-          <a:ext cx="0" cy="6134100"/>
+          <a:off x="18836640" y="7620"/>
+          <a:ext cx="0" cy="6865620"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -768,17 +771,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>9.1999999999999993</v>
+        <v>5.98</v>
       </c>
       <c r="E3" s="4">
-        <v>45956</v>
+        <v>46059</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45956</v>
+        <v>46059</v>
       </c>
       <c r="G3" s="4">
-        <v>46058</v>
+        <v>46135</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -786,11 +789,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>164.6</f>
-        <v>164.6</v>
+        <v>167.2</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -799,7 +801,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>1514.32</v>
+        <v>999.85599999999999</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -807,11 +809,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>797.7</f>
-        <v>797.7</v>
+        <f>792.6</f>
+        <v>792.6</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -822,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -831,7 +833,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>797.7</v>
+        <v>792.6</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -840,7 +842,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>716.61999999999989</v>
+        <v>207.25599999999997</v>
       </c>
     </row>
   </sheetData>
@@ -850,15 +852,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD2C2134-7EC8-4CEE-86B3-FA6CD313EB77}">
-  <dimension ref="B2:EN33"/>
+  <dimension ref="B2:ER33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:52" x14ac:dyDescent="0.3">
       <c r="C2" s="6" t="s">
         <v>28</v>
       </c>
@@ -943,59 +945,63 @@
       <c r="AD2" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AF2">
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
+      <c r="AH2" s="6"/>
+      <c r="AJ2">
         <v>2019</v>
       </c>
-      <c r="AG2">
+      <c r="AK2">
         <v>2020</v>
       </c>
-      <c r="AH2">
+      <c r="AL2">
         <v>2021</v>
       </c>
-      <c r="AI2">
+      <c r="AM2">
         <v>2022</v>
       </c>
-      <c r="AJ2">
+      <c r="AN2">
         <v>2023</v>
       </c>
-      <c r="AK2">
+      <c r="AO2">
         <v>2024</v>
       </c>
-      <c r="AL2">
+      <c r="AP2">
         <v>2025</v>
       </c>
-      <c r="AM2">
+      <c r="AQ2">
         <v>2026</v>
       </c>
-      <c r="AN2">
+      <c r="AR2">
         <v>2027</v>
       </c>
-      <c r="AO2">
+      <c r="AS2">
         <v>2028</v>
       </c>
-      <c r="AP2">
+      <c r="AT2">
         <v>2029</v>
       </c>
-      <c r="AQ2">
+      <c r="AU2">
         <v>2030</v>
       </c>
-      <c r="AR2">
+      <c r="AV2">
         <v>2031</v>
       </c>
-      <c r="AS2">
+      <c r="AW2">
         <v>2032</v>
       </c>
-      <c r="AT2">
+      <c r="AX2">
         <v>2033</v>
       </c>
-      <c r="AU2">
+      <c r="AY2">
         <v>2034</v>
       </c>
-      <c r="AV2">
+      <c r="AZ2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:52" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>70</v>
       </c>
@@ -1024,15 +1030,23 @@
       <c r="Y3" s="6">
         <v>162</v>
       </c>
-      <c r="Z3" s="6"/>
+      <c r="Z3" s="6">
+        <v>168</v>
+      </c>
       <c r="AA3" s="6"/>
       <c r="AB3" s="6"/>
       <c r="AC3" s="6">
         <v>191</v>
       </c>
-      <c r="AD3" s="6"/>
+      <c r="AD3" s="6">
+        <v>197</v>
+      </c>
+      <c r="AE3" s="6"/>
+      <c r="AF3" s="6"/>
+      <c r="AG3" s="6"/>
+      <c r="AH3" s="6"/>
     </row>
-    <row r="4" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:52" x14ac:dyDescent="0.3">
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -1061,8 +1075,12 @@
       <c r="AB4" s="6"/>
       <c r="AC4" s="6"/>
       <c r="AD4" s="6"/>
+      <c r="AE4" s="6"/>
+      <c r="AF4" s="6"/>
+      <c r="AG4" s="6"/>
+      <c r="AH4" s="6"/>
     </row>
-    <row r="5" spans="2:48" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:52" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
@@ -1118,76 +1136,79 @@
         <v>194.2</v>
       </c>
       <c r="AD5" s="8">
-        <f>Z5*1.08</f>
-        <v>193.536</v>
-      </c>
-      <c r="AF5" s="8">
+        <v>196.9</v>
+      </c>
+      <c r="AE5" s="8"/>
+      <c r="AF5" s="8"/>
+      <c r="AG5" s="8"/>
+      <c r="AH5" s="8"/>
+      <c r="AJ5" s="8">
         <v>184.4</v>
       </c>
-      <c r="AG5" s="8">
+      <c r="AK5" s="8">
         <v>293.5</v>
       </c>
-      <c r="AH5" s="8">
+      <c r="AL5" s="8">
         <v>415.3</v>
       </c>
-      <c r="AI5" s="8">
+      <c r="AM5" s="8">
         <f>SUM(O5:R5)</f>
         <v>523.79999999999995</v>
       </c>
-      <c r="AJ5" s="8">
+      <c r="AN5" s="8">
         <f>SUM(S5:V5)</f>
         <v>635.69999999999993</v>
       </c>
-      <c r="AK5" s="8">
+      <c r="AO5" s="8">
         <f>SUM(W5:Z5)</f>
         <v>694.7</v>
       </c>
-      <c r="AL5" s="8">
+      <c r="AP5" s="8">
         <f>SUM(AA5:AD5)</f>
-        <v>754.13599999999997</v>
-      </c>
-      <c r="AM5" s="8">
-        <f>AL5*1.05</f>
-        <v>791.84280000000001</v>
-      </c>
-      <c r="AN5" s="8">
-        <f>AM5*1.04</f>
-        <v>823.51651200000003</v>
-      </c>
-      <c r="AO5" s="8">
-        <f>AN5*1.03</f>
-        <v>848.22200736000002</v>
-      </c>
-      <c r="AP5" s="8">
-        <f t="shared" ref="AP5:AV5" si="0">AO5*1.03</f>
-        <v>873.66866758080005</v>
+        <v>757.49999999999989</v>
       </c>
       <c r="AQ5" s="8">
-        <f t="shared" si="0"/>
-        <v>899.87872760822404</v>
+        <f>AP5*1.07</f>
+        <v>810.52499999999998</v>
       </c>
       <c r="AR5" s="8">
-        <f t="shared" si="0"/>
-        <v>926.87508943647083</v>
+        <f>AQ5*1.05</f>
+        <v>851.05124999999998</v>
       </c>
       <c r="AS5" s="8">
-        <f t="shared" si="0"/>
-        <v>954.68134211956499</v>
+        <f>AR5*1.03</f>
+        <v>876.58278749999999</v>
       </c>
       <c r="AT5" s="8">
-        <f t="shared" si="0"/>
-        <v>983.32178238315191</v>
+        <f t="shared" ref="AT5:AZ5" si="0">AS5*1.03</f>
+        <v>902.88027112500004</v>
       </c>
       <c r="AU5" s="8">
         <f t="shared" si="0"/>
-        <v>1012.8214358546466</v>
+        <v>929.9666792587501</v>
       </c>
       <c r="AV5" s="8">
         <f t="shared" si="0"/>
-        <v>1043.2060789302859</v>
+        <v>957.8656796365126</v>
+      </c>
+      <c r="AW5" s="8">
+        <f t="shared" si="0"/>
+        <v>986.60165002560802</v>
+      </c>
+      <c r="AX5" s="8">
+        <f t="shared" si="0"/>
+        <v>1016.1996995263763</v>
+      </c>
+      <c r="AY5" s="8">
+        <f t="shared" si="0"/>
+        <v>1046.6856905121676</v>
+      </c>
+      <c r="AZ5" s="8">
+        <f t="shared" si="0"/>
+        <v>1078.0862612275328</v>
       </c>
     </row>
-    <row r="6" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:52" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>13</v>
       </c>
@@ -1243,81 +1264,84 @@
         <v>88.2</v>
       </c>
       <c r="AD6" s="5">
-        <f>AD5-AD7</f>
-        <v>87.091199999999986</v>
-      </c>
-      <c r="AF6" s="5">
+        <v>90.1</v>
+      </c>
+      <c r="AE6" s="5"/>
+      <c r="AF6" s="5"/>
+      <c r="AG6" s="5"/>
+      <c r="AH6" s="5"/>
+      <c r="AJ6" s="5">
         <v>89.6</v>
       </c>
-      <c r="AG6" s="5">
+      <c r="AK6" s="5">
         <v>138.80000000000001</v>
       </c>
-      <c r="AH6" s="5">
+      <c r="AL6" s="5">
         <v>165.8</v>
       </c>
-      <c r="AI6" s="5">
+      <c r="AM6" s="5">
         <f>SUM(O6:R6)</f>
         <v>192.3</v>
       </c>
-      <c r="AJ6" s="5">
+      <c r="AN6" s="5">
         <f>SUM(S6:V6)</f>
         <v>306.10000000000002</v>
       </c>
-      <c r="AK6" s="5">
+      <c r="AO6" s="5">
         <f>SUM(W6:Z6)</f>
         <v>323.3</v>
       </c>
-      <c r="AL6" s="5">
+      <c r="AP6" s="5">
         <f>SUM(AA6:AD6)</f>
-        <v>341.09119999999996</v>
-      </c>
-      <c r="AM6" s="5">
-        <f>AM5-AM7</f>
-        <v>348.41083199999997</v>
-      </c>
-      <c r="AN6" s="5">
-        <f t="shared" ref="AN6:AV6" si="1">AN5-AN7</f>
-        <v>354.11210016000007</v>
-      </c>
-      <c r="AO6" s="5">
-        <f t="shared" si="1"/>
-        <v>356.25324309120003</v>
-      </c>
-      <c r="AP6" s="5">
-        <f t="shared" si="1"/>
-        <v>366.94084038393606</v>
+        <v>344.1</v>
       </c>
       <c r="AQ6" s="5">
-        <f t="shared" si="1"/>
-        <v>377.94906559545416</v>
+        <f>AQ5-AQ7</f>
+        <v>356.63099999999997</v>
       </c>
       <c r="AR6" s="5">
-        <f t="shared" si="1"/>
-        <v>389.28753756331776</v>
+        <f t="shared" ref="AR6:AZ6" si="1">AR5-AR7</f>
+        <v>365.95203750000002</v>
       </c>
       <c r="AS6" s="5">
         <f t="shared" si="1"/>
-        <v>400.96616369021729</v>
+        <v>376.93059862500002</v>
       </c>
       <c r="AT6" s="5">
         <f t="shared" si="1"/>
-        <v>412.99514860092381</v>
+        <v>388.23851658375008</v>
       </c>
       <c r="AU6" s="5">
         <f t="shared" si="1"/>
-        <v>425.38500305895161</v>
+        <v>399.88567208126256</v>
       </c>
       <c r="AV6" s="5">
         <f t="shared" si="1"/>
-        <v>438.14655315072014</v>
+        <v>411.88224224370049</v>
+      </c>
+      <c r="AW6" s="5">
+        <f t="shared" si="1"/>
+        <v>424.23870951101151</v>
+      </c>
+      <c r="AX6" s="5">
+        <f t="shared" si="1"/>
+        <v>436.96587079634185</v>
+      </c>
+      <c r="AY6" s="5">
+        <f t="shared" si="1"/>
+        <v>450.07484692023218</v>
+      </c>
+      <c r="AZ6" s="5">
+        <f t="shared" si="1"/>
+        <v>463.57709232783918</v>
       </c>
     </row>
-    <row r="7" spans="2:48" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:52" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="M7" s="8">
-        <f t="shared" ref="M7:AC7" si="2">M5-M6</f>
+        <f t="shared" ref="M7:AD7" si="2">M5-M6</f>
         <v>67.7</v>
       </c>
       <c r="N7" s="8">
@@ -1385,79 +1409,83 @@
         <v>105.99999999999999</v>
       </c>
       <c r="AD7" s="8">
-        <f t="shared" ref="AD7" si="3">AD5*0.55</f>
-        <v>106.44480000000001</v>
-      </c>
-      <c r="AF7" s="8">
-        <f t="shared" ref="AF7:AL7" si="4">AF5-AF6</f>
+        <f t="shared" si="2"/>
+        <v>106.80000000000001</v>
+      </c>
+      <c r="AE7" s="8"/>
+      <c r="AF7" s="8"/>
+      <c r="AG7" s="8"/>
+      <c r="AH7" s="8"/>
+      <c r="AJ7" s="8">
+        <f t="shared" ref="AJ7:AP7" si="3">AJ5-AJ6</f>
         <v>94.800000000000011</v>
       </c>
-      <c r="AG7" s="8">
+      <c r="AK7" s="8">
+        <f t="shared" si="3"/>
+        <v>154.69999999999999</v>
+      </c>
+      <c r="AL7" s="8">
+        <f t="shared" si="3"/>
+        <v>249.5</v>
+      </c>
+      <c r="AM7" s="8">
+        <f t="shared" si="3"/>
+        <v>331.49999999999994</v>
+      </c>
+      <c r="AN7" s="8">
+        <f t="shared" si="3"/>
+        <v>329.59999999999991</v>
+      </c>
+      <c r="AO7" s="8">
+        <f t="shared" si="3"/>
+        <v>371.40000000000003</v>
+      </c>
+      <c r="AP7" s="8">
+        <f t="shared" si="3"/>
+        <v>413.39999999999986</v>
+      </c>
+      <c r="AQ7" s="8">
+        <f>AQ5*0.56</f>
+        <v>453.89400000000001</v>
+      </c>
+      <c r="AR7" s="8">
+        <f>AR5*0.57</f>
+        <v>485.09921249999996</v>
+      </c>
+      <c r="AS7" s="8">
+        <f t="shared" ref="AS7:AZ7" si="4">AS5*0.57</f>
+        <v>499.65218887499998</v>
+      </c>
+      <c r="AT7" s="8">
         <f t="shared" si="4"/>
-        <v>154.69999999999999</v>
-      </c>
-      <c r="AH7" s="8">
+        <v>514.64175454124995</v>
+      </c>
+      <c r="AU7" s="8">
         <f t="shared" si="4"/>
-        <v>249.5</v>
-      </c>
-      <c r="AI7" s="8">
+        <v>530.08100717748755</v>
+      </c>
+      <c r="AV7" s="8">
         <f t="shared" si="4"/>
-        <v>331.49999999999994</v>
-      </c>
-      <c r="AJ7" s="8">
+        <v>545.98343739281211</v>
+      </c>
+      <c r="AW7" s="8">
         <f t="shared" si="4"/>
-        <v>329.59999999999991</v>
-      </c>
-      <c r="AK7" s="8">
+        <v>562.36294051459652</v>
+      </c>
+      <c r="AX7" s="8">
         <f t="shared" si="4"/>
-        <v>371.40000000000003</v>
-      </c>
-      <c r="AL7" s="8">
+        <v>579.23382873003447</v>
+      </c>
+      <c r="AY7" s="8">
         <f t="shared" si="4"/>
-        <v>413.04480000000001</v>
-      </c>
-      <c r="AM7" s="8">
-        <f>AM5*0.56</f>
-        <v>443.43196800000004</v>
-      </c>
-      <c r="AN7" s="8">
-        <f>AN5*0.57</f>
-        <v>469.40441183999997</v>
-      </c>
-      <c r="AO7" s="8">
-        <f>AO5*0.58</f>
-        <v>491.96876426879999</v>
-      </c>
-      <c r="AP7" s="8">
-        <f t="shared" ref="AP7:AV7" si="5">AP5*0.58</f>
-        <v>506.72782719686398</v>
-      </c>
-      <c r="AQ7" s="8">
-        <f t="shared" si="5"/>
-        <v>521.92966201276988</v>
-      </c>
-      <c r="AR7" s="8">
-        <f t="shared" si="5"/>
-        <v>537.58755187315307</v>
-      </c>
-      <c r="AS7" s="8">
-        <f t="shared" si="5"/>
-        <v>553.7151784293477</v>
-      </c>
-      <c r="AT7" s="8">
-        <f t="shared" si="5"/>
-        <v>570.3266337822281</v>
-      </c>
-      <c r="AU7" s="8">
-        <f t="shared" si="5"/>
-        <v>587.43643279569494</v>
-      </c>
-      <c r="AV7" s="8">
-        <f t="shared" si="5"/>
-        <v>605.05952577956577</v>
+        <v>596.61084359193546</v>
+      </c>
+      <c r="AZ7" s="8">
+        <f t="shared" si="4"/>
+        <v>614.50916889969358</v>
       </c>
     </row>
-    <row r="8" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:52" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>15</v>
       </c>
@@ -1513,76 +1541,79 @@
         <v>30</v>
       </c>
       <c r="AD8" s="5">
-        <f>Z8*0.96</f>
-        <v>30.815999999999999</v>
-      </c>
-      <c r="AF8" s="5">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="AE8" s="5"/>
+      <c r="AF8" s="5"/>
+      <c r="AG8" s="5"/>
+      <c r="AH8" s="5"/>
+      <c r="AJ8" s="5">
         <v>56.4</v>
       </c>
-      <c r="AG8" s="5">
+      <c r="AK8" s="5">
         <v>76.8</v>
       </c>
-      <c r="AH8" s="5">
+      <c r="AL8" s="5">
         <v>135.4</v>
       </c>
-      <c r="AI8" s="5">
-        <f t="shared" ref="AI8:AI11" si="6">SUM(O8:R8)</f>
+      <c r="AM8" s="5">
+        <f t="shared" ref="AM8:AM11" si="5">SUM(O8:R8)</f>
         <v>165.10000000000002</v>
       </c>
-      <c r="AJ8" s="5">
-        <f t="shared" ref="AJ8:AJ11" si="7">SUM(S8:V8)</f>
+      <c r="AN8" s="5">
+        <f t="shared" ref="AN8:AN11" si="6">SUM(S8:V8)</f>
         <v>160.1</v>
       </c>
-      <c r="AK8" s="5">
-        <f t="shared" ref="AK8:AK11" si="8">SUM(W8:Z8)</f>
+      <c r="AO8" s="5">
+        <f t="shared" ref="AO8:AO11" si="7">SUM(W8:Z8)</f>
         <v>132</v>
       </c>
-      <c r="AL8" s="5">
-        <f t="shared" ref="AL8:AL11" si="9">SUM(AA8:AD8)</f>
-        <v>119.616</v>
-      </c>
-      <c r="AM8" s="5">
-        <f>AL8*0.94</f>
-        <v>112.43903999999999</v>
-      </c>
-      <c r="AN8" s="5">
-        <f t="shared" ref="AN8:AV8" si="10">AM8*1.01</f>
-        <v>113.56343039999999</v>
-      </c>
-      <c r="AO8" s="5">
-        <f t="shared" si="10"/>
-        <v>114.69906470399999</v>
-      </c>
       <c r="AP8" s="5">
-        <f t="shared" si="10"/>
-        <v>115.84605535103999</v>
+        <f t="shared" ref="AP8:AP11" si="8">SUM(AA8:AD8)</f>
+        <v>121.6</v>
       </c>
       <c r="AQ8" s="5">
-        <f t="shared" si="10"/>
-        <v>117.00451590455039</v>
+        <f>AP8*0.94</f>
+        <v>114.30399999999999</v>
       </c>
       <c r="AR8" s="5">
-        <f t="shared" si="10"/>
-        <v>118.17456106359589</v>
+        <f t="shared" ref="AR8:AZ8" si="9">AQ8*1.01</f>
+        <v>115.44703999999999</v>
       </c>
       <c r="AS8" s="5">
-        <f t="shared" si="10"/>
-        <v>119.35630667423185</v>
+        <f t="shared" si="9"/>
+        <v>116.60151039999998</v>
       </c>
       <c r="AT8" s="5">
-        <f t="shared" si="10"/>
-        <v>120.54986974097416</v>
+        <f t="shared" si="9"/>
+        <v>117.76752550399998</v>
       </c>
       <c r="AU8" s="5">
-        <f t="shared" si="10"/>
-        <v>121.7553684383839</v>
+        <f t="shared" si="9"/>
+        <v>118.94520075903998</v>
       </c>
       <c r="AV8" s="5">
-        <f t="shared" si="10"/>
-        <v>122.97292212276774</v>
+        <f t="shared" si="9"/>
+        <v>120.13465276663038</v>
+      </c>
+      <c r="AW8" s="5">
+        <f t="shared" si="9"/>
+        <v>121.33599929429668</v>
+      </c>
+      <c r="AX8" s="5">
+        <f t="shared" si="9"/>
+        <v>122.54935928723965</v>
+      </c>
+      <c r="AY8" s="5">
+        <f t="shared" si="9"/>
+        <v>123.77485288011205</v>
+      </c>
+      <c r="AZ8" s="5">
+        <f t="shared" si="9"/>
+        <v>125.01260140891317</v>
       </c>
     </row>
-    <row r="9" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:52" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>16</v>
       </c>
@@ -1638,76 +1669,79 @@
         <v>67.400000000000006</v>
       </c>
       <c r="AD9" s="5">
-        <f t="shared" ref="AD9" si="11">AD5*0.34</f>
-        <v>65.802240000000012</v>
-      </c>
-      <c r="AF9" s="5">
+        <v>67.900000000000006</v>
+      </c>
+      <c r="AE9" s="5"/>
+      <c r="AF9" s="5"/>
+      <c r="AG9" s="5"/>
+      <c r="AH9" s="5"/>
+      <c r="AJ9" s="5">
         <v>57</v>
       </c>
-      <c r="AG9" s="5">
+      <c r="AK9" s="5">
         <v>107.2</v>
       </c>
-      <c r="AH9" s="5">
+      <c r="AL9" s="5">
         <v>179.3</v>
       </c>
-      <c r="AI9" s="5">
+      <c r="AM9" s="5">
+        <f t="shared" si="5"/>
+        <v>227.70000000000002</v>
+      </c>
+      <c r="AN9" s="5">
         <f t="shared" si="6"/>
-        <v>227.70000000000002</v>
-      </c>
-      <c r="AJ9" s="5">
+        <v>222.79999999999998</v>
+      </c>
+      <c r="AO9" s="5">
         <f t="shared" si="7"/>
-        <v>222.79999999999998</v>
-      </c>
-      <c r="AK9" s="5">
+        <v>234.89999999999998</v>
+      </c>
+      <c r="AP9" s="5">
         <f t="shared" si="8"/>
-        <v>234.89999999999998</v>
-      </c>
-      <c r="AL9" s="5">
-        <f t="shared" si="9"/>
-        <v>253.60224000000002</v>
-      </c>
-      <c r="AM9" s="5">
-        <f>AM5*0.33</f>
-        <v>261.30812400000002</v>
-      </c>
-      <c r="AN9" s="5">
-        <f>AN5*0.32</f>
-        <v>263.52528384000004</v>
-      </c>
-      <c r="AO9" s="5">
-        <f>AO5*0.31</f>
-        <v>262.94882228160003</v>
-      </c>
-      <c r="AP9" s="5">
-        <f t="shared" ref="AP9:AV9" si="12">AP5*0.31</f>
-        <v>270.837286950048</v>
+        <v>255.70000000000002</v>
       </c>
       <c r="AQ9" s="5">
-        <f t="shared" si="12"/>
-        <v>278.96240555854945</v>
+        <f>AQ5*0.33</f>
+        <v>267.47325000000001</v>
       </c>
       <c r="AR9" s="5">
-        <f t="shared" si="12"/>
-        <v>287.33127772530594</v>
+        <f>AR5*0.32</f>
+        <v>272.33640000000003</v>
       </c>
       <c r="AS9" s="5">
-        <f t="shared" si="12"/>
-        <v>295.95121605706515</v>
+        <f>AS5*0.31</f>
+        <v>271.74066412500002</v>
       </c>
       <c r="AT9" s="5">
-        <f t="shared" si="12"/>
-        <v>304.82975253877709</v>
+        <f t="shared" ref="AT9:AZ9" si="10">AT5*0.31</f>
+        <v>279.89288404875003</v>
       </c>
       <c r="AU9" s="5">
-        <f t="shared" si="12"/>
-        <v>313.97464511494042</v>
+        <f t="shared" si="10"/>
+        <v>288.28967057021254</v>
       </c>
       <c r="AV9" s="5">
-        <f t="shared" si="12"/>
-        <v>323.39388446838865</v>
+        <f t="shared" si="10"/>
+        <v>296.93836068731889</v>
+      </c>
+      <c r="AW9" s="5">
+        <f t="shared" si="10"/>
+        <v>305.84651150793849</v>
+      </c>
+      <c r="AX9" s="5">
+        <f t="shared" si="10"/>
+        <v>315.02190685317663</v>
+      </c>
+      <c r="AY9" s="5">
+        <f t="shared" si="10"/>
+        <v>324.47256405877198</v>
+      </c>
+      <c r="AZ9" s="5">
+        <f t="shared" si="10"/>
+        <v>334.20674098053513</v>
       </c>
     </row>
-    <row r="10" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:52" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>17</v>
       </c>
@@ -1763,76 +1797,79 @@
         <v>24.2</v>
       </c>
       <c r="AD10" s="5">
-        <f>Z10*0.9</f>
-        <v>24.21</v>
-      </c>
-      <c r="AF10" s="5">
+        <v>38.4</v>
+      </c>
+      <c r="AE10" s="5"/>
+      <c r="AF10" s="5"/>
+      <c r="AG10" s="5"/>
+      <c r="AH10" s="5"/>
+      <c r="AJ10" s="5">
         <v>29.8</v>
       </c>
-      <c r="AG10" s="5">
+      <c r="AK10" s="5">
         <v>37.200000000000003</v>
       </c>
-      <c r="AH10" s="5">
+      <c r="AL10" s="5">
         <v>77.8</v>
       </c>
-      <c r="AI10" s="5">
+      <c r="AM10" s="5">
+        <f t="shared" si="5"/>
+        <v>105.9</v>
+      </c>
+      <c r="AN10" s="5">
         <f t="shared" si="6"/>
-        <v>105.9</v>
-      </c>
-      <c r="AJ10" s="5">
+        <v>98.199999999999989</v>
+      </c>
+      <c r="AO10" s="5">
         <f t="shared" si="7"/>
-        <v>98.199999999999989</v>
-      </c>
-      <c r="AK10" s="5">
+        <v>108.9</v>
+      </c>
+      <c r="AP10" s="5">
         <f t="shared" si="8"/>
-        <v>108.9</v>
-      </c>
-      <c r="AL10" s="5">
-        <f t="shared" si="9"/>
-        <v>100.21000000000001</v>
-      </c>
-      <c r="AM10" s="5">
-        <f>AL10*0.96</f>
-        <v>96.201599999999999</v>
-      </c>
-      <c r="AN10" s="5">
-        <f>AM10*1.01</f>
-        <v>97.163616000000005</v>
-      </c>
-      <c r="AO10" s="5">
-        <f t="shared" ref="AO10:AV10" si="13">AN10*1.01</f>
-        <v>98.135252160000007</v>
-      </c>
-      <c r="AP10" s="5">
-        <f t="shared" si="13"/>
-        <v>99.116604681600009</v>
+        <v>114.4</v>
       </c>
       <c r="AQ10" s="5">
-        <f t="shared" si="13"/>
-        <v>100.10777072841601</v>
+        <f>AP10*0.96</f>
+        <v>109.824</v>
       </c>
       <c r="AR10" s="5">
-        <f t="shared" si="13"/>
-        <v>101.10884843570018</v>
+        <f>AQ10*1.01</f>
+        <v>110.92224</v>
       </c>
       <c r="AS10" s="5">
-        <f t="shared" si="13"/>
-        <v>102.11993692005719</v>
+        <f t="shared" ref="AS10:AZ10" si="11">AR10*1.01</f>
+        <v>112.03146240000001</v>
       </c>
       <c r="AT10" s="5">
-        <f t="shared" si="13"/>
-        <v>103.14113628925776</v>
+        <f t="shared" si="11"/>
+        <v>113.15177702400001</v>
       </c>
       <c r="AU10" s="5">
-        <f t="shared" si="13"/>
-        <v>104.17254765215034</v>
+        <f t="shared" si="11"/>
+        <v>114.28329479424001</v>
       </c>
       <c r="AV10" s="5">
-        <f t="shared" si="13"/>
-        <v>105.21427312867185</v>
+        <f t="shared" si="11"/>
+        <v>115.4261277421824</v>
+      </c>
+      <c r="AW10" s="5">
+        <f t="shared" si="11"/>
+        <v>116.58038901960423</v>
+      </c>
+      <c r="AX10" s="5">
+        <f t="shared" si="11"/>
+        <v>117.74619290980027</v>
+      </c>
+      <c r="AY10" s="5">
+        <f t="shared" si="11"/>
+        <v>118.92365483889827</v>
+      </c>
+      <c r="AZ10" s="5">
+        <f t="shared" si="11"/>
+        <v>120.11289138728726</v>
       </c>
     </row>
-    <row r="11" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:52" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>19</v>
       </c>
@@ -1890,42 +1927,34 @@
       <c r="AD11" s="5">
         <v>0</v>
       </c>
-      <c r="AF11" s="5">
+      <c r="AE11" s="5"/>
+      <c r="AF11" s="5"/>
+      <c r="AG11" s="5"/>
+      <c r="AH11" s="5"/>
+      <c r="AJ11" s="5">
         <v>0</v>
       </c>
-      <c r="AG11" s="5">
+      <c r="AK11" s="5">
         <v>0</v>
       </c>
-      <c r="AH11" s="5">
+      <c r="AL11" s="5">
         <v>0</v>
       </c>
-      <c r="AI11" s="5">
+      <c r="AM11" s="5">
+        <f t="shared" si="5"/>
+        <v>10.1</v>
+      </c>
+      <c r="AN11" s="5">
         <f t="shared" si="6"/>
-        <v>10.1</v>
-      </c>
-      <c r="AJ11" s="5">
+        <v>-5.6000000000000005</v>
+      </c>
+      <c r="AO11" s="5">
         <f t="shared" si="7"/>
-        <v>-5.6000000000000005</v>
-      </c>
-      <c r="AK11" s="5">
+        <v>8.9</v>
+      </c>
+      <c r="AP11" s="5">
         <f t="shared" si="8"/>
-        <v>8.9</v>
-      </c>
-      <c r="AL11" s="5">
-        <f t="shared" si="9"/>
         <v>-0.9</v>
-      </c>
-      <c r="AM11" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN11" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO11" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP11" s="5">
-        <v>0</v>
       </c>
       <c r="AQ11" s="5">
         <v>0</v>
@@ -1945,298 +1974,318 @@
       <c r="AV11" s="5">
         <v>0</v>
       </c>
+      <c r="AW11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:52" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>18</v>
       </c>
       <c r="M12" s="5">
-        <f t="shared" ref="M12:AB12" si="14">SUM(M8:M11)</f>
+        <f t="shared" ref="M12:AB12" si="12">SUM(M8:M11)</f>
         <v>99.1</v>
       </c>
       <c r="N12" s="5">
+        <f t="shared" si="12"/>
+        <v>118.80000000000001</v>
+      </c>
+      <c r="O12" s="5">
+        <f t="shared" si="12"/>
+        <v>114.9</v>
+      </c>
+      <c r="P12" s="5">
+        <f t="shared" si="12"/>
+        <v>126.2</v>
+      </c>
+      <c r="Q12" s="5">
+        <f t="shared" si="12"/>
+        <v>123.9</v>
+      </c>
+      <c r="R12" s="5">
+        <f t="shared" si="12"/>
+        <v>143.79999999999998</v>
+      </c>
+      <c r="S12" s="5">
+        <f t="shared" si="12"/>
+        <v>116.49999999999999</v>
+      </c>
+      <c r="T12" s="5">
+        <f t="shared" si="12"/>
+        <v>118.29999999999998</v>
+      </c>
+      <c r="U12" s="5">
+        <f t="shared" si="12"/>
+        <v>122.80000000000001</v>
+      </c>
+      <c r="V12" s="5">
+        <f t="shared" si="12"/>
+        <v>117.9</v>
+      </c>
+      <c r="W12" s="5">
+        <f t="shared" si="12"/>
+        <v>119.3</v>
+      </c>
+      <c r="X12" s="5">
+        <f t="shared" si="12"/>
+        <v>121.4</v>
+      </c>
+      <c r="Y12" s="5">
+        <f t="shared" si="12"/>
+        <v>118</v>
+      </c>
+      <c r="Z12" s="5">
+        <f t="shared" si="12"/>
+        <v>126.00000000000001</v>
+      </c>
+      <c r="AA12" s="5">
+        <f t="shared" si="12"/>
+        <v>112.29999999999998</v>
+      </c>
+      <c r="AB12" s="5">
+        <f t="shared" si="12"/>
+        <v>117.80000000000001</v>
+      </c>
+      <c r="AC12" s="5">
+        <f t="shared" ref="AC12:AD12" si="13">SUM(AC8:AC11)</f>
+        <v>121.60000000000001</v>
+      </c>
+      <c r="AD12" s="5">
+        <f t="shared" si="13"/>
+        <v>139.1</v>
+      </c>
+      <c r="AE12" s="5"/>
+      <c r="AF12" s="5"/>
+      <c r="AG12" s="5"/>
+      <c r="AH12" s="5"/>
+      <c r="AJ12" s="5">
+        <f t="shared" ref="AJ12:AP12" si="14">SUM(AJ8:AJ11)</f>
+        <v>143.20000000000002</v>
+      </c>
+      <c r="AK12" s="5">
         <f t="shared" si="14"/>
-        <v>118.80000000000001</v>
-      </c>
-      <c r="O12" s="5">
+        <v>221.2</v>
+      </c>
+      <c r="AL12" s="5">
         <f t="shared" si="14"/>
-        <v>114.9</v>
-      </c>
-      <c r="P12" s="5">
+        <v>392.50000000000006</v>
+      </c>
+      <c r="AM12" s="5">
         <f t="shared" si="14"/>
-        <v>126.2</v>
-      </c>
-      <c r="Q12" s="5">
+        <v>508.80000000000007</v>
+      </c>
+      <c r="AN12" s="5">
         <f t="shared" si="14"/>
-        <v>123.9</v>
-      </c>
-      <c r="R12" s="5">
+        <v>475.49999999999994</v>
+      </c>
+      <c r="AO12" s="5">
         <f t="shared" si="14"/>
-        <v>143.79999999999998</v>
-      </c>
-      <c r="S12" s="5">
+        <v>484.69999999999993</v>
+      </c>
+      <c r="AP12" s="5">
         <f t="shared" si="14"/>
-        <v>116.49999999999999</v>
-      </c>
-      <c r="T12" s="5">
-        <f t="shared" si="14"/>
-        <v>118.29999999999998</v>
-      </c>
-      <c r="U12" s="5">
-        <f t="shared" si="14"/>
-        <v>122.80000000000001</v>
-      </c>
-      <c r="V12" s="5">
-        <f t="shared" si="14"/>
-        <v>117.9</v>
-      </c>
-      <c r="W12" s="5">
-        <f t="shared" si="14"/>
-        <v>119.3</v>
-      </c>
-      <c r="X12" s="5">
-        <f t="shared" si="14"/>
-        <v>121.4</v>
-      </c>
-      <c r="Y12" s="5">
-        <f t="shared" si="14"/>
-        <v>118</v>
-      </c>
-      <c r="Z12" s="5">
-        <f t="shared" si="14"/>
-        <v>126.00000000000001</v>
-      </c>
-      <c r="AA12" s="5">
-        <f t="shared" si="14"/>
-        <v>112.29999999999998</v>
-      </c>
-      <c r="AB12" s="5">
-        <f t="shared" si="14"/>
-        <v>117.80000000000001</v>
-      </c>
-      <c r="AC12" s="5">
-        <f t="shared" ref="AC12:AD12" si="15">SUM(AC8:AC11)</f>
-        <v>121.60000000000001</v>
-      </c>
-      <c r="AD12" s="5">
+        <v>490.80000000000007</v>
+      </c>
+      <c r="AQ12" s="5">
+        <f t="shared" ref="AQ12:AR12" si="15">SUM(AQ8:AQ11)</f>
+        <v>491.60124999999999</v>
+      </c>
+      <c r="AR12" s="5">
         <f t="shared" si="15"/>
-        <v>120.82824000000002</v>
-      </c>
-      <c r="AF12" s="5">
-        <f t="shared" ref="AF12:AL12" si="16">SUM(AF8:AF11)</f>
-        <v>143.20000000000002</v>
-      </c>
-      <c r="AG12" s="5">
-        <f t="shared" si="16"/>
-        <v>221.2</v>
-      </c>
-      <c r="AH12" s="5">
-        <f t="shared" si="16"/>
-        <v>392.50000000000006</v>
-      </c>
-      <c r="AI12" s="5">
-        <f t="shared" si="16"/>
-        <v>508.80000000000007</v>
-      </c>
-      <c r="AJ12" s="5">
-        <f t="shared" si="16"/>
-        <v>475.49999999999994</v>
-      </c>
-      <c r="AK12" s="5">
-        <f t="shared" si="16"/>
-        <v>484.69999999999993</v>
-      </c>
-      <c r="AL12" s="5">
-        <f t="shared" si="16"/>
-        <v>472.5282400000001</v>
-      </c>
-      <c r="AM12" s="5">
-        <f t="shared" ref="AM12:AN12" si="17">SUM(AM8:AM11)</f>
-        <v>469.94876399999998</v>
-      </c>
-      <c r="AN12" s="5">
-        <f t="shared" si="17"/>
-        <v>474.25233024000005</v>
-      </c>
-      <c r="AO12" s="5">
-        <f t="shared" ref="AO12" si="18">SUM(AO8:AO11)</f>
-        <v>475.78313914560005</v>
-      </c>
-      <c r="AP12" s="5">
-        <f t="shared" ref="AP12" si="19">SUM(AP8:AP11)</f>
-        <v>485.79994698268797</v>
-      </c>
-      <c r="AQ12" s="5">
-        <f t="shared" ref="AQ12" si="20">SUM(AQ8:AQ11)</f>
-        <v>496.07469219151585</v>
-      </c>
-      <c r="AR12" s="5">
-        <f t="shared" ref="AR12" si="21">SUM(AR8:AR11)</f>
-        <v>506.61468722460199</v>
+        <v>498.70568000000003</v>
       </c>
       <c r="AS12" s="5">
-        <f t="shared" ref="AS12" si="22">SUM(AS8:AS11)</f>
-        <v>517.42745965135418</v>
+        <f t="shared" ref="AS12" si="16">SUM(AS8:AS11)</f>
+        <v>500.37363692500003</v>
       </c>
       <c r="AT12" s="5">
-        <f t="shared" ref="AT12" si="23">SUM(AT8:AT11)</f>
-        <v>528.52075856900899</v>
+        <f t="shared" ref="AT12" si="17">SUM(AT8:AT11)</f>
+        <v>510.81218657675004</v>
       </c>
       <c r="AU12" s="5">
-        <f t="shared" ref="AU12" si="24">SUM(AU8:AU11)</f>
-        <v>539.90256120547463</v>
+        <f t="shared" ref="AU12" si="18">SUM(AU8:AU11)</f>
+        <v>521.51816612349251</v>
       </c>
       <c r="AV12" s="5">
-        <f t="shared" ref="AV12" si="25">SUM(AV8:AV11)</f>
-        <v>551.58107971982827</v>
+        <f t="shared" ref="AV12" si="19">SUM(AV8:AV11)</f>
+        <v>532.49914119613163</v>
+      </c>
+      <c r="AW12" s="5">
+        <f t="shared" ref="AW12" si="20">SUM(AW8:AW11)</f>
+        <v>543.76289982183937</v>
+      </c>
+      <c r="AX12" s="5">
+        <f t="shared" ref="AX12" si="21">SUM(AX8:AX11)</f>
+        <v>555.3174590502166</v>
+      </c>
+      <c r="AY12" s="5">
+        <f t="shared" ref="AY12" si="22">SUM(AY8:AY11)</f>
+        <v>567.17107177778234</v>
+      </c>
+      <c r="AZ12" s="5">
+        <f t="shared" ref="AZ12" si="23">SUM(AZ8:AZ11)</f>
+        <v>579.33223377673551</v>
       </c>
     </row>
-    <row r="13" spans="2:48" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:52" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="M13" s="8">
-        <f t="shared" ref="M13:AB13" si="26">M7-M12</f>
+        <f t="shared" ref="M13:AB13" si="24">M7-M12</f>
         <v>-31.399999999999991</v>
       </c>
       <c r="N13" s="8">
+        <f t="shared" si="24"/>
+        <v>-47.500000000000014</v>
+      </c>
+      <c r="O13" s="8">
+        <f t="shared" si="24"/>
+        <v>-37.299999999999997</v>
+      </c>
+      <c r="P13" s="8">
+        <f t="shared" si="24"/>
+        <v>-47.8</v>
+      </c>
+      <c r="Q13" s="8">
+        <f t="shared" si="24"/>
+        <v>-36.299999999999997</v>
+      </c>
+      <c r="R13" s="8">
+        <f t="shared" si="24"/>
+        <v>-55.899999999999991</v>
+      </c>
+      <c r="S13" s="8">
+        <f t="shared" si="24"/>
+        <v>-39.099999999999994</v>
+      </c>
+      <c r="T13" s="8">
+        <f t="shared" si="24"/>
+        <v>-38.599999999999994</v>
+      </c>
+      <c r="U13" s="8">
+        <f t="shared" si="24"/>
+        <v>-39.600000000000009</v>
+      </c>
+      <c r="V13" s="8">
+        <f t="shared" si="24"/>
+        <v>-28.599999999999994</v>
+      </c>
+      <c r="W13" s="8">
+        <f t="shared" si="24"/>
+        <v>-29.799999999999997</v>
+      </c>
+      <c r="X13" s="8">
+        <f t="shared" si="24"/>
+        <v>-31.199999999999989</v>
+      </c>
+      <c r="Y13" s="8">
+        <f t="shared" si="24"/>
+        <v>-21.800000000000011</v>
+      </c>
+      <c r="Z13" s="8">
+        <f t="shared" si="24"/>
+        <v>-30.500000000000028</v>
+      </c>
+      <c r="AA13" s="8">
+        <f t="shared" si="24"/>
+        <v>-14.399999999999977</v>
+      </c>
+      <c r="AB13" s="8">
+        <f t="shared" si="24"/>
+        <v>-15.100000000000023</v>
+      </c>
+      <c r="AC13" s="8">
+        <f t="shared" ref="AC13:AD13" si="25">AC7-AC12</f>
+        <v>-15.600000000000023</v>
+      </c>
+      <c r="AD13" s="8">
+        <f t="shared" si="25"/>
+        <v>-32.299999999999983</v>
+      </c>
+      <c r="AE13" s="8"/>
+      <c r="AF13" s="8"/>
+      <c r="AG13" s="8"/>
+      <c r="AH13" s="8"/>
+      <c r="AJ13" s="8">
+        <f t="shared" ref="AJ13:AP13" si="26">AJ7-AJ12</f>
+        <v>-48.400000000000006</v>
+      </c>
+      <c r="AK13" s="8">
         <f t="shared" si="26"/>
-        <v>-47.500000000000014</v>
-      </c>
-      <c r="O13" s="8">
+        <v>-66.5</v>
+      </c>
+      <c r="AL13" s="8">
         <f t="shared" si="26"/>
-        <v>-37.299999999999997</v>
-      </c>
-      <c r="P13" s="8">
+        <v>-143.00000000000006</v>
+      </c>
+      <c r="AM13" s="8">
         <f t="shared" si="26"/>
-        <v>-47.8</v>
-      </c>
-      <c r="Q13" s="8">
+        <v>-177.30000000000013</v>
+      </c>
+      <c r="AN13" s="8">
         <f t="shared" si="26"/>
-        <v>-36.299999999999997</v>
-      </c>
-      <c r="R13" s="8">
+        <v>-145.90000000000003</v>
+      </c>
+      <c r="AO13" s="8">
         <f t="shared" si="26"/>
-        <v>-55.899999999999991</v>
-      </c>
-      <c r="S13" s="8">
+        <v>-113.2999999999999</v>
+      </c>
+      <c r="AP13" s="8">
         <f t="shared" si="26"/>
-        <v>-39.099999999999994</v>
-      </c>
-      <c r="T13" s="8">
-        <f t="shared" si="26"/>
-        <v>-38.599999999999994</v>
-      </c>
-      <c r="U13" s="8">
-        <f t="shared" si="26"/>
-        <v>-39.600000000000009</v>
-      </c>
-      <c r="V13" s="8">
-        <f t="shared" si="26"/>
-        <v>-28.599999999999994</v>
-      </c>
-      <c r="W13" s="8">
-        <f t="shared" si="26"/>
-        <v>-29.799999999999997</v>
-      </c>
-      <c r="X13" s="8">
-        <f t="shared" si="26"/>
-        <v>-31.199999999999989</v>
-      </c>
-      <c r="Y13" s="8">
-        <f t="shared" si="26"/>
-        <v>-21.800000000000011</v>
-      </c>
-      <c r="Z13" s="8">
-        <f t="shared" si="26"/>
-        <v>-30.500000000000028</v>
-      </c>
-      <c r="AA13" s="8">
-        <f t="shared" si="26"/>
-        <v>-14.399999999999977</v>
-      </c>
-      <c r="AB13" s="8">
-        <f t="shared" si="26"/>
-        <v>-15.100000000000023</v>
-      </c>
-      <c r="AC13" s="8">
-        <f t="shared" ref="AC13:AD13" si="27">AC7-AC12</f>
-        <v>-15.600000000000023</v>
-      </c>
-      <c r="AD13" s="8">
+        <v>-77.400000000000205</v>
+      </c>
+      <c r="AQ13" s="8">
+        <f t="shared" ref="AQ13:AR13" si="27">AQ7-AQ12</f>
+        <v>-37.707249999999988</v>
+      </c>
+      <c r="AR13" s="8">
         <f t="shared" si="27"/>
-        <v>-14.383440000000007</v>
-      </c>
-      <c r="AF13" s="8">
-        <f t="shared" ref="AF13:AL13" si="28">AF7-AF12</f>
-        <v>-48.400000000000006</v>
-      </c>
-      <c r="AG13" s="8">
-        <f t="shared" si="28"/>
-        <v>-66.5</v>
-      </c>
-      <c r="AH13" s="8">
-        <f t="shared" si="28"/>
-        <v>-143.00000000000006</v>
-      </c>
-      <c r="AI13" s="8">
-        <f t="shared" si="28"/>
-        <v>-177.30000000000013</v>
-      </c>
-      <c r="AJ13" s="8">
-        <f t="shared" si="28"/>
-        <v>-145.90000000000003</v>
-      </c>
-      <c r="AK13" s="8">
-        <f t="shared" si="28"/>
-        <v>-113.2999999999999</v>
-      </c>
-      <c r="AL13" s="8">
-        <f t="shared" si="28"/>
-        <v>-59.483440000000087</v>
-      </c>
-      <c r="AM13" s="8">
-        <f t="shared" ref="AM13:AN13" si="29">AM7-AM12</f>
-        <v>-26.516795999999943</v>
-      </c>
-      <c r="AN13" s="8">
-        <f t="shared" si="29"/>
-        <v>-4.8479184000000828</v>
-      </c>
-      <c r="AO13" s="8">
-        <f t="shared" ref="AO13" si="30">AO7-AO12</f>
-        <v>16.185625123199941</v>
-      </c>
-      <c r="AP13" s="8">
-        <f t="shared" ref="AP13" si="31">AP7-AP12</f>
-        <v>20.927880214176014</v>
-      </c>
-      <c r="AQ13" s="8">
-        <f t="shared" ref="AQ13" si="32">AQ7-AQ12</f>
-        <v>25.854969821254031</v>
-      </c>
-      <c r="AR13" s="8">
-        <f t="shared" ref="AR13" si="33">AR7-AR12</f>
-        <v>30.972864648551081</v>
+        <v>-13.606467500000065</v>
       </c>
       <c r="AS13" s="8">
-        <f t="shared" ref="AS13" si="34">AS7-AS12</f>
-        <v>36.287718777993518</v>
+        <f t="shared" ref="AS13" si="28">AS7-AS12</f>
+        <v>-0.72144805000004908</v>
       </c>
       <c r="AT13" s="8">
-        <f t="shared" ref="AT13" si="35">AT7-AT12</f>
-        <v>41.80587521321911</v>
+        <f t="shared" ref="AT13" si="29">AT7-AT12</f>
+        <v>3.8295679644999154</v>
       </c>
       <c r="AU13" s="8">
-        <f t="shared" ref="AU13" si="36">AU7-AU12</f>
-        <v>47.533871590220315</v>
+        <f t="shared" ref="AU13" si="30">AU7-AU12</f>
+        <v>8.5628410539950437</v>
       </c>
       <c r="AV13" s="8">
-        <f t="shared" ref="AV13" si="37">AV7-AV12</f>
-        <v>53.478446059737507</v>
+        <f t="shared" ref="AV13" si="31">AV7-AV12</f>
+        <v>13.484296196680475</v>
+      </c>
+      <c r="AW13" s="8">
+        <f t="shared" ref="AW13" si="32">AW7-AW12</f>
+        <v>18.600040692757148</v>
+      </c>
+      <c r="AX13" s="8">
+        <f t="shared" ref="AX13" si="33">AX7-AX12</f>
+        <v>23.916369679817876</v>
+      </c>
+      <c r="AY13" s="8">
+        <f t="shared" ref="AY13" si="34">AY7-AY12</f>
+        <v>29.439771814153119</v>
+      </c>
+      <c r="AZ13" s="8">
+        <f t="shared" ref="AZ13" si="35">AZ7-AZ12</f>
+        <v>35.176935122958071</v>
       </c>
     </row>
-    <row r="14" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:52" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>21</v>
       </c>
@@ -2292,75 +2341,79 @@
         <v>-8.3000000000000007</v>
       </c>
       <c r="AD14" s="5">
-        <v>-8</v>
-      </c>
-      <c r="AF14" s="5">
+        <v>-7.9</v>
+      </c>
+      <c r="AE14" s="5"/>
+      <c r="AF14" s="5"/>
+      <c r="AG14" s="5"/>
+      <c r="AH14" s="5"/>
+      <c r="AJ14" s="5">
         <v>-3.3</v>
       </c>
-      <c r="AG14" s="5">
+      <c r="AK14" s="5">
         <v>-1.2</v>
       </c>
-      <c r="AH14" s="5">
+      <c r="AL14" s="5">
         <v>-0.3</v>
       </c>
-      <c r="AI14" s="5">
-        <f t="shared" ref="AI14:AI15" si="38">SUM(O14:R14)</f>
+      <c r="AM14" s="5">
+        <f t="shared" ref="AM14:AM15" si="36">SUM(O14:R14)</f>
         <v>-9.1</v>
       </c>
-      <c r="AJ14" s="5">
-        <f t="shared" ref="AJ14:AJ15" si="39">SUM(S14:V14)</f>
+      <c r="AN14" s="5">
+        <f t="shared" ref="AN14:AN15" si="37">SUM(S14:V14)</f>
         <v>-34.400000000000006</v>
       </c>
-      <c r="AK14" s="5">
-        <f t="shared" ref="AK14:AK15" si="40">SUM(W14:Z14)</f>
+      <c r="AO14" s="5">
+        <f t="shared" ref="AO14:AO15" si="38">SUM(W14:Z14)</f>
         <v>-36.799999999999997</v>
       </c>
-      <c r="AL14" s="5">
-        <f t="shared" ref="AL14:AL15" si="41">SUM(AA14:AD14)</f>
-        <v>-32.1</v>
-      </c>
-      <c r="AM14" s="5">
-        <f>AL14*1.01</f>
-        <v>-32.420999999999999</v>
-      </c>
-      <c r="AN14" s="5">
-        <f>AM14*1.01</f>
-        <v>-32.74521</v>
-      </c>
-      <c r="AO14" s="5">
-        <f t="shared" ref="AO14:AV14" si="42">AN14*1.01</f>
-        <v>-33.072662100000002</v>
-      </c>
       <c r="AP14" s="5">
-        <f t="shared" si="42"/>
-        <v>-33.403388721000006</v>
+        <f t="shared" ref="AP14:AP15" si="39">SUM(AA14:AD14)</f>
+        <v>-32</v>
       </c>
       <c r="AQ14" s="5">
-        <f t="shared" si="42"/>
-        <v>-33.737422608210004</v>
+        <f>AP14*1.01</f>
+        <v>-32.32</v>
       </c>
       <c r="AR14" s="5">
-        <f t="shared" si="42"/>
-        <v>-34.074796834292101</v>
+        <f>AQ14*1.01</f>
+        <v>-32.6432</v>
       </c>
       <c r="AS14" s="5">
-        <f t="shared" si="42"/>
-        <v>-34.415544802635026</v>
+        <f t="shared" ref="AS14:AZ14" si="40">AR14*1.01</f>
+        <v>-32.969631999999997</v>
       </c>
       <c r="AT14" s="5">
-        <f t="shared" si="42"/>
-        <v>-34.759700250661375</v>
+        <f t="shared" si="40"/>
+        <v>-33.299328320000001</v>
       </c>
       <c r="AU14" s="5">
-        <f t="shared" si="42"/>
-        <v>-35.107297253167992</v>
+        <f t="shared" si="40"/>
+        <v>-33.632321603199998</v>
       </c>
       <c r="AV14" s="5">
-        <f t="shared" si="42"/>
-        <v>-35.458370225699674</v>
+        <f t="shared" si="40"/>
+        <v>-33.968644819231997</v>
+      </c>
+      <c r="AW14" s="5">
+        <f t="shared" si="40"/>
+        <v>-34.308331267424315</v>
+      </c>
+      <c r="AX14" s="5">
+        <f t="shared" si="40"/>
+        <v>-34.65141458009856</v>
+      </c>
+      <c r="AY14" s="5">
+        <f t="shared" si="40"/>
+        <v>-34.997928725899548</v>
+      </c>
+      <c r="AZ14" s="5">
+        <f t="shared" si="40"/>
+        <v>-35.347908013158545</v>
       </c>
     </row>
-    <row r="15" spans="2:48" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:52" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>22</v>
       </c>
@@ -2416,45 +2469,37 @@
         <v>0.5</v>
       </c>
       <c r="AD15" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="AE15" s="5"/>
+      <c r="AF15" s="5"/>
+      <c r="AG15" s="5"/>
+      <c r="AH15" s="5"/>
+      <c r="AJ15" s="5">
         <f>0.6+0.3</f>
         <v>0.89999999999999991</v>
       </c>
-      <c r="AG15" s="5">
+      <c r="AK15" s="5">
         <v>-0.1</v>
       </c>
-      <c r="AH15" s="5">
+      <c r="AL15" s="5">
         <v>0.3</v>
       </c>
-      <c r="AI15" s="5">
+      <c r="AM15" s="5">
+        <f t="shared" si="36"/>
+        <v>2.4</v>
+      </c>
+      <c r="AN15" s="5">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="AO15" s="5">
         <f t="shared" si="38"/>
-        <v>2.4</v>
-      </c>
-      <c r="AJ15" s="5">
+        <v>2</v>
+      </c>
+      <c r="AP15" s="5">
         <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="AK15" s="5">
-        <f t="shared" si="40"/>
-        <v>2</v>
-      </c>
-      <c r="AL15" s="5">
-        <f t="shared" si="41"/>
-        <v>9.9999999999999978E-2</v>
-      </c>
-      <c r="AM15" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="5">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ15" s="5">
         <v>0</v>
@@ -2474,153 +2519,169 @@
       <c r="AV15" s="5">
         <v>0</v>
       </c>
+      <c r="AW15" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX15" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY15" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="2:48" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:52" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>23</v>
       </c>
       <c r="M16" s="8">
-        <f t="shared" ref="M16:AB16" si="43">M13-M14-M15</f>
+        <f t="shared" ref="M16:AB16" si="41">M13-M14-M15</f>
         <v>-31.599999999999991</v>
       </c>
       <c r="N16" s="8">
+        <f t="shared" si="41"/>
+        <v>-47.500000000000014</v>
+      </c>
+      <c r="O16" s="8">
+        <f t="shared" si="41"/>
+        <v>-37.4</v>
+      </c>
+      <c r="P16" s="8">
+        <f t="shared" si="41"/>
+        <v>-48.2</v>
+      </c>
+      <c r="Q16" s="8">
+        <f t="shared" si="41"/>
+        <v>-35</v>
+      </c>
+      <c r="R16" s="8">
+        <f t="shared" si="41"/>
+        <v>-49.999999999999986</v>
+      </c>
+      <c r="S16" s="8">
+        <f t="shared" si="41"/>
+        <v>-30.999999999999993</v>
+      </c>
+      <c r="T16" s="8">
+        <f t="shared" si="41"/>
+        <v>-30.399999999999995</v>
+      </c>
+      <c r="U16" s="8">
+        <f t="shared" si="41"/>
+        <v>-31.000000000000011</v>
+      </c>
+      <c r="V16" s="8">
+        <f t="shared" si="41"/>
+        <v>-19.099999999999994</v>
+      </c>
+      <c r="W16" s="8">
+        <f t="shared" si="41"/>
+        <v>-20.499999999999996</v>
+      </c>
+      <c r="X16" s="8">
+        <f t="shared" si="41"/>
+        <v>-21.899999999999988</v>
+      </c>
+      <c r="Y16" s="8">
+        <f t="shared" si="41"/>
+        <v>-12.200000000000012</v>
+      </c>
+      <c r="Z16" s="8">
+        <f t="shared" si="41"/>
+        <v>-23.900000000000027</v>
+      </c>
+      <c r="AA16" s="8">
+        <f t="shared" si="41"/>
+        <v>-6.2999999999999776</v>
+      </c>
+      <c r="AB16" s="8">
+        <f t="shared" si="41"/>
+        <v>-7.0000000000000231</v>
+      </c>
+      <c r="AC16" s="8">
+        <f t="shared" ref="AC16:AD16" si="42">AC13-AC14-AC15</f>
+        <v>-7.800000000000022</v>
+      </c>
+      <c r="AD16" s="8">
+        <f t="shared" si="42"/>
+        <v>-24.799999999999983</v>
+      </c>
+      <c r="AE16" s="8"/>
+      <c r="AF16" s="8"/>
+      <c r="AG16" s="8"/>
+      <c r="AH16" s="8"/>
+      <c r="AJ16" s="8">
+        <f t="shared" ref="AJ16:AP16" si="43">AJ13-AJ14-AJ15</f>
+        <v>-46.000000000000007</v>
+      </c>
+      <c r="AK16" s="8">
         <f t="shared" si="43"/>
-        <v>-47.500000000000014</v>
-      </c>
-      <c r="O16" s="8">
+        <v>-65.2</v>
+      </c>
+      <c r="AL16" s="8">
         <f t="shared" si="43"/>
-        <v>-37.4</v>
-      </c>
-      <c r="P16" s="8">
+        <v>-143.00000000000006</v>
+      </c>
+      <c r="AM16" s="8">
         <f t="shared" si="43"/>
-        <v>-48.2</v>
-      </c>
-      <c r="Q16" s="8">
+        <v>-170.60000000000014</v>
+      </c>
+      <c r="AN16" s="8">
         <f t="shared" si="43"/>
-        <v>-35</v>
-      </c>
-      <c r="R16" s="8">
+        <v>-111.50000000000003</v>
+      </c>
+      <c r="AO16" s="8">
         <f t="shared" si="43"/>
-        <v>-49.999999999999986</v>
-      </c>
-      <c r="S16" s="8">
+        <v>-78.499999999999901</v>
+      </c>
+      <c r="AP16" s="8">
         <f t="shared" si="43"/>
-        <v>-30.999999999999993</v>
-      </c>
-      <c r="T16" s="8">
-        <f t="shared" si="43"/>
-        <v>-30.399999999999995</v>
-      </c>
-      <c r="U16" s="8">
-        <f t="shared" si="43"/>
-        <v>-31.000000000000011</v>
-      </c>
-      <c r="V16" s="8">
-        <f t="shared" si="43"/>
-        <v>-19.099999999999994</v>
-      </c>
-      <c r="W16" s="8">
-        <f t="shared" si="43"/>
-        <v>-20.499999999999996</v>
-      </c>
-      <c r="X16" s="8">
-        <f t="shared" si="43"/>
-        <v>-21.899999999999988</v>
-      </c>
-      <c r="Y16" s="8">
-        <f t="shared" si="43"/>
-        <v>-12.200000000000012</v>
-      </c>
-      <c r="Z16" s="8">
-        <f t="shared" si="43"/>
-        <v>-23.900000000000027</v>
-      </c>
-      <c r="AA16" s="8">
-        <f t="shared" si="43"/>
-        <v>-6.2999999999999776</v>
-      </c>
-      <c r="AB16" s="8">
-        <f t="shared" si="43"/>
-        <v>-7.0000000000000231</v>
-      </c>
-      <c r="AC16" s="8">
-        <f t="shared" ref="AC16:AD16" si="44">AC13-AC14-AC15</f>
-        <v>-7.800000000000022</v>
-      </c>
-      <c r="AD16" s="8">
+        <v>-45.900000000000205</v>
+      </c>
+      <c r="AQ16" s="8">
+        <f t="shared" ref="AQ16:AR16" si="44">AQ13-AQ14-AQ15</f>
+        <v>-5.3872499999999874</v>
+      </c>
+      <c r="AR16" s="8">
         <f t="shared" si="44"/>
-        <v>-6.3834400000000073</v>
-      </c>
-      <c r="AF16" s="8">
-        <f t="shared" ref="AF16:AL16" si="45">AF13-AF14-AF15</f>
-        <v>-46.000000000000007</v>
-      </c>
-      <c r="AG16" s="8">
-        <f t="shared" si="45"/>
-        <v>-65.2</v>
-      </c>
-      <c r="AH16" s="8">
-        <f t="shared" si="45"/>
-        <v>-143.00000000000006</v>
-      </c>
-      <c r="AI16" s="8">
-        <f t="shared" si="45"/>
-        <v>-170.60000000000014</v>
-      </c>
-      <c r="AJ16" s="8">
-        <f t="shared" si="45"/>
-        <v>-111.50000000000003</v>
-      </c>
-      <c r="AK16" s="8">
-        <f t="shared" si="45"/>
-        <v>-78.499999999999901</v>
-      </c>
-      <c r="AL16" s="8">
-        <f t="shared" si="45"/>
-        <v>-27.483440000000087</v>
-      </c>
-      <c r="AM16" s="8">
-        <f t="shared" ref="AM16:AN16" si="46">AM13-AM14-AM15</f>
-        <v>5.9042040000000569</v>
-      </c>
-      <c r="AN16" s="8">
-        <f t="shared" si="46"/>
-        <v>27.897291599999917</v>
-      </c>
-      <c r="AO16" s="8">
-        <f t="shared" ref="AO16" si="47">AO13-AO14-AO15</f>
-        <v>49.258287223199943</v>
-      </c>
-      <c r="AP16" s="8">
-        <f t="shared" ref="AP16" si="48">AP13-AP14-AP15</f>
-        <v>54.33126893517602</v>
-      </c>
-      <c r="AQ16" s="8">
-        <f t="shared" ref="AQ16" si="49">AQ13-AQ14-AQ15</f>
-        <v>59.592392429464034</v>
-      </c>
-      <c r="AR16" s="8">
-        <f t="shared" ref="AR16" si="50">AR13-AR14-AR15</f>
-        <v>65.047661482843182</v>
+        <v>19.036732499999935</v>
       </c>
       <c r="AS16" s="8">
-        <f t="shared" ref="AS16" si="51">AS13-AS14-AS15</f>
-        <v>70.703263580628544</v>
+        <f t="shared" ref="AS16" si="45">AS13-AS14-AS15</f>
+        <v>32.248183949999948</v>
       </c>
       <c r="AT16" s="8">
-        <f t="shared" ref="AT16" si="52">AT13-AT14-AT15</f>
-        <v>76.565575463880492</v>
+        <f t="shared" ref="AT16" si="46">AT13-AT14-AT15</f>
+        <v>37.128896284499916</v>
       </c>
       <c r="AU16" s="8">
-        <f t="shared" ref="AU16" si="53">AU13-AU14-AU15</f>
-        <v>82.6411688433883</v>
+        <f t="shared" ref="AU16" si="47">AU13-AU14-AU15</f>
+        <v>42.195162657195041</v>
       </c>
       <c r="AV16" s="8">
-        <f t="shared" ref="AV16" si="54">AV13-AV14-AV15</f>
-        <v>88.936816285437175</v>
+        <f t="shared" ref="AV16" si="48">AV13-AV14-AV15</f>
+        <v>47.452941015912472</v>
+      </c>
+      <c r="AW16" s="8">
+        <f t="shared" ref="AW16" si="49">AW13-AW14-AW15</f>
+        <v>52.908371960181462</v>
+      </c>
+      <c r="AX16" s="8">
+        <f t="shared" ref="AX16" si="50">AX13-AX14-AX15</f>
+        <v>58.567784259916436</v>
+      </c>
+      <c r="AY16" s="8">
+        <f t="shared" ref="AY16" si="51">AY13-AY14-AY15</f>
+        <v>64.437700540052674</v>
+      </c>
+      <c r="AZ16" s="8">
+        <f t="shared" ref="AZ16" si="52">AZ13-AZ14-AZ15</f>
+        <v>70.524843136116615</v>
       </c>
     </row>
-    <row r="17" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>24</v>
       </c>
@@ -2676,604 +2737,612 @@
         <v>0.8</v>
       </c>
       <c r="AD17" s="5">
-        <v>1</v>
-      </c>
-      <c r="AF17" s="5">
+        <v>2</v>
+      </c>
+      <c r="AE17" s="5"/>
+      <c r="AF17" s="5"/>
+      <c r="AG17" s="5"/>
+      <c r="AH17" s="5"/>
+      <c r="AJ17" s="5">
         <v>0.7</v>
       </c>
-      <c r="AG17" s="5">
+      <c r="AK17" s="5">
         <v>1.5</v>
       </c>
-      <c r="AH17" s="5">
+      <c r="AL17" s="5">
         <v>2.1</v>
       </c>
-      <c r="AI17" s="5">
+      <c r="AM17" s="5">
         <f>SUM(O17:R17)</f>
         <v>4.7</v>
       </c>
-      <c r="AJ17" s="5">
+      <c r="AN17" s="5">
         <f>SUM(S17:V17)</f>
         <v>5.3</v>
       </c>
-      <c r="AK17" s="5">
+      <c r="AO17" s="5">
         <f>SUM(W17:Z17)</f>
         <v>1</v>
       </c>
-      <c r="AL17" s="5">
+      <c r="AP17" s="5">
         <f>SUM(AA17:AD17)</f>
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="AM17" s="5">
-        <f>AM16*0.1</f>
-        <v>0.59042040000000573</v>
-      </c>
-      <c r="AN17" s="5">
-        <f>AN16*0.1</f>
-        <v>2.7897291599999918</v>
-      </c>
-      <c r="AO17" s="5">
-        <f t="shared" ref="AO17:AV17" si="55">AO16*0.1</f>
-        <v>4.925828722319995</v>
-      </c>
-      <c r="AP17" s="5">
-        <f t="shared" si="55"/>
-        <v>5.4331268935176027</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="AQ17" s="5">
-        <f t="shared" si="55"/>
-        <v>5.9592392429464036</v>
+        <f>AQ16*0.1</f>
+        <v>-0.53872499999999879</v>
       </c>
       <c r="AR17" s="5">
-        <f t="shared" si="55"/>
-        <v>6.5047661482843182</v>
+        <f>AR16*0.1</f>
+        <v>1.9036732499999935</v>
       </c>
       <c r="AS17" s="5">
-        <f t="shared" si="55"/>
-        <v>7.0703263580628546</v>
+        <f t="shared" ref="AS17:AZ17" si="53">AS16*0.1</f>
+        <v>3.2248183949999949</v>
       </c>
       <c r="AT17" s="5">
-        <f t="shared" si="55"/>
-        <v>7.6565575463880498</v>
+        <f t="shared" si="53"/>
+        <v>3.7128896284499917</v>
       </c>
       <c r="AU17" s="5">
-        <f t="shared" si="55"/>
-        <v>8.2641168843388311</v>
+        <f t="shared" si="53"/>
+        <v>4.2195162657195047</v>
       </c>
       <c r="AV17" s="5">
-        <f t="shared" si="55"/>
-        <v>8.8936816285437175</v>
+        <f t="shared" si="53"/>
+        <v>4.7452941015912478</v>
+      </c>
+      <c r="AW17" s="5">
+        <f t="shared" si="53"/>
+        <v>5.2908371960181464</v>
+      </c>
+      <c r="AX17" s="5">
+        <f t="shared" si="53"/>
+        <v>5.856778425991644</v>
+      </c>
+      <c r="AY17" s="5">
+        <f t="shared" si="53"/>
+        <v>6.4437700540052676</v>
+      </c>
+      <c r="AZ17" s="5">
+        <f t="shared" si="53"/>
+        <v>7.0524843136116617</v>
       </c>
     </row>
-    <row r="18" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:148" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="M18" s="8">
-        <f t="shared" ref="M18:AB18" si="56">M16-M17</f>
+        <f t="shared" ref="M18:AB18" si="54">M16-M17</f>
         <v>-32.399999999999991</v>
       </c>
       <c r="N18" s="8">
+        <f t="shared" si="54"/>
+        <v>-47.700000000000017</v>
+      </c>
+      <c r="O18" s="8">
+        <f t="shared" si="54"/>
+        <v>-38.4</v>
+      </c>
+      <c r="P18" s="8">
+        <f t="shared" si="54"/>
+        <v>-49.400000000000006</v>
+      </c>
+      <c r="Q18" s="8">
+        <f t="shared" si="54"/>
+        <v>-36</v>
+      </c>
+      <c r="R18" s="8">
+        <f t="shared" si="54"/>
+        <v>-51.499999999999986</v>
+      </c>
+      <c r="S18" s="8">
+        <f t="shared" si="54"/>
+        <v>-32.399999999999991</v>
+      </c>
+      <c r="T18" s="8">
+        <f t="shared" si="54"/>
+        <v>-31.999999999999996</v>
+      </c>
+      <c r="U18" s="8">
+        <f t="shared" si="54"/>
+        <v>-32.000000000000014</v>
+      </c>
+      <c r="V18" s="8">
+        <f t="shared" si="54"/>
+        <v>-20.399999999999995</v>
+      </c>
+      <c r="W18" s="8">
+        <f t="shared" si="54"/>
+        <v>-21.299999999999997</v>
+      </c>
+      <c r="X18" s="8">
+        <f t="shared" si="54"/>
+        <v>-22.899999999999988</v>
+      </c>
+      <c r="Y18" s="8">
+        <f t="shared" si="54"/>
+        <v>-13.700000000000012</v>
+      </c>
+      <c r="Z18" s="8">
+        <f t="shared" si="54"/>
+        <v>-21.600000000000026</v>
+      </c>
+      <c r="AA18" s="8">
+        <f t="shared" si="54"/>
+        <v>-7.7999999999999776</v>
+      </c>
+      <c r="AB18" s="8">
+        <f t="shared" si="54"/>
+        <v>-7.8000000000000229</v>
+      </c>
+      <c r="AC18" s="8">
+        <f t="shared" ref="AC18:AD18" si="55">AC16-AC17</f>
+        <v>-8.6000000000000227</v>
+      </c>
+      <c r="AD18" s="8">
+        <f t="shared" si="55"/>
+        <v>-26.799999999999983</v>
+      </c>
+      <c r="AE18" s="8"/>
+      <c r="AF18" s="8"/>
+      <c r="AG18" s="8"/>
+      <c r="AH18" s="8"/>
+      <c r="AJ18" s="8">
+        <f t="shared" ref="AJ18:AP18" si="56">AJ16-AJ17</f>
+        <v>-46.70000000000001</v>
+      </c>
+      <c r="AK18" s="8">
         <f t="shared" si="56"/>
-        <v>-47.700000000000017</v>
-      </c>
-      <c r="O18" s="8">
+        <v>-66.7</v>
+      </c>
+      <c r="AL18" s="8">
         <f t="shared" si="56"/>
-        <v>-38.4</v>
-      </c>
-      <c r="P18" s="8">
+        <v>-145.10000000000005</v>
+      </c>
+      <c r="AM18" s="8">
         <f t="shared" si="56"/>
-        <v>-49.400000000000006</v>
-      </c>
-      <c r="Q18" s="8">
+        <v>-175.30000000000013</v>
+      </c>
+      <c r="AN18" s="8">
         <f t="shared" si="56"/>
-        <v>-36</v>
-      </c>
-      <c r="R18" s="8">
+        <v>-116.80000000000003</v>
+      </c>
+      <c r="AO18" s="8">
         <f t="shared" si="56"/>
-        <v>-51.499999999999986</v>
-      </c>
-      <c r="S18" s="8">
+        <v>-79.499999999999901</v>
+      </c>
+      <c r="AP18" s="8">
         <f t="shared" si="56"/>
-        <v>-32.399999999999991</v>
-      </c>
-      <c r="T18" s="8">
-        <f t="shared" si="56"/>
-        <v>-31.999999999999996</v>
-      </c>
-      <c r="U18" s="8">
-        <f t="shared" si="56"/>
-        <v>-32.000000000000014</v>
-      </c>
-      <c r="V18" s="8">
-        <f t="shared" si="56"/>
-        <v>-20.399999999999995</v>
-      </c>
-      <c r="W18" s="8">
-        <f t="shared" si="56"/>
-        <v>-21.299999999999997</v>
-      </c>
-      <c r="X18" s="8">
-        <f t="shared" si="56"/>
-        <v>-22.899999999999988</v>
-      </c>
-      <c r="Y18" s="8">
-        <f t="shared" si="56"/>
-        <v>-13.700000000000012</v>
-      </c>
-      <c r="Z18" s="8">
-        <f t="shared" si="56"/>
-        <v>-21.600000000000026</v>
-      </c>
-      <c r="AA18" s="8">
-        <f t="shared" si="56"/>
-        <v>-7.7999999999999776</v>
-      </c>
-      <c r="AB18" s="8">
-        <f t="shared" si="56"/>
-        <v>-7.8000000000000229</v>
-      </c>
-      <c r="AC18" s="8">
-        <f t="shared" ref="AC18:AD18" si="57">AC16-AC17</f>
-        <v>-8.6000000000000227</v>
-      </c>
-      <c r="AD18" s="8">
+        <v>-51.000000000000206</v>
+      </c>
+      <c r="AQ18" s="8">
+        <f t="shared" ref="AQ18:AR18" si="57">AQ16-AQ17</f>
+        <v>-4.8485249999999889</v>
+      </c>
+      <c r="AR18" s="8">
         <f t="shared" si="57"/>
-        <v>-7.3834400000000073</v>
-      </c>
-      <c r="AF18" s="8">
-        <f t="shared" ref="AF18:AL18" si="58">AF16-AF17</f>
-        <v>-46.70000000000001</v>
-      </c>
-      <c r="AG18" s="8">
-        <f t="shared" si="58"/>
-        <v>-66.7</v>
-      </c>
-      <c r="AH18" s="8">
-        <f t="shared" si="58"/>
-        <v>-145.10000000000005</v>
-      </c>
-      <c r="AI18" s="8">
-        <f t="shared" si="58"/>
-        <v>-175.30000000000013</v>
-      </c>
-      <c r="AJ18" s="8">
-        <f t="shared" si="58"/>
-        <v>-116.80000000000003</v>
-      </c>
-      <c r="AK18" s="8">
-        <f t="shared" si="58"/>
-        <v>-79.499999999999901</v>
-      </c>
-      <c r="AL18" s="8">
-        <f t="shared" si="58"/>
-        <v>-31.583440000000088</v>
-      </c>
-      <c r="AM18" s="8">
-        <f t="shared" ref="AM18:AN18" si="59">AM16-AM17</f>
-        <v>5.3137836000000513</v>
-      </c>
-      <c r="AN18" s="8">
-        <f t="shared" si="59"/>
-        <v>25.107562439999924</v>
-      </c>
-      <c r="AO18" s="8">
-        <f t="shared" ref="AO18" si="60">AO16-AO17</f>
-        <v>44.332458500879952</v>
-      </c>
-      <c r="AP18" s="8">
-        <f t="shared" ref="AP18" si="61">AP16-AP17</f>
-        <v>48.898142041658417</v>
-      </c>
-      <c r="AQ18" s="8">
-        <f t="shared" ref="AQ18" si="62">AQ16-AQ17</f>
-        <v>53.633153186517632</v>
-      </c>
-      <c r="AR18" s="8">
-        <f t="shared" ref="AR18" si="63">AR16-AR17</f>
-        <v>58.542895334558864</v>
+        <v>17.133059249999942</v>
       </c>
       <c r="AS18" s="8">
-        <f t="shared" ref="AS18" si="64">AS16-AS17</f>
-        <v>63.632937222565687</v>
+        <f t="shared" ref="AS18" si="58">AS16-AS17</f>
+        <v>29.023365554999952</v>
       </c>
       <c r="AT18" s="8">
-        <f t="shared" ref="AT18" si="65">AT16-AT17</f>
-        <v>68.909017917492449</v>
+        <f t="shared" ref="AT18" si="59">AT16-AT17</f>
+        <v>33.416006656049923</v>
       </c>
       <c r="AU18" s="8">
-        <f t="shared" ref="AU18" si="66">AU16-AU17</f>
-        <v>74.377051959049467</v>
+        <f t="shared" ref="AU18" si="60">AU16-AU17</f>
+        <v>37.975646391475536</v>
       </c>
       <c r="AV18" s="8">
-        <f t="shared" ref="AV18" si="67">AV16-AV17</f>
-        <v>80.043134656893457</v>
-      </c>
-      <c r="AW18" s="1">
-        <f>AV18*(1+$AY$25)</f>
-        <v>79.242703310324515</v>
-      </c>
-      <c r="AX18" s="1">
-        <f t="shared" ref="AX18:DI18" si="68">AW18*(1+$AY$25)</f>
-        <v>78.450276277221263</v>
-      </c>
-      <c r="AY18" s="1">
-        <f t="shared" si="68"/>
-        <v>77.665773514449043</v>
-      </c>
-      <c r="AZ18" s="1">
-        <f t="shared" si="68"/>
-        <v>76.889115779304547</v>
+        <f t="shared" ref="AV18" si="61">AV16-AV17</f>
+        <v>42.707646914321224</v>
+      </c>
+      <c r="AW18" s="8">
+        <f t="shared" ref="AW18" si="62">AW16-AW17</f>
+        <v>47.617534764163317</v>
+      </c>
+      <c r="AX18" s="8">
+        <f t="shared" ref="AX18" si="63">AX16-AX17</f>
+        <v>52.711005833924794</v>
+      </c>
+      <c r="AY18" s="8">
+        <f t="shared" ref="AY18" si="64">AY16-AY17</f>
+        <v>57.993930486047404</v>
+      </c>
+      <c r="AZ18" s="8">
+        <f t="shared" ref="AZ18" si="65">AZ16-AZ17</f>
+        <v>63.472358822504951</v>
       </c>
       <c r="BA18" s="1">
-        <f t="shared" si="68"/>
-        <v>76.120224621511497</v>
+        <f>AZ18*(1+$BC$25)</f>
+        <v>62.837635234279901</v>
       </c>
       <c r="BB18" s="1">
-        <f t="shared" si="68"/>
-        <v>75.359022375296377</v>
+        <f t="shared" ref="BB18:DM18" si="66">BA18*(1+$BC$25)</f>
+        <v>62.209258881937103</v>
       </c>
       <c r="BC18" s="1">
-        <f t="shared" si="68"/>
-        <v>74.605432151543411</v>
+        <f t="shared" si="66"/>
+        <v>61.587166293117733</v>
       </c>
       <c r="BD18" s="1">
-        <f t="shared" si="68"/>
-        <v>73.859377830027981</v>
+        <f t="shared" si="66"/>
+        <v>60.971294630186556</v>
       </c>
       <c r="BE18" s="1">
-        <f t="shared" si="68"/>
-        <v>73.120784051727696</v>
+        <f t="shared" si="66"/>
+        <v>60.361581683884687</v>
       </c>
       <c r="BF18" s="1">
-        <f t="shared" si="68"/>
-        <v>72.389576211210425</v>
+        <f t="shared" si="66"/>
+        <v>59.75796586704584</v>
       </c>
       <c r="BG18" s="1">
-        <f t="shared" si="68"/>
-        <v>71.665680449098318</v>
+        <f t="shared" si="66"/>
+        <v>59.160386208375378</v>
       </c>
       <c r="BH18" s="1">
-        <f t="shared" si="68"/>
-        <v>70.949023644607337</v>
+        <f t="shared" si="66"/>
+        <v>58.568782346291627</v>
       </c>
       <c r="BI18" s="1">
-        <f t="shared" si="68"/>
-        <v>70.239533408161265</v>
+        <f t="shared" si="66"/>
+        <v>57.983094522828708</v>
       </c>
       <c r="BJ18" s="1">
-        <f t="shared" si="68"/>
-        <v>69.53713807407965</v>
+        <f t="shared" si="66"/>
+        <v>57.40326357760042</v>
       </c>
       <c r="BK18" s="1">
-        <f t="shared" si="68"/>
-        <v>68.841766693338855</v>
+        <f t="shared" si="66"/>
+        <v>56.829230941824413</v>
       </c>
       <c r="BL18" s="1">
-        <f t="shared" si="68"/>
-        <v>68.153349026405465</v>
+        <f t="shared" si="66"/>
+        <v>56.260938632406166</v>
       </c>
       <c r="BM18" s="1">
-        <f t="shared" si="68"/>
-        <v>67.471815536141406</v>
+        <f t="shared" si="66"/>
+        <v>55.698329246082103</v>
       </c>
       <c r="BN18" s="1">
-        <f t="shared" si="68"/>
-        <v>66.797097380779988</v>
+        <f t="shared" si="66"/>
+        <v>55.141345953621283</v>
       </c>
       <c r="BO18" s="1">
-        <f t="shared" si="68"/>
-        <v>66.12912640697219</v>
+        <f t="shared" si="66"/>
+        <v>54.589932494085069</v>
       </c>
       <c r="BP18" s="1">
-        <f t="shared" si="68"/>
-        <v>65.467835142902473</v>
+        <f t="shared" si="66"/>
+        <v>54.044033169144221</v>
       </c>
       <c r="BQ18" s="1">
-        <f t="shared" si="68"/>
-        <v>64.813156791473446</v>
+        <f t="shared" si="66"/>
+        <v>53.503592837452778</v>
       </c>
       <c r="BR18" s="1">
-        <f t="shared" si="68"/>
-        <v>64.165025223558715</v>
+        <f t="shared" si="66"/>
+        <v>52.968556909078252</v>
       </c>
       <c r="BS18" s="1">
-        <f t="shared" si="68"/>
-        <v>63.523374971323129</v>
+        <f t="shared" si="66"/>
+        <v>52.438871339987472</v>
       </c>
       <c r="BT18" s="1">
-        <f t="shared" si="68"/>
-        <v>62.888141221609899</v>
+        <f t="shared" si="66"/>
+        <v>51.914482626587599</v>
       </c>
       <c r="BU18" s="1">
-        <f t="shared" si="68"/>
-        <v>62.259259809393797</v>
+        <f t="shared" si="66"/>
+        <v>51.39533780032172</v>
       </c>
       <c r="BV18" s="1">
-        <f t="shared" si="68"/>
-        <v>61.636667211299859</v>
+        <f t="shared" si="66"/>
+        <v>50.881384422318504</v>
       </c>
       <c r="BW18" s="1">
-        <f t="shared" si="68"/>
-        <v>61.020300539186863</v>
+        <f t="shared" si="66"/>
+        <v>50.372570578095321</v>
       </c>
       <c r="BX18" s="1">
-        <f t="shared" si="68"/>
-        <v>60.410097533794996</v>
+        <f t="shared" si="66"/>
+        <v>49.868844872314369</v>
       </c>
       <c r="BY18" s="1">
-        <f t="shared" si="68"/>
-        <v>59.805996558457046</v>
+        <f t="shared" si="66"/>
+        <v>49.370156423591226</v>
       </c>
       <c r="BZ18" s="1">
-        <f t="shared" si="68"/>
-        <v>59.207936592872478</v>
+        <f t="shared" si="66"/>
+        <v>48.876454859355313</v>
       </c>
       <c r="CA18" s="1">
-        <f t="shared" si="68"/>
-        <v>58.615857226943753</v>
+        <f t="shared" si="66"/>
+        <v>48.387690310761762</v>
       </c>
       <c r="CB18" s="1">
-        <f t="shared" si="68"/>
-        <v>58.029698654674313</v>
+        <f t="shared" si="66"/>
+        <v>47.903813407654141</v>
       </c>
       <c r="CC18" s="1">
-        <f t="shared" si="68"/>
-        <v>57.449401668127571</v>
+        <f t="shared" si="66"/>
+        <v>47.424775273577602</v>
       </c>
       <c r="CD18" s="1">
-        <f t="shared" si="68"/>
-        <v>56.874907651446293</v>
+        <f t="shared" si="66"/>
+        <v>46.950527520841824</v>
       </c>
       <c r="CE18" s="1">
-        <f t="shared" si="68"/>
-        <v>56.306158574931828</v>
+        <f t="shared" si="66"/>
+        <v>46.481022245633405</v>
       </c>
       <c r="CF18" s="1">
-        <f t="shared" si="68"/>
-        <v>55.743096989182511</v>
+        <f t="shared" si="66"/>
+        <v>46.016212023177069</v>
       </c>
       <c r="CG18" s="1">
-        <f t="shared" si="68"/>
-        <v>55.185666019290686</v>
+        <f t="shared" si="66"/>
+        <v>45.556049902945297</v>
       </c>
       <c r="CH18" s="1">
-        <f t="shared" si="68"/>
-        <v>54.633809359097782</v>
+        <f t="shared" si="66"/>
+        <v>45.100489403915844</v>
       </c>
       <c r="CI18" s="1">
-        <f t="shared" si="68"/>
-        <v>54.087471265506807</v>
+        <f t="shared" si="66"/>
+        <v>44.649484509876686</v>
       </c>
       <c r="CJ18" s="1">
-        <f t="shared" si="68"/>
-        <v>53.546596552851739</v>
+        <f t="shared" si="66"/>
+        <v>44.202989664777917</v>
       </c>
       <c r="CK18" s="1">
-        <f t="shared" si="68"/>
-        <v>53.011130587323223</v>
+        <f t="shared" si="66"/>
+        <v>43.760959768130135</v>
       </c>
       <c r="CL18" s="1">
-        <f t="shared" si="68"/>
-        <v>52.481019281449989</v>
+        <f t="shared" si="66"/>
+        <v>43.323350170448833</v>
       </c>
       <c r="CM18" s="1">
-        <f t="shared" si="68"/>
-        <v>51.956209088635489</v>
+        <f t="shared" si="66"/>
+        <v>42.890116668744348</v>
       </c>
       <c r="CN18" s="1">
-        <f t="shared" si="68"/>
-        <v>51.436646997749136</v>
+        <f t="shared" si="66"/>
+        <v>42.461215502056902</v>
       </c>
       <c r="CO18" s="1">
-        <f t="shared" si="68"/>
-        <v>50.922280527771647</v>
+        <f t="shared" si="66"/>
+        <v>42.036603347036333</v>
       </c>
       <c r="CP18" s="1">
-        <f t="shared" si="68"/>
-        <v>50.413057722493932</v>
+        <f t="shared" si="66"/>
+        <v>41.616237313565968</v>
       </c>
       <c r="CQ18" s="1">
-        <f t="shared" si="68"/>
-        <v>49.90892714526899</v>
+        <f t="shared" si="66"/>
+        <v>41.200074940430305</v>
       </c>
       <c r="CR18" s="1">
-        <f t="shared" si="68"/>
-        <v>49.409837873816301</v>
+        <f t="shared" si="66"/>
+        <v>40.788074191025999</v>
       </c>
       <c r="CS18" s="1">
-        <f t="shared" si="68"/>
-        <v>48.915739495078135</v>
+        <f t="shared" si="66"/>
+        <v>40.380193449115737</v>
       </c>
       <c r="CT18" s="1">
-        <f t="shared" si="68"/>
-        <v>48.426582100127355</v>
+        <f t="shared" si="66"/>
+        <v>39.976391514624581</v>
       </c>
       <c r="CU18" s="1">
-        <f t="shared" si="68"/>
-        <v>47.942316279126082</v>
+        <f t="shared" si="66"/>
+        <v>39.576627599478336</v>
       </c>
       <c r="CV18" s="1">
-        <f t="shared" si="68"/>
-        <v>47.462893116334818</v>
+        <f t="shared" si="66"/>
+        <v>39.180861323483555</v>
       </c>
       <c r="CW18" s="1">
-        <f t="shared" si="68"/>
-        <v>46.988264185171467</v>
+        <f t="shared" si="66"/>
+        <v>38.789052710248718</v>
       </c>
       <c r="CX18" s="1">
-        <f t="shared" si="68"/>
-        <v>46.518381543319748</v>
+        <f t="shared" si="66"/>
+        <v>38.401162183146234</v>
       </c>
       <c r="CY18" s="1">
-        <f t="shared" si="68"/>
-        <v>46.053197727886548</v>
+        <f t="shared" si="66"/>
+        <v>38.017150561314772</v>
       </c>
       <c r="CZ18" s="1">
-        <f t="shared" si="68"/>
-        <v>45.592665750607679</v>
+        <f t="shared" si="66"/>
+        <v>37.636979055701623</v>
       </c>
       <c r="DA18" s="1">
-        <f t="shared" si="68"/>
-        <v>45.136739093101603</v>
+        <f t="shared" si="66"/>
+        <v>37.260609265144609</v>
       </c>
       <c r="DB18" s="1">
-        <f t="shared" si="68"/>
-        <v>44.685371702170585</v>
+        <f t="shared" si="66"/>
+        <v>36.888003172493164</v>
       </c>
       <c r="DC18" s="1">
-        <f t="shared" si="68"/>
-        <v>44.238517985148881</v>
+        <f t="shared" si="66"/>
+        <v>36.51912314076823</v>
       </c>
       <c r="DD18" s="1">
-        <f t="shared" si="68"/>
-        <v>43.79613280529739</v>
+        <f t="shared" si="66"/>
+        <v>36.153931909360544</v>
       </c>
       <c r="DE18" s="1">
-        <f t="shared" si="68"/>
-        <v>43.358171477244419</v>
+        <f t="shared" si="66"/>
+        <v>35.792392590266935</v>
       </c>
       <c r="DF18" s="1">
-        <f t="shared" si="68"/>
-        <v>42.924589762471975</v>
+        <f t="shared" si="66"/>
+        <v>35.434468664364267</v>
       </c>
       <c r="DG18" s="1">
-        <f t="shared" si="68"/>
-        <v>42.495343864847257</v>
+        <f t="shared" si="66"/>
+        <v>35.080123977720625</v>
       </c>
       <c r="DH18" s="1">
-        <f t="shared" si="68"/>
-        <v>42.070390426198784</v>
+        <f t="shared" si="66"/>
+        <v>34.72932273794342</v>
       </c>
       <c r="DI18" s="1">
-        <f t="shared" si="68"/>
-        <v>41.649686521936793</v>
+        <f t="shared" si="66"/>
+        <v>34.382029510563989</v>
       </c>
       <c r="DJ18" s="1">
-        <f t="shared" ref="DJ18:EN18" si="69">DI18*(1+$AY$25)</f>
-        <v>41.233189656717428</v>
+        <f t="shared" si="66"/>
+        <v>34.038209215458352</v>
       </c>
       <c r="DK18" s="1">
-        <f t="shared" si="69"/>
-        <v>40.820857760150254</v>
+        <f t="shared" si="66"/>
+        <v>33.697827123303767</v>
       </c>
       <c r="DL18" s="1">
-        <f t="shared" si="69"/>
-        <v>40.412649182548748</v>
+        <f t="shared" si="66"/>
+        <v>33.360848852070731</v>
       </c>
       <c r="DM18" s="1">
-        <f t="shared" si="69"/>
-        <v>40.008522690723261</v>
+        <f t="shared" si="66"/>
+        <v>33.027240363550021</v>
       </c>
       <c r="DN18" s="1">
-        <f t="shared" si="69"/>
-        <v>39.608437463816031</v>
+        <f t="shared" ref="DN18:ER18" si="67">DM18*(1+$BC$25)</f>
+        <v>32.696967959914524</v>
       </c>
       <c r="DO18" s="1">
-        <f t="shared" si="69"/>
-        <v>39.212353089177867</v>
+        <f t="shared" si="67"/>
+        <v>32.369998280315379</v>
       </c>
       <c r="DP18" s="1">
-        <f t="shared" si="69"/>
-        <v>38.820229558286087</v>
+        <f t="shared" si="67"/>
+        <v>32.046298297512223</v>
       </c>
       <c r="DQ18" s="1">
-        <f t="shared" si="69"/>
-        <v>38.432027262703222</v>
+        <f t="shared" si="67"/>
+        <v>31.7258353145371</v>
       </c>
       <c r="DR18" s="1">
-        <f t="shared" si="69"/>
-        <v>38.047706990076193</v>
+        <f t="shared" si="67"/>
+        <v>31.408576961391731</v>
       </c>
       <c r="DS18" s="1">
-        <f t="shared" si="69"/>
-        <v>37.66722992017543</v>
+        <f t="shared" si="67"/>
+        <v>31.094491191777813</v>
       </c>
       <c r="DT18" s="1">
-        <f t="shared" si="69"/>
-        <v>37.290557620973672</v>
+        <f t="shared" si="67"/>
+        <v>30.783546279860033</v>
       </c>
       <c r="DU18" s="1">
-        <f t="shared" si="69"/>
-        <v>36.917652044763933</v>
+        <f t="shared" si="67"/>
+        <v>30.475710817061433</v>
       </c>
       <c r="DV18" s="1">
-        <f t="shared" si="69"/>
-        <v>36.548475524316295</v>
+        <f t="shared" si="67"/>
+        <v>30.170953708890817</v>
       </c>
       <c r="DW18" s="1">
-        <f t="shared" si="69"/>
-        <v>36.182990769073129</v>
+        <f t="shared" si="67"/>
+        <v>29.86924417180191</v>
       </c>
       <c r="DX18" s="1">
-        <f t="shared" si="69"/>
-        <v>35.821160861382396</v>
+        <f t="shared" si="67"/>
+        <v>29.570551730083892</v>
       </c>
       <c r="DY18" s="1">
-        <f t="shared" si="69"/>
-        <v>35.462949252768574</v>
+        <f t="shared" si="67"/>
+        <v>29.274846212783054</v>
       </c>
       <c r="DZ18" s="1">
-        <f t="shared" si="69"/>
-        <v>35.108319760240889</v>
+        <f t="shared" si="67"/>
+        <v>28.982097750655221</v>
       </c>
       <c r="EA18" s="1">
-        <f t="shared" si="69"/>
-        <v>34.757236562638482</v>
+        <f t="shared" si="67"/>
+        <v>28.69227677314867</v>
       </c>
       <c r="EB18" s="1">
-        <f t="shared" si="69"/>
-        <v>34.409664197012098</v>
+        <f t="shared" si="67"/>
+        <v>28.405354005417184</v>
       </c>
       <c r="EC18" s="1">
-        <f t="shared" si="69"/>
-        <v>34.06556755504198</v>
+        <f t="shared" si="67"/>
+        <v>28.121300465363014</v>
       </c>
       <c r="ED18" s="1">
-        <f t="shared" si="69"/>
-        <v>33.724911879491557</v>
+        <f t="shared" si="67"/>
+        <v>27.840087460709384</v>
       </c>
       <c r="EE18" s="1">
-        <f t="shared" si="69"/>
-        <v>33.387662760696642</v>
+        <f t="shared" si="67"/>
+        <v>27.56168658610229</v>
       </c>
       <c r="EF18" s="1">
-        <f t="shared" si="69"/>
-        <v>33.053786133089673</v>
+        <f t="shared" si="67"/>
+        <v>27.286069720241269</v>
       </c>
       <c r="EG18" s="1">
-        <f t="shared" si="69"/>
-        <v>32.723248271758777</v>
+        <f t="shared" si="67"/>
+        <v>27.013209023038854</v>
       </c>
       <c r="EH18" s="1">
-        <f t="shared" si="69"/>
-        <v>32.396015789041186</v>
+        <f t="shared" si="67"/>
+        <v>26.743076932808464</v>
       </c>
       <c r="EI18" s="1">
-        <f t="shared" si="69"/>
-        <v>32.072055631150775</v>
+        <f t="shared" si="67"/>
+        <v>26.475646163480377</v>
       </c>
       <c r="EJ18" s="1">
-        <f t="shared" si="69"/>
-        <v>31.751335074839268</v>
+        <f t="shared" si="67"/>
+        <v>26.210889701845574</v>
       </c>
       <c r="EK18" s="1">
-        <f t="shared" si="69"/>
-        <v>31.433821724090876</v>
+        <f t="shared" si="67"/>
+        <v>25.948780804827116</v>
       </c>
       <c r="EL18" s="1">
-        <f t="shared" si="69"/>
-        <v>31.119483506849967</v>
+        <f t="shared" si="67"/>
+        <v>25.689292996778846</v>
       </c>
       <c r="EM18" s="1">
-        <f t="shared" si="69"/>
-        <v>30.808288671781469</v>
+        <f t="shared" si="67"/>
+        <v>25.432400066811056</v>
       </c>
       <c r="EN18" s="1">
-        <f t="shared" si="69"/>
-        <v>30.500205785063653</v>
+        <f t="shared" si="67"/>
+        <v>25.178076066142946</v>
+      </c>
+      <c r="EO18" s="1">
+        <f t="shared" si="67"/>
+        <v>24.926295305481517</v>
+      </c>
+      <c r="EP18" s="1">
+        <f t="shared" si="67"/>
+        <v>24.6770323524267</v>
+      </c>
+      <c r="EQ18" s="1">
+        <f t="shared" si="67"/>
+        <v>24.430262028902433</v>
+      </c>
+      <c r="ER18" s="1">
+        <f t="shared" si="67"/>
+        <v>24.18595940861341</v>
       </c>
     </row>
-    <row r="19" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>2</v>
       </c>
@@ -3330,21 +3399,12 @@
         <v>164.6</v>
       </c>
       <c r="AD19" s="5">
-        <f>164.6</f>
-        <v>164.6</v>
-      </c>
-      <c r="AF19" s="5">
-        <v>163.69999999999999</v>
-      </c>
-      <c r="AG19" s="5">
-        <v>163.69999999999999</v>
-      </c>
-      <c r="AH19" s="5">
-        <v>163.69999999999999</v>
-      </c>
-      <c r="AI19" s="5">
-        <v>163.69999999999999</v>
-      </c>
+        <v>167.2</v>
+      </c>
+      <c r="AE19" s="5"/>
+      <c r="AF19" s="5"/>
+      <c r="AG19" s="5"/>
+      <c r="AH19" s="5"/>
       <c r="AJ19" s="5">
         <v>163.69999999999999</v>
       </c>
@@ -3352,205 +3412,214 @@
         <v>163.69999999999999</v>
       </c>
       <c r="AL19" s="5">
-        <f t="shared" ref="AL19:AV19" si="70">164.6</f>
-        <v>164.6</v>
+        <v>163.69999999999999</v>
       </c>
       <c r="AM19" s="5">
-        <f t="shared" si="70"/>
-        <v>164.6</v>
+        <v>163.69999999999999</v>
       </c>
       <c r="AN19" s="5">
-        <f t="shared" si="70"/>
-        <v>164.6</v>
+        <v>163.69999999999999</v>
       </c>
       <c r="AO19" s="5">
-        <f t="shared" si="70"/>
-        <v>164.6</v>
+        <v>163.69999999999999</v>
       </c>
       <c r="AP19" s="5">
-        <f t="shared" si="70"/>
-        <v>164.6</v>
+        <v>167.2</v>
       </c>
       <c r="AQ19" s="5">
-        <f t="shared" si="70"/>
-        <v>164.6</v>
+        <v>167.2</v>
       </c>
       <c r="AR19" s="5">
-        <f t="shared" si="70"/>
-        <v>164.6</v>
+        <v>167.2</v>
       </c>
       <c r="AS19" s="5">
-        <f t="shared" si="70"/>
-        <v>164.6</v>
+        <v>167.2</v>
       </c>
       <c r="AT19" s="5">
-        <f t="shared" si="70"/>
-        <v>164.6</v>
+        <v>167.2</v>
       </c>
       <c r="AU19" s="5">
-        <f t="shared" si="70"/>
-        <v>164.6</v>
+        <v>167.2</v>
       </c>
       <c r="AV19" s="5">
-        <f t="shared" si="70"/>
-        <v>164.6</v>
+        <v>167.2</v>
+      </c>
+      <c r="AW19" s="5">
+        <v>167.2</v>
+      </c>
+      <c r="AX19" s="5">
+        <v>167.2</v>
+      </c>
+      <c r="AY19" s="5">
+        <v>167.2</v>
+      </c>
+      <c r="AZ19" s="5">
+        <v>167.2</v>
       </c>
     </row>
-    <row r="20" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>26</v>
       </c>
       <c r="M20" s="7">
-        <f t="shared" ref="M20:AB20" si="71">M18/M19</f>
+        <f t="shared" ref="M20:AB20" si="68">M18/M19</f>
         <v>-0.19792302993280386</v>
       </c>
       <c r="N20" s="7">
+        <f t="shared" si="68"/>
+        <v>-0.29138668295662812</v>
+      </c>
+      <c r="O20" s="7">
+        <f t="shared" si="68"/>
+        <v>-0.23457544288332316</v>
+      </c>
+      <c r="P20" s="7">
+        <f t="shared" si="68"/>
+        <v>-0.30177153329260847</v>
+      </c>
+      <c r="Q20" s="7">
+        <f t="shared" si="68"/>
+        <v>-0.21991447770311548</v>
+      </c>
+      <c r="R20" s="7">
+        <f t="shared" si="68"/>
+        <v>-0.31459987782529009</v>
+      </c>
+      <c r="S20" s="7">
+        <f t="shared" si="68"/>
+        <v>-0.19792302993280386</v>
+      </c>
+      <c r="T20" s="7">
+        <f t="shared" si="68"/>
+        <v>-0.19547953573610261</v>
+      </c>
+      <c r="U20" s="7">
+        <f t="shared" si="68"/>
+        <v>-0.19547953573610272</v>
+      </c>
+      <c r="V20" s="7">
+        <f t="shared" si="68"/>
+        <v>-0.12461820403176541</v>
+      </c>
+      <c r="W20" s="7">
+        <f t="shared" si="68"/>
+        <v>-0.1301160659743433</v>
+      </c>
+      <c r="X20" s="7">
+        <f t="shared" si="68"/>
+        <v>-0.13989004276114839</v>
+      </c>
+      <c r="Y20" s="7">
+        <f t="shared" si="68"/>
+        <v>-8.368967623701902E-2</v>
+      </c>
+      <c r="Z20" s="7">
+        <f t="shared" si="68"/>
+        <v>-0.13194868662186945</v>
+      </c>
+      <c r="AA20" s="7">
+        <f t="shared" si="68"/>
+        <v>-4.7648136835674884E-2</v>
+      </c>
+      <c r="AB20" s="7">
+        <f t="shared" si="68"/>
+        <v>-4.7648136835675162E-2</v>
+      </c>
+      <c r="AC20" s="7">
+        <f t="shared" ref="AC20:AD20" si="69">AC18/AC19</f>
+        <v>-5.224787363304996E-2</v>
+      </c>
+      <c r="AD20" s="7">
+        <f t="shared" si="69"/>
+        <v>-0.16028708133971284</v>
+      </c>
+      <c r="AE20" s="7"/>
+      <c r="AF20" s="7"/>
+      <c r="AG20" s="7"/>
+      <c r="AH20" s="7"/>
+      <c r="AJ20" s="7">
+        <f t="shared" ref="AJ20:AP20" si="70">AJ18/AJ19</f>
+        <v>-0.28527794746487484</v>
+      </c>
+      <c r="AK20" s="7">
+        <f t="shared" si="70"/>
+        <v>-0.40745265729993896</v>
+      </c>
+      <c r="AL20" s="7">
+        <f t="shared" si="70"/>
+        <v>-0.88637751985339075</v>
+      </c>
+      <c r="AM20" s="7">
+        <f t="shared" si="70"/>
+        <v>-1.0708613317043381</v>
+      </c>
+      <c r="AN20" s="7">
+        <f t="shared" si="70"/>
+        <v>-0.71350030543677478</v>
+      </c>
+      <c r="AO20" s="7">
+        <f t="shared" si="70"/>
+        <v>-0.4856444715943794</v>
+      </c>
+      <c r="AP20" s="7">
+        <f t="shared" si="70"/>
+        <v>-0.30502392344497731</v>
+      </c>
+      <c r="AQ20" s="7">
+        <f t="shared" ref="AQ20:AR20" si="71">AQ18/AQ19</f>
+        <v>-2.8998355263157829E-2</v>
+      </c>
+      <c r="AR20" s="7">
         <f t="shared" si="71"/>
-        <v>-0.29138668295662812</v>
-      </c>
-      <c r="O20" s="7">
-        <f t="shared" si="71"/>
-        <v>-0.23457544288332316</v>
-      </c>
-      <c r="P20" s="7">
-        <f t="shared" si="71"/>
-        <v>-0.30177153329260847</v>
-      </c>
-      <c r="Q20" s="7">
-        <f t="shared" si="71"/>
-        <v>-0.21991447770311548</v>
-      </c>
-      <c r="R20" s="7">
-        <f t="shared" si="71"/>
-        <v>-0.31459987782529009</v>
-      </c>
-      <c r="S20" s="7">
-        <f t="shared" si="71"/>
-        <v>-0.19792302993280386</v>
-      </c>
-      <c r="T20" s="7">
-        <f t="shared" si="71"/>
-        <v>-0.19547953573610261</v>
-      </c>
-      <c r="U20" s="7">
-        <f t="shared" si="71"/>
-        <v>-0.19547953573610272</v>
-      </c>
-      <c r="V20" s="7">
-        <f t="shared" si="71"/>
-        <v>-0.12461820403176541</v>
-      </c>
-      <c r="W20" s="7">
-        <f t="shared" si="71"/>
-        <v>-0.1301160659743433</v>
-      </c>
-      <c r="X20" s="7">
-        <f t="shared" si="71"/>
-        <v>-0.13989004276114839</v>
-      </c>
-      <c r="Y20" s="7">
-        <f t="shared" si="71"/>
-        <v>-8.368967623701902E-2</v>
-      </c>
-      <c r="Z20" s="7">
-        <f t="shared" si="71"/>
-        <v>-0.13194868662186945</v>
-      </c>
-      <c r="AA20" s="7">
-        <f t="shared" si="71"/>
-        <v>-4.7648136835674884E-2</v>
-      </c>
-      <c r="AB20" s="7">
-        <f t="shared" si="71"/>
-        <v>-4.7648136835675162E-2</v>
-      </c>
-      <c r="AC20" s="7">
-        <f t="shared" ref="AC20:AD20" si="72">AC18/AC19</f>
-        <v>-5.224787363304996E-2</v>
-      </c>
-      <c r="AD20" s="7">
-        <f t="shared" si="72"/>
-        <v>-4.4856865127582066E-2</v>
-      </c>
-      <c r="AF20" s="7">
-        <f t="shared" ref="AF20:AL20" si="73">AF18/AF19</f>
-        <v>-0.28527794746487484</v>
-      </c>
-      <c r="AG20" s="7">
-        <f t="shared" si="73"/>
-        <v>-0.40745265729993896</v>
-      </c>
-      <c r="AH20" s="7">
-        <f t="shared" si="73"/>
-        <v>-0.88637751985339075</v>
-      </c>
-      <c r="AI20" s="7">
-        <f t="shared" si="73"/>
-        <v>-1.0708613317043381</v>
-      </c>
-      <c r="AJ20" s="7">
-        <f t="shared" si="73"/>
-        <v>-0.71350030543677478</v>
-      </c>
-      <c r="AK20" s="7">
-        <f t="shared" si="73"/>
-        <v>-0.4856444715943794</v>
-      </c>
-      <c r="AL20" s="7">
-        <f t="shared" si="73"/>
-        <v>-0.19187995139732739</v>
-      </c>
-      <c r="AM20" s="7">
-        <f t="shared" ref="AM20:AN20" si="74">AM18/AM19</f>
-        <v>3.2283010935601771E-2</v>
-      </c>
-      <c r="AN20" s="7">
-        <f t="shared" si="74"/>
-        <v>0.15253683134872373</v>
-      </c>
-      <c r="AO20" s="7">
-        <f t="shared" ref="AO20" si="75">AO18/AO19</f>
-        <v>0.26933449879027921</v>
-      </c>
-      <c r="AP20" s="7">
-        <f t="shared" ref="AP20" si="76">AP18/AP19</f>
-        <v>0.29707255189342902</v>
-      </c>
-      <c r="AQ20" s="7">
-        <f t="shared" ref="AQ20" si="77">AQ18/AQ19</f>
-        <v>0.32583932677106703</v>
-      </c>
-      <c r="AR20" s="7">
-        <f t="shared" ref="AR20" si="78">AR18/AR19</f>
-        <v>0.35566765087824342</v>
+        <v>0.10247045005980827</v>
       </c>
       <c r="AS20" s="7">
-        <f t="shared" ref="AS20" si="79">AS18/AS19</f>
-        <v>0.38659135615167489</v>
+        <f t="shared" ref="AS20" si="72">AS18/AS19</f>
+        <v>0.17358472221889926</v>
       </c>
       <c r="AT20" s="7">
-        <f t="shared" ref="AT20" si="80">AT18/AT19</f>
-        <v>0.41864530934078037</v>
+        <f t="shared" ref="AT20" si="73">AT18/AT19</f>
+        <v>0.19985649913905457</v>
       </c>
       <c r="AU20" s="7">
-        <f t="shared" ref="AU20" si="81">AU18/AU19</f>
-        <v>0.45186544325060429</v>
+        <f t="shared" ref="AU20" si="74">AU18/AU19</f>
+        <v>0.22712707171935131</v>
       </c>
       <c r="AV20" s="7">
-        <f t="shared" ref="AV20" si="82">AV18/AV19</f>
-        <v>0.48628878892401861</v>
+        <f t="shared" ref="AV20" si="75">AV18/AV19</f>
+        <v>0.25542851025311736</v>
+      </c>
+      <c r="AW20" s="7">
+        <f t="shared" ref="AW20" si="76">AW18/AW19</f>
+        <v>0.28479386820671843</v>
+      </c>
+      <c r="AX20" s="7">
+        <f t="shared" ref="AX20" si="77">AX18/AX19</f>
+        <v>0.31525721192538753</v>
+      </c>
+      <c r="AY20" s="7">
+        <f t="shared" ref="AY20" si="78">AY18/AY19</f>
+        <v>0.34685365123234096</v>
+      </c>
+      <c r="AZ20" s="7">
+        <f t="shared" ref="AZ20" si="79">AZ18/AZ19</f>
+        <v>0.37961937094799614</v>
       </c>
     </row>
-    <row r="22" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>71</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" ref="AC22:AD24" si="83">AC3/Y3-1</f>
+        <f t="shared" ref="AC22:AD24" si="80">AC3/Y3-1</f>
         <v>0.17901234567901225</v>
       </c>
+      <c r="AD22" s="9">
+        <f t="shared" si="80"/>
+        <v>0.17261904761904767</v>
+      </c>
     </row>
-    <row r="24" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>55</v>
       </c>
@@ -3559,47 +3628,47 @@
       <c r="O24" s="9"/>
       <c r="P24" s="9"/>
       <c r="Q24" s="9">
-        <f t="shared" ref="Q24:AA24" si="84">Q5/M5-1</f>
+        <f t="shared" ref="Q24:AA24" si="81">Q5/M5-1</f>
         <v>0.2411282984531391</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>0.23652173913043462</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>0.2259136212624584</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>0.23157051282051277</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>0.21334310850439886</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>0.18776371308016881</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>0.14566395663956633</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>0.10800260247234883</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>6.4048338368579927E-2</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>6.0982830076968586E-2</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>6.0319337670017736E-2</v>
       </c>
       <c r="AB24" s="9">
@@ -3607,141 +3676,145 @@
         <v>9.8649442160892331E-2</v>
       </c>
       <c r="AC24" s="9">
+        <f t="shared" si="80"/>
+        <v>0.10278250993753546</v>
+      </c>
+      <c r="AD24" s="9">
+        <f t="shared" si="80"/>
+        <v>9.8772321428571619E-2</v>
+      </c>
+      <c r="AE24" s="9"/>
+      <c r="AF24" s="9"/>
+      <c r="AG24" s="9"/>
+      <c r="AH24" s="9"/>
+      <c r="AJ24" s="9"/>
+      <c r="AK24" s="9">
+        <f t="shared" ref="AK24:AN24" si="82">AK5/AJ5-1</f>
+        <v>0.5916485900216919</v>
+      </c>
+      <c r="AL24" s="9">
+        <f t="shared" si="82"/>
+        <v>0.41499148211243608</v>
+      </c>
+      <c r="AM24" s="9">
+        <f t="shared" si="82"/>
+        <v>0.26125692270647716</v>
+      </c>
+      <c r="AN24" s="9">
+        <f t="shared" si="82"/>
+        <v>0.21363115693012591</v>
+      </c>
+      <c r="AO24" s="9">
+        <f>AO5/AN5-1</f>
+        <v>9.2811074406166538E-2</v>
+      </c>
+      <c r="AP24" s="9">
+        <f t="shared" ref="AP24:AZ24" si="83">AP5/AO5-1</f>
+        <v>9.0398733266157771E-2</v>
+      </c>
+      <c r="AQ24" s="9">
         <f t="shared" si="83"/>
-        <v>0.10278250993753546</v>
-      </c>
-      <c r="AD24" s="9">
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="AR24" s="9">
         <f t="shared" si="83"/>
-        <v>8.0000000000000071E-2</v>
-      </c>
-      <c r="AF24" s="9"/>
-      <c r="AG24" s="9">
-        <f t="shared" ref="AG24:AJ24" si="85">AG5/AF5-1</f>
-        <v>0.5916485900216919</v>
-      </c>
-      <c r="AH24" s="9">
-        <f t="shared" si="85"/>
-        <v>0.41499148211243608</v>
-      </c>
-      <c r="AI24" s="9">
-        <f t="shared" si="85"/>
-        <v>0.26125692270647716</v>
-      </c>
-      <c r="AJ24" s="9">
-        <f t="shared" si="85"/>
-        <v>0.21363115693012591</v>
-      </c>
-      <c r="AK24" s="9">
-        <f>AK5/AJ5-1</f>
-        <v>9.2811074406166538E-2</v>
-      </c>
-      <c r="AL24" s="9">
-        <f t="shared" ref="AL24:AV24" si="86">AL5/AK5-1</f>
-        <v>8.5556355261263706E-2</v>
-      </c>
-      <c r="AM24" s="9">
-        <f t="shared" si="86"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AN24" s="9">
-        <f t="shared" si="86"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="AO24" s="9">
-        <f t="shared" si="86"/>
+      <c r="AS24" s="9">
+        <f t="shared" si="83"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AP24" s="9">
-        <f t="shared" si="86"/>
+      <c r="AT24" s="9">
+        <f t="shared" si="83"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AQ24" s="9">
-        <f t="shared" si="86"/>
+      <c r="AU24" s="9">
+        <f t="shared" si="83"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AR24" s="9">
-        <f t="shared" si="86"/>
+      <c r="AV24" s="9">
+        <f t="shared" si="83"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AS24" s="9">
-        <f t="shared" si="86"/>
+      <c r="AW24" s="9">
+        <f t="shared" si="83"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AT24" s="9">
-        <f t="shared" si="86"/>
+      <c r="AX24" s="9">
+        <f t="shared" si="83"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AU24" s="9">
-        <f t="shared" si="86"/>
+      <c r="AY24" s="9">
+        <f t="shared" si="83"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AV24" s="9">
-        <f t="shared" si="86"/>
+      <c r="AZ24" s="9">
+        <f t="shared" si="83"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
-    <row r="25" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>54</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" ref="M25:AA25" si="87">M7/M5</f>
+        <f t="shared" ref="M25:AA25" si="84">M7/M5</f>
         <v>0.61601455868971788</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>0.62</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>0.64451827242524917</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>0.6282051282051283</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>0.64222873900293254</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>0.61814345991561181</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>0.52439024390243894</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>0.51854261548471048</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>0.50271903323262845</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>0.52871521610420369</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>0.52927261975162632</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>0.52965355255431601</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>0.54628052243043723</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>0.5329241071428571</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="84"/>
         <v>0.54601226993865026</v>
       </c>
       <c r="AB25" s="9">
@@ -3749,89 +3822,93 @@
         <v>0.54890432923570276</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" ref="AC25:AD25" si="88">AC7/AC5</f>
+        <f t="shared" ref="AC25:AD25" si="85">AC7/AC5</f>
         <v>0.54582904222451079</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="88"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="AF25" s="9">
-        <f t="shared" ref="AF25:AJ25" si="89">AF7/AF5</f>
+        <f t="shared" si="85"/>
+        <v>0.54240731335703407</v>
+      </c>
+      <c r="AE25" s="9"/>
+      <c r="AF25" s="9"/>
+      <c r="AG25" s="9"/>
+      <c r="AH25" s="9"/>
+      <c r="AJ25" s="9">
+        <f t="shared" ref="AJ25:AN25" si="86">AJ7/AJ5</f>
         <v>0.51409978308026039</v>
       </c>
-      <c r="AG25" s="9">
-        <f t="shared" si="89"/>
+      <c r="AK25" s="9">
+        <f t="shared" si="86"/>
         <v>0.52708688245315161</v>
       </c>
-      <c r="AH25" s="9">
-        <f t="shared" si="89"/>
+      <c r="AL25" s="9">
+        <f t="shared" si="86"/>
         <v>0.6007705273296412</v>
       </c>
-      <c r="AI25" s="9">
-        <f t="shared" si="89"/>
+      <c r="AM25" s="9">
+        <f t="shared" si="86"/>
         <v>0.63287514318442151</v>
       </c>
-      <c r="AJ25" s="9">
-        <f t="shared" si="89"/>
+      <c r="AN25" s="9">
+        <f t="shared" si="86"/>
         <v>0.51848356142834662</v>
       </c>
-      <c r="AK25" s="9">
-        <f t="shared" ref="AK25:AV25" si="90">AK7/AK5</f>
+      <c r="AO25" s="9">
+        <f t="shared" ref="AO25:AZ25" si="87">AO7/AO5</f>
         <v>0.53461926011227867</v>
       </c>
-      <c r="AL25" s="9">
-        <f t="shared" si="90"/>
-        <v>0.54770598406653448</v>
-      </c>
-      <c r="AM25" s="9">
-        <f t="shared" si="90"/>
+      <c r="AP25" s="9">
+        <f t="shared" si="87"/>
+        <v>0.54574257425742567</v>
+      </c>
+      <c r="AQ25" s="9">
+        <f t="shared" si="87"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="AN25" s="9">
-        <f t="shared" si="90"/>
+      <c r="AR25" s="9">
+        <f t="shared" si="87"/>
         <v>0.56999999999999995</v>
       </c>
-      <c r="AO25" s="9">
-        <f t="shared" si="90"/>
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="AP25" s="9">
-        <f t="shared" si="90"/>
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="AQ25" s="9">
-        <f t="shared" si="90"/>
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="AR25" s="9">
-        <f t="shared" si="90"/>
-        <v>0.57999999999999996</v>
-      </c>
       <c r="AS25" s="9">
-        <f t="shared" si="90"/>
-        <v>0.57999999999999996</v>
+        <f t="shared" si="87"/>
+        <v>0.56999999999999995</v>
       </c>
       <c r="AT25" s="9">
-        <f t="shared" si="90"/>
-        <v>0.57999999999999996</v>
+        <f t="shared" si="87"/>
+        <v>0.56999999999999995</v>
       </c>
       <c r="AU25" s="9">
-        <f t="shared" si="90"/>
-        <v>0.57999999999999996</v>
+        <f t="shared" si="87"/>
+        <v>0.56999999999999995</v>
       </c>
       <c r="AV25" s="9">
-        <f t="shared" si="90"/>
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="AX25" t="s">
+        <f t="shared" si="87"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AW25" s="9">
+        <f t="shared" si="87"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AX25" s="9">
+        <f t="shared" si="87"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AY25" s="9">
+        <f t="shared" si="87"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AZ25" s="9">
+        <f t="shared" si="87"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="BB25" t="s">
         <v>61</v>
       </c>
-      <c r="AY25" s="9">
+      <c r="BC25" s="9">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="26" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>56</v>
       </c>
@@ -3840,47 +3917,47 @@
       <c r="O26" s="9"/>
       <c r="P26" s="9"/>
       <c r="Q26" s="9">
-        <f t="shared" ref="Q26:AA26" si="91">Q8/M8-1</f>
+        <f t="shared" ref="Q26:AA26" si="88">Q8/M8-1</f>
         <v>0.16224188790560468</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="88"/>
         <v>0.11749347258485643</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="88"/>
         <v>0.15263157894736845</v>
       </c>
       <c r="T26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="88"/>
         <v>-8.0178173719376411E-2</v>
       </c>
       <c r="U26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="88"/>
         <v>-4.5685279187817174E-2</v>
       </c>
       <c r="V26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="88"/>
         <v>-0.12616822429906538</v>
       </c>
       <c r="W26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="88"/>
         <v>-0.2100456621004565</v>
       </c>
       <c r="X26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="88"/>
         <v>-0.18401937046004835</v>
       </c>
       <c r="Y26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="88"/>
         <v>-0.15957446808510634</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="88"/>
         <v>-0.14171122994652396</v>
       </c>
       <c r="AA26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="88"/>
         <v>-0.14739884393063585</v>
       </c>
       <c r="AB26" s="9">
@@ -3888,147 +3965,151 @@
         <v>-0.13056379821958464</v>
       </c>
       <c r="AC26" s="9">
-        <f t="shared" ref="AC26:AD26" si="92">AC8/Y8-1</f>
+        <f t="shared" ref="AC26:AD26" si="89">AC8/Y8-1</f>
         <v>-5.0632911392405111E-2</v>
       </c>
       <c r="AD26" s="9">
-        <f t="shared" si="92"/>
-        <v>-4.0000000000000036E-2</v>
-      </c>
+        <f t="shared" si="89"/>
+        <v>2.1806853582554409E-2</v>
+      </c>
+      <c r="AE26" s="9"/>
       <c r="AF26" s="9"/>
-      <c r="AG26" s="9">
-        <f t="shared" ref="AG26:AJ26" si="93">AG8/AF8-1</f>
+      <c r="AG26" s="9"/>
+      <c r="AH26" s="9"/>
+      <c r="AJ26" s="9"/>
+      <c r="AK26" s="9">
+        <f t="shared" ref="AK26:AN26" si="90">AK8/AJ8-1</f>
         <v>0.36170212765957444</v>
       </c>
-      <c r="AH26" s="9">
-        <f t="shared" si="93"/>
+      <c r="AL26" s="9">
+        <f t="shared" si="90"/>
         <v>0.76302083333333348</v>
       </c>
-      <c r="AI26" s="9">
-        <f t="shared" si="93"/>
+      <c r="AM26" s="9">
+        <f t="shared" si="90"/>
         <v>0.21935007385524385</v>
       </c>
-      <c r="AJ26" s="9">
-        <f t="shared" si="93"/>
+      <c r="AN26" s="9">
+        <f t="shared" si="90"/>
         <v>-3.0284675953967444E-2</v>
       </c>
-      <c r="AK26" s="9">
-        <f>AK8/AJ8-1</f>
+      <c r="AO26" s="9">
+        <f>AO8/AN8-1</f>
         <v>-0.1755153029356652</v>
       </c>
-      <c r="AL26" s="9">
-        <f t="shared" ref="AL26:AV26" si="94">AL8/AK8-1</f>
-        <v>-9.3818181818181801E-2</v>
-      </c>
-      <c r="AM26" s="9">
-        <f t="shared" si="94"/>
+      <c r="AP26" s="9">
+        <f t="shared" ref="AP26:AZ26" si="91">AP8/AO8-1</f>
+        <v>-7.8787878787878851E-2</v>
+      </c>
+      <c r="AQ26" s="9">
+        <f t="shared" si="91"/>
         <v>-6.0000000000000053E-2</v>
       </c>
-      <c r="AN26" s="9">
-        <f t="shared" si="94"/>
+      <c r="AR26" s="9">
+        <f t="shared" si="91"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AO26" s="9">
-        <f t="shared" si="94"/>
+      <c r="AS26" s="9">
+        <f t="shared" si="91"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AP26" s="9">
-        <f t="shared" si="94"/>
+      <c r="AT26" s="9">
+        <f t="shared" si="91"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AQ26" s="9">
-        <f t="shared" si="94"/>
+      <c r="AU26" s="9">
+        <f t="shared" si="91"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AR26" s="9">
-        <f t="shared" si="94"/>
+      <c r="AV26" s="9">
+        <f t="shared" si="91"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AS26" s="9">
-        <f t="shared" si="94"/>
+      <c r="AW26" s="9">
+        <f t="shared" si="91"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AT26" s="9">
-        <f t="shared" si="94"/>
+      <c r="AX26" s="9">
+        <f t="shared" si="91"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AU26" s="9">
-        <f t="shared" si="94"/>
+      <c r="AY26" s="9">
+        <f t="shared" si="91"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AV26" s="9">
-        <f t="shared" si="94"/>
+      <c r="AZ26" s="9">
+        <f t="shared" si="91"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AX26" t="s">
+      <c r="BB26" t="s">
         <v>62</v>
       </c>
-      <c r="AY26" s="9">
+      <c r="BC26" s="9">
         <v>0.1</v>
       </c>
     </row>
-    <row r="27" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>57</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" ref="M27:AA27" si="95">M9/M5</f>
+        <f t="shared" ref="M27:AA27" si="92">M9/M5</f>
         <v>0.41219290263876246</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="92"/>
         <v>0.50086956521739134</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="92"/>
         <v>0.42940199335548174</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="92"/>
         <v>0.44551282051282054</v>
       </c>
       <c r="Q27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="92"/>
         <v>0.42888563049853373</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="92"/>
         <v>0.43530239099859358</v>
       </c>
       <c r="S27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="92"/>
         <v>0.35840108401084009</v>
       </c>
       <c r="T27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="92"/>
         <v>0.33832140533506833</v>
       </c>
       <c r="U27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="92"/>
         <v>0.36132930513595163</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="92"/>
         <v>0.34399052693901716</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="92"/>
         <v>0.34062684801892373</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="92"/>
         <v>0.34116265413975339</v>
       </c>
       <c r="Y27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="92"/>
         <v>0.3350369108461102</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="92"/>
         <v>0.33593750000000006</v>
       </c>
       <c r="AA27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="92"/>
         <v>0.316787506971556</v>
       </c>
       <c r="AB27" s="9">
@@ -4036,90 +4117,94 @@
         <v>0.33992517370390168</v>
       </c>
       <c r="AC27" s="9">
-        <f t="shared" ref="AC27:AD27" si="96">AC9/AC5</f>
+        <f t="shared" ref="AC27:AD27" si="93">AC9/AC5</f>
         <v>0.34706488156539655</v>
       </c>
       <c r="AD27" s="9">
-        <f t="shared" si="96"/>
-        <v>0.34000000000000008</v>
-      </c>
-      <c r="AF27" s="9">
-        <f t="shared" ref="AF27:AJ27" si="97">AF9/AF5</f>
+        <f t="shared" si="93"/>
+        <v>0.34484509903504318</v>
+      </c>
+      <c r="AE27" s="9"/>
+      <c r="AF27" s="9"/>
+      <c r="AG27" s="9"/>
+      <c r="AH27" s="9"/>
+      <c r="AJ27" s="9">
+        <f t="shared" ref="AJ27:AN27" si="94">AJ9/AJ5</f>
         <v>0.30911062906724512</v>
       </c>
-      <c r="AG27" s="9">
-        <f t="shared" si="97"/>
+      <c r="AK27" s="9">
+        <f t="shared" si="94"/>
         <v>0.36524701873935267</v>
       </c>
-      <c r="AH27" s="9">
-        <f t="shared" si="97"/>
+      <c r="AL27" s="9">
+        <f t="shared" si="94"/>
         <v>0.43173609438959792</v>
       </c>
-      <c r="AI27" s="9">
-        <f t="shared" si="97"/>
+      <c r="AM27" s="9">
+        <f t="shared" si="94"/>
         <v>0.43470790378006879</v>
       </c>
-      <c r="AJ27" s="9">
-        <f t="shared" si="97"/>
+      <c r="AN27" s="9">
+        <f t="shared" si="94"/>
         <v>0.35047978606260816</v>
       </c>
-      <c r="AK27" s="9">
-        <f t="shared" ref="AK27:AV27" si="98">AK9/AK5</f>
+      <c r="AO27" s="9">
+        <f t="shared" ref="AO27:AZ27" si="95">AO9/AO5</f>
         <v>0.33813156758312934</v>
       </c>
-      <c r="AL27" s="9">
-        <f t="shared" si="98"/>
-        <v>0.33628183775870668</v>
-      </c>
-      <c r="AM27" s="9">
-        <f t="shared" si="98"/>
+      <c r="AP27" s="9">
+        <f t="shared" si="95"/>
+        <v>0.33755775577557762</v>
+      </c>
+      <c r="AQ27" s="9">
+        <f t="shared" si="95"/>
         <v>0.33</v>
       </c>
-      <c r="AN27" s="9">
-        <f t="shared" si="98"/>
+      <c r="AR27" s="9">
+        <f t="shared" si="95"/>
         <v>0.32000000000000006</v>
       </c>
-      <c r="AO27" s="9">
-        <f t="shared" si="98"/>
+      <c r="AS27" s="9">
+        <f t="shared" si="95"/>
         <v>0.31000000000000005</v>
       </c>
-      <c r="AP27" s="9">
-        <f t="shared" si="98"/>
+      <c r="AT27" s="9">
+        <f t="shared" si="95"/>
         <v>0.31</v>
       </c>
-      <c r="AQ27" s="9">
-        <f t="shared" si="98"/>
+      <c r="AU27" s="9">
+        <f t="shared" si="95"/>
         <v>0.31</v>
       </c>
-      <c r="AR27" s="9">
-        <f t="shared" si="98"/>
+      <c r="AV27" s="9">
+        <f t="shared" si="95"/>
         <v>0.31</v>
       </c>
-      <c r="AS27" s="9">
-        <f t="shared" si="98"/>
+      <c r="AW27" s="9">
+        <f t="shared" si="95"/>
         <v>0.31</v>
       </c>
-      <c r="AT27" s="9">
-        <f t="shared" si="98"/>
+      <c r="AX27" s="9">
+        <f t="shared" si="95"/>
         <v>0.31</v>
       </c>
-      <c r="AU27" s="9">
-        <f t="shared" si="98"/>
+      <c r="AY27" s="9">
+        <f t="shared" si="95"/>
         <v>0.31</v>
       </c>
-      <c r="AV27" s="9">
-        <f t="shared" si="98"/>
+      <c r="AZ27" s="9">
+        <f t="shared" si="95"/>
         <v>0.31</v>
       </c>
-      <c r="AX27" t="s">
+      <c r="BB27" t="s">
         <v>63</v>
       </c>
-      <c r="AY27" s="5">
-        <f>NPV(AY26,AL18:EN18)</f>
-        <v>483.62190587587548</v>
+      <c r="BC27" s="5">
+        <f>NPV(BC26,AQ18:ER18)</f>
+        <v>420.39330070917367</v>
       </c>
     </row>
-    <row r="28" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>58</v>
       </c>
@@ -4128,47 +4213,47 @@
       <c r="O28" s="9"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="9">
-        <f t="shared" ref="Q28:AA28" si="99">Q10/M10-1</f>
+        <f t="shared" ref="Q28:AA28" si="96">Q10/M10-1</f>
         <v>0.30653266331658302</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>0.26637554585152845</v>
       </c>
       <c r="S28" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>1.1904761904761862E-2</v>
       </c>
       <c r="T28" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>-3.1128404669260701E-2</v>
       </c>
       <c r="U28" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>-2.3076923076923106E-2</v>
       </c>
       <c r="V28" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>-0.22758620689655173</v>
       </c>
       <c r="W28" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>-1.9607843137254943E-2</v>
       </c>
       <c r="X28" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>0.18875502008032141</v>
       </c>
       <c r="Y28" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>7.8740157480315043E-2</v>
       </c>
       <c r="Z28" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>0.20089285714285721</v>
       </c>
       <c r="AA28" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>7.5999999999999845E-2</v>
       </c>
       <c r="AB28" s="9">
@@ -4176,148 +4261,152 @@
         <v>-0.15878378378378388</v>
       </c>
       <c r="AC28" s="9">
-        <f t="shared" ref="AC28:AD28" si="100">AC10/Y10-1</f>
+        <f t="shared" ref="AC28:AD28" si="97">AC10/Y10-1</f>
         <v>-0.11678832116788318</v>
       </c>
       <c r="AD28" s="9">
-        <f t="shared" si="100"/>
-        <v>-9.9999999999999867E-2</v>
-      </c>
+        <f t="shared" si="97"/>
+        <v>0.42750929368029733</v>
+      </c>
+      <c r="AE28" s="9"/>
       <c r="AF28" s="9"/>
-      <c r="AG28" s="9">
-        <f t="shared" ref="AG28:AJ28" si="101">AG10/AF10-1</f>
+      <c r="AG28" s="9"/>
+      <c r="AH28" s="9"/>
+      <c r="AJ28" s="9"/>
+      <c r="AK28" s="9">
+        <f t="shared" ref="AK28:AN28" si="98">AK10/AJ10-1</f>
         <v>0.24832214765100669</v>
       </c>
-      <c r="AH28" s="9">
-        <f t="shared" si="101"/>
+      <c r="AL28" s="9">
+        <f t="shared" si="98"/>
         <v>1.0913978494623655</v>
       </c>
-      <c r="AI28" s="9">
-        <f t="shared" si="101"/>
+      <c r="AM28" s="9">
+        <f t="shared" si="98"/>
         <v>0.36118251928020584</v>
       </c>
-      <c r="AJ28" s="9">
-        <f t="shared" si="101"/>
+      <c r="AN28" s="9">
+        <f t="shared" si="98"/>
         <v>-7.271010387157717E-2</v>
       </c>
-      <c r="AK28" s="9">
-        <f>AK10/AJ10-1</f>
+      <c r="AO28" s="9">
+        <f>AO10/AN10-1</f>
         <v>0.10896130346232202</v>
       </c>
-      <c r="AL28" s="9">
-        <f t="shared" ref="AL28:AV28" si="102">AL10/AK10-1</f>
-        <v>-7.9797979797979757E-2</v>
-      </c>
-      <c r="AM28" s="9">
-        <f t="shared" si="102"/>
+      <c r="AP28" s="9">
+        <f t="shared" ref="AP28:AZ28" si="99">AP10/AO10-1</f>
+        <v>5.0505050505050608E-2</v>
+      </c>
+      <c r="AQ28" s="9">
+        <f t="shared" si="99"/>
         <v>-4.0000000000000036E-2</v>
       </c>
-      <c r="AN28" s="9">
-        <f t="shared" si="102"/>
+      <c r="AR28" s="9">
+        <f t="shared" si="99"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AO28" s="9">
-        <f t="shared" si="102"/>
+      <c r="AS28" s="9">
+        <f t="shared" si="99"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AP28" s="9">
-        <f t="shared" si="102"/>
+      <c r="AT28" s="9">
+        <f t="shared" si="99"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AQ28" s="9">
-        <f t="shared" si="102"/>
+      <c r="AU28" s="9">
+        <f t="shared" si="99"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AR28" s="9">
-        <f t="shared" si="102"/>
+      <c r="AV28" s="9">
+        <f t="shared" si="99"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AS28" s="9">
-        <f t="shared" si="102"/>
+      <c r="AW28" s="9">
+        <f t="shared" si="99"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AT28" s="9">
-        <f t="shared" si="102"/>
+      <c r="AX28" s="9">
+        <f t="shared" si="99"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AU28" s="9">
-        <f t="shared" si="102"/>
+      <c r="AY28" s="9">
+        <f t="shared" si="99"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AV28" s="9">
-        <f t="shared" si="102"/>
+      <c r="AZ28" s="9">
+        <f t="shared" si="99"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AX28" t="s">
+      <c r="BB28" t="s">
         <v>64</v>
       </c>
-      <c r="AY28" s="5">
+      <c r="BC28" s="5">
         <f>Main!D8</f>
-        <v>797.7</v>
+        <v>792.6</v>
       </c>
     </row>
-    <row r="29" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>59</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" ref="M29:AA29" si="103">M13/M5</f>
+        <f t="shared" ref="M29:AA29" si="100">M13/M5</f>
         <v>-0.28571428571428564</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="100"/>
         <v>-0.41304347826086968</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="100"/>
         <v>-0.30980066445182719</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="100"/>
         <v>-0.38301282051282048</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="100"/>
         <v>-0.2661290322580645</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="100"/>
         <v>-0.39310829817158927</v>
       </c>
       <c r="S29" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="100"/>
         <v>-0.26490514905149048</v>
       </c>
       <c r="T29" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="100"/>
         <v>-0.25113858165256991</v>
       </c>
       <c r="U29" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="100"/>
         <v>-0.23927492447129914</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="100"/>
         <v>-0.16933096506808759</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="100"/>
         <v>-0.17622708456534594</v>
       </c>
       <c r="X29" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="100"/>
         <v>-0.18320610687022892</v>
       </c>
       <c r="Y29" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="100"/>
         <v>-0.12379329926178315</v>
       </c>
       <c r="Z29" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="100"/>
         <v>-0.17020089285714302</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="100"/>
         <v>-8.0312325711098587E-2</v>
       </c>
       <c r="AB29" s="9">
@@ -4325,151 +4414,155 @@
         <v>-8.0705505077498782E-2</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" ref="AC29:AD29" si="104">AC13/AC5</f>
+        <f t="shared" ref="AC29:AD29" si="101">AC13/AC5</f>
         <v>-8.0329557157569634E-2</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" si="104"/>
-        <v>-7.431919642857146E-2</v>
-      </c>
-      <c r="AF29" s="9">
-        <f t="shared" ref="AF29:AJ29" si="105">AF13/AF5</f>
+        <f t="shared" si="101"/>
+        <v>-0.16404266124936506</v>
+      </c>
+      <c r="AE29" s="9"/>
+      <c r="AF29" s="9"/>
+      <c r="AG29" s="9"/>
+      <c r="AH29" s="9"/>
+      <c r="AJ29" s="9">
+        <f t="shared" ref="AJ29:AN29" si="102">AJ13/AJ5</f>
         <v>-0.26247288503253796</v>
       </c>
-      <c r="AG29" s="9">
-        <f t="shared" si="105"/>
+      <c r="AK29" s="9">
+        <f t="shared" si="102"/>
         <v>-0.22657580919931858</v>
       </c>
-      <c r="AH29" s="9">
-        <f t="shared" si="105"/>
+      <c r="AL29" s="9">
+        <f t="shared" si="102"/>
         <v>-0.34432940043342175</v>
       </c>
-      <c r="AI29" s="9">
-        <f t="shared" si="105"/>
+      <c r="AM29" s="9">
+        <f t="shared" si="102"/>
         <v>-0.33848797250859131</v>
       </c>
-      <c r="AJ29" s="9">
-        <f t="shared" si="105"/>
+      <c r="AN29" s="9">
+        <f t="shared" si="102"/>
         <v>-0.22951077552304555</v>
       </c>
-      <c r="AK29" s="9">
-        <f t="shared" ref="AK29:AV29" si="106">AK13/AK5</f>
+      <c r="AO29" s="9">
+        <f t="shared" ref="AO29:AZ29" si="103">AO13/AO5</f>
         <v>-0.16309198215056844</v>
       </c>
-      <c r="AL29" s="9">
-        <f t="shared" si="106"/>
-        <v>-7.8876276958002395E-2</v>
-      </c>
-      <c r="AM29" s="9">
-        <f t="shared" si="106"/>
-        <v>-3.348744978169902E-2</v>
-      </c>
-      <c r="AN29" s="9">
-        <f t="shared" si="106"/>
-        <v>-5.886850268765567E-3</v>
-      </c>
-      <c r="AO29" s="9">
-        <f t="shared" si="106"/>
-        <v>1.9081826435482337E-2</v>
-      </c>
       <c r="AP29" s="9">
-        <f t="shared" si="106"/>
-        <v>2.395402398042451E-2</v>
+        <f t="shared" si="103"/>
+        <v>-0.10217821782178246</v>
       </c>
       <c r="AQ29" s="9">
-        <f t="shared" si="106"/>
-        <v>2.8731615747794838E-2</v>
+        <f t="shared" si="103"/>
+        <v>-4.6522007340920997E-2</v>
       </c>
       <c r="AR29" s="9">
-        <f t="shared" si="106"/>
-        <v>3.341643874298339E-2</v>
+        <f t="shared" si="103"/>
+        <v>-1.5987835632695523E-2</v>
       </c>
       <c r="AS29" s="9">
-        <f t="shared" si="106"/>
-        <v>3.8010294301372045E-2</v>
+        <f t="shared" si="103"/>
+        <v>-8.2302329031306589E-4</v>
       </c>
       <c r="AT29" s="9">
-        <f t="shared" si="106"/>
-        <v>4.251494878095706E-2</v>
+        <f t="shared" si="103"/>
+        <v>4.2415014337706444E-3</v>
       </c>
       <c r="AU29" s="9">
-        <f t="shared" si="106"/>
-        <v>4.6932134241520991E-2</v>
+        <f t="shared" si="103"/>
+        <v>9.2076858719499933E-3</v>
       </c>
       <c r="AV29" s="9">
-        <f t="shared" si="106"/>
-        <v>5.1263549110617576E-2</v>
-      </c>
-      <c r="AX29" t="s">
+        <f t="shared" si="103"/>
+        <v>1.4077439544339293E-2</v>
+      </c>
+      <c r="AW29" s="9">
+        <f t="shared" si="103"/>
+        <v>1.8852634892992902E-2</v>
+      </c>
+      <c r="AX29" s="9">
+        <f t="shared" si="103"/>
+        <v>2.3535108001866818E-2</v>
+      </c>
+      <c r="AY29" s="9">
+        <f t="shared" si="103"/>
+        <v>2.8126659302801355E-2</v>
+      </c>
+      <c r="AZ29" s="9">
+        <f t="shared" si="103"/>
+        <v>3.2629054267795637E-2</v>
+      </c>
+      <c r="BB29" t="s">
         <v>65</v>
       </c>
-      <c r="AY29" s="5">
-        <f>AY27+AY28</f>
-        <v>1281.3219058758755</v>
+      <c r="BC29" s="5">
+        <f>BC27+BC28</f>
+        <v>1212.9933007091736</v>
       </c>
     </row>
-    <row r="30" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>24</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" ref="M30:AA30" si="107">M17/M16</f>
+        <f t="shared" ref="M30:AA30" si="104">M17/M16</f>
         <v>-2.5316455696202542E-2</v>
       </c>
       <c r="N30" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="104"/>
         <v>-4.2105263157894727E-3</v>
       </c>
       <c r="O30" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="104"/>
         <v>-2.6737967914438502E-2</v>
       </c>
       <c r="P30" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="104"/>
         <v>-2.4896265560165973E-2</v>
       </c>
       <c r="Q30" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="104"/>
         <v>-2.8571428571428571E-2</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="104"/>
         <v>-3.0000000000000009E-2</v>
       </c>
       <c r="S30" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="104"/>
         <v>-4.5161290322580649E-2</v>
       </c>
       <c r="T30" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="104"/>
         <v>-5.2631578947368432E-2</v>
       </c>
       <c r="U30" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="104"/>
         <v>-3.2258064516129024E-2</v>
       </c>
       <c r="V30" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="104"/>
         <v>-6.8062827225130906E-2</v>
       </c>
       <c r="W30" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="104"/>
         <v>-3.9024390243902446E-2</v>
       </c>
       <c r="X30" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="104"/>
         <v>-4.566210045662103E-2</v>
       </c>
       <c r="Y30" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="104"/>
         <v>-0.12295081967213103</v>
       </c>
       <c r="Z30" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="104"/>
         <v>9.6234309623430853E-2</v>
       </c>
       <c r="AA30" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="104"/>
         <v>-0.23809523809523894</v>
       </c>
       <c r="AB30" s="9">
@@ -4477,151 +4570,155 @@
         <v>-0.11428571428571392</v>
       </c>
       <c r="AC30" s="9">
-        <f t="shared" ref="AC30:AD30" si="108">AC17/AC16</f>
+        <f t="shared" ref="AC30:AD30" si="105">AC17/AC16</f>
         <v>-0.10256410256410228</v>
       </c>
       <c r="AD30" s="9">
-        <f t="shared" si="108"/>
-        <v>-0.15665534570701672</v>
-      </c>
-      <c r="AF30" s="9">
-        <f t="shared" ref="AF30:AJ30" si="109">AF17/AF16</f>
+        <f t="shared" si="105"/>
+        <v>-8.0645161290322634E-2</v>
+      </c>
+      <c r="AE30" s="9"/>
+      <c r="AF30" s="9"/>
+      <c r="AG30" s="9"/>
+      <c r="AH30" s="9"/>
+      <c r="AJ30" s="9">
+        <f t="shared" ref="AJ30:AN30" si="106">AJ17/AJ16</f>
         <v>-1.5217391304347823E-2</v>
       </c>
-      <c r="AG30" s="9">
-        <f t="shared" si="109"/>
+      <c r="AK30" s="9">
+        <f t="shared" si="106"/>
         <v>-2.3006134969325152E-2</v>
       </c>
-      <c r="AH30" s="9">
-        <f t="shared" si="109"/>
+      <c r="AL30" s="9">
+        <f t="shared" si="106"/>
         <v>-1.468531468531468E-2</v>
       </c>
-      <c r="AI30" s="9">
-        <f t="shared" si="109"/>
+      <c r="AM30" s="9">
+        <f t="shared" si="106"/>
         <v>-2.7549824150058595E-2</v>
       </c>
-      <c r="AJ30" s="9">
-        <f t="shared" si="109"/>
+      <c r="AN30" s="9">
+        <f t="shared" si="106"/>
         <v>-4.7533632286995503E-2</v>
       </c>
-      <c r="AK30" s="9">
-        <f t="shared" ref="AK30:AV30" si="110">AK17/AK16</f>
+      <c r="AO30" s="9">
+        <f t="shared" ref="AO30:AZ30" si="107">AO17/AO16</f>
         <v>-1.273885350318473E-2</v>
       </c>
-      <c r="AL30" s="9">
-        <f t="shared" si="110"/>
-        <v>-0.14918074302197928</v>
-      </c>
-      <c r="AM30" s="9">
-        <f t="shared" si="110"/>
+      <c r="AP30" s="9">
+        <f t="shared" si="107"/>
+        <v>-0.11111111111111061</v>
+      </c>
+      <c r="AQ30" s="9">
+        <f t="shared" si="107"/>
         <v>0.1</v>
       </c>
-      <c r="AN30" s="9">
-        <f t="shared" si="110"/>
+      <c r="AR30" s="9">
+        <f t="shared" si="107"/>
         <v>0.1</v>
       </c>
-      <c r="AO30" s="9">
-        <f t="shared" si="110"/>
+      <c r="AS30" s="9">
+        <f t="shared" si="107"/>
+        <v>0.1</v>
+      </c>
+      <c r="AT30" s="9">
+        <f t="shared" si="107"/>
+        <v>0.1</v>
+      </c>
+      <c r="AU30" s="9">
+        <f t="shared" si="107"/>
         <v>0.10000000000000002</v>
       </c>
-      <c r="AP30" s="9">
-        <f t="shared" si="110"/>
-        <v>0.10000000000000002</v>
-      </c>
-      <c r="AQ30" s="9">
-        <f t="shared" si="110"/>
+      <c r="AV30" s="9">
+        <f t="shared" si="107"/>
         <v>0.1</v>
       </c>
-      <c r="AR30" s="9">
-        <f t="shared" si="110"/>
+      <c r="AW30" s="9">
+        <f t="shared" si="107"/>
         <v>0.1</v>
       </c>
-      <c r="AS30" s="9">
-        <f t="shared" si="110"/>
+      <c r="AX30" s="9">
+        <f t="shared" si="107"/>
         <v>0.1</v>
       </c>
-      <c r="AT30" s="9">
-        <f t="shared" si="110"/>
+      <c r="AY30" s="9">
+        <f t="shared" si="107"/>
         <v>0.1</v>
       </c>
-      <c r="AU30" s="9">
-        <f t="shared" si="110"/>
-        <v>0.10000000000000002</v>
-      </c>
-      <c r="AV30" s="9">
-        <f t="shared" si="110"/>
+      <c r="AZ30" s="9">
+        <f t="shared" si="107"/>
         <v>0.1</v>
       </c>
-      <c r="AX30" t="s">
+      <c r="BB30" t="s">
         <v>66</v>
       </c>
-      <c r="AY30" s="2">
-        <f>AY29/AV19</f>
-        <v>7.7844587234257325</v>
+      <c r="BC30" s="2">
+        <f>BC29/AZ19</f>
+        <v>7.25474462146635</v>
       </c>
     </row>
-    <row r="31" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>60</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" ref="M31:AA31" si="111">M18/M5</f>
+        <f t="shared" ref="M31:AA31" si="108">M18/M5</f>
         <v>-0.29481346678798898</v>
       </c>
       <c r="N31" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="108"/>
         <v>-0.41478260869565231</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="108"/>
         <v>-0.31893687707641194</v>
       </c>
       <c r="P31" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="108"/>
         <v>-0.39583333333333337</v>
       </c>
       <c r="Q31" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="108"/>
         <v>-0.26392961876832843</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="108"/>
         <v>-0.36216596343178614</v>
       </c>
       <c r="S31" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="108"/>
         <v>-0.21951219512195116</v>
       </c>
       <c r="T31" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="108"/>
         <v>-0.20819778789850357</v>
       </c>
       <c r="U31" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="108"/>
         <v>-0.19335347432024177</v>
       </c>
       <c r="V31" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="108"/>
         <v>-0.12078152753108345</v>
       </c>
       <c r="W31" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="108"/>
         <v>-0.12596096984033114</v>
       </c>
       <c r="X31" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="108"/>
         <v>-0.13446858485026417</v>
       </c>
       <c r="Y31" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="108"/>
         <v>-7.7796706416808706E-2</v>
       </c>
       <c r="Z31" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="108"/>
         <v>-0.12053571428571444</v>
       </c>
       <c r="AA31" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="108"/>
         <v>-4.3502509760178346E-2</v>
       </c>
       <c r="AB31" s="9">
@@ -4629,103 +4726,107 @@
         <v>-4.1688936397648438E-2</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" ref="AC31:AD31" si="112">AC18/AC5</f>
+        <f t="shared" ref="AC31:AD31" si="109">AC18/AC5</f>
         <v>-4.428424304840383E-2</v>
       </c>
       <c r="AD31" s="9">
-        <f t="shared" si="112"/>
-        <v>-3.8150214947089985E-2</v>
-      </c>
-      <c r="AF31" s="9">
-        <f t="shared" ref="AF31:AJ31" si="113">AF18/AF5</f>
+        <f t="shared" si="109"/>
+        <v>-0.13610970035551032</v>
+      </c>
+      <c r="AE31" s="9"/>
+      <c r="AF31" s="9"/>
+      <c r="AG31" s="9"/>
+      <c r="AH31" s="9"/>
+      <c r="AJ31" s="9">
+        <f t="shared" ref="AJ31:AN31" si="110">AJ18/AJ5</f>
         <v>-0.25325379609544474</v>
       </c>
-      <c r="AG31" s="9">
-        <f t="shared" si="113"/>
+      <c r="AK31" s="9">
+        <f t="shared" si="110"/>
         <v>-0.22725724020442931</v>
       </c>
-      <c r="AH31" s="9">
-        <f t="shared" si="113"/>
+      <c r="AL31" s="9">
+        <f t="shared" si="110"/>
         <v>-0.34938598603419224</v>
       </c>
-      <c r="AI31" s="9">
-        <f t="shared" si="113"/>
+      <c r="AM31" s="9">
+        <f t="shared" si="110"/>
         <v>-0.3346697212676597</v>
       </c>
-      <c r="AJ31" s="9">
-        <f t="shared" si="113"/>
+      <c r="AN31" s="9">
+        <f t="shared" si="110"/>
         <v>-0.18373446594305495</v>
       </c>
-      <c r="AK31" s="9">
-        <f t="shared" ref="AK31:AV31" si="114">AK18/AK5</f>
+      <c r="AO31" s="9">
+        <f t="shared" ref="AO31:AZ31" si="111">AO18/AO5</f>
         <v>-0.11443788685763624</v>
       </c>
-      <c r="AL31" s="9">
-        <f t="shared" si="114"/>
-        <v>-4.1880297452979422E-2</v>
-      </c>
-      <c r="AM31" s="9">
-        <f t="shared" si="114"/>
-        <v>6.7106546905522802E-3</v>
-      </c>
-      <c r="AN31" s="9">
-        <f t="shared" si="114"/>
-        <v>3.0488231959093885E-2</v>
-      </c>
-      <c r="AO31" s="9">
-        <f t="shared" si="114"/>
-        <v>5.2265159493868792E-2</v>
-      </c>
       <c r="AP31" s="9">
-        <f t="shared" si="114"/>
-        <v>5.5968748629910248E-2</v>
+        <f t="shared" si="111"/>
+        <v>-6.7326732673267609E-2</v>
       </c>
       <c r="AQ31" s="9">
-        <f t="shared" si="114"/>
-        <v>5.9600423413795428E-2</v>
+        <f t="shared" si="111"/>
+        <v>-5.9819561395391737E-3</v>
       </c>
       <c r="AR31" s="9">
-        <f t="shared" si="114"/>
-        <v>6.3161580240712112E-2</v>
+        <f t="shared" si="111"/>
+        <v>2.0131642189586046E-2</v>
       </c>
       <c r="AS31" s="9">
-        <f t="shared" si="114"/>
-        <v>6.6653588391377874E-2</v>
+        <f t="shared" si="111"/>
+        <v>3.3109668554836817E-2</v>
       </c>
       <c r="AT31" s="9">
-        <f t="shared" si="114"/>
-        <v>7.0077790558535608E-2</v>
+        <f t="shared" si="111"/>
+        <v>3.7010451689694322E-2</v>
       </c>
       <c r="AU31" s="9">
-        <f t="shared" si="114"/>
-        <v>7.3435503363224214E-2</v>
+        <f t="shared" si="111"/>
+        <v>4.083549146271008E-2</v>
       </c>
       <c r="AV31" s="9">
-        <f t="shared" si="114"/>
-        <v>7.6728017861025594E-2</v>
-      </c>
-      <c r="AX31" t="s">
+        <f t="shared" si="111"/>
+        <v>4.4586258618773945E-2</v>
+      </c>
+      <c r="AW31" s="9">
+        <f t="shared" si="111"/>
+        <v>4.8264195344622993E-2</v>
+      </c>
+      <c r="AX31" s="9">
+        <f t="shared" si="111"/>
+        <v>5.1870715823368177E-2</v>
+      </c>
+      <c r="AY31" s="9">
+        <f t="shared" si="111"/>
+        <v>5.5407206778254156E-2</v>
+      </c>
+      <c r="AZ31" s="9">
+        <f t="shared" si="111"/>
+        <v>5.8875028005860981E-2</v>
+      </c>
+      <c r="BB31" t="s">
         <v>67</v>
       </c>
-      <c r="AY31" s="2">
+      <c r="BC31" s="2">
         <f>Main!D3</f>
-        <v>9.1999999999999993</v>
+        <v>5.98</v>
       </c>
     </row>
-    <row r="32" spans="2:144" x14ac:dyDescent="0.3">
-      <c r="AX32" s="1" t="s">
+    <row r="32" spans="2:148" x14ac:dyDescent="0.3">
+      <c r="BB32" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AY32" s="10">
-        <f>AY30/AY31-1</f>
-        <v>-0.15386318223633333</v>
+      <c r="BC32" s="10">
+        <f>BC30/BC31-1</f>
+        <v>0.21316799690072741</v>
       </c>
     </row>
-    <row r="33" spans="50:51" x14ac:dyDescent="0.3">
-      <c r="AX33" t="s">
+    <row r="33" spans="54:55" x14ac:dyDescent="0.3">
+      <c r="BB33" t="s">
         <v>69</v>
       </c>
-      <c r="AY33" s="6" t="s">
+      <c r="BC33" s="6" t="s">
         <v>72</v>
       </c>
     </row>

--- a/Financial Analysis/COUR.xlsx
+++ b/Financial Analysis/COUR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F54242D-6FC6-4BFF-B2CC-0E784211647D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5794E6D8-7C85-421C-9AA3-669B79B2C7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{31E8D773-A0F0-4A5C-8306-0B953AC75F07}"/>
   </bookViews>
@@ -778,7 +778,7 @@
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>46059</v>
+        <v>46076</v>
       </c>
       <c r="G3" s="4">
         <v>46135</v>
@@ -4045,7 +4045,7 @@
         <v>62</v>
       </c>
       <c r="BC26" s="9">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="27" spans="2:148" x14ac:dyDescent="0.3">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="BC27" s="5">
         <f>NPV(BC26,AQ18:ER18)</f>
-        <v>420.39330070917367</v>
+        <v>373.39180979389926</v>
       </c>
     </row>
     <row r="28" spans="2:148" x14ac:dyDescent="0.3">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="BC29" s="5">
         <f>BC27+BC28</f>
-        <v>1212.9933007091736</v>
+        <v>1165.9918097938994</v>
       </c>
     </row>
     <row r="30" spans="2:148" x14ac:dyDescent="0.3">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="BC30" s="2">
         <f>BC29/AZ19</f>
-        <v>7.25474462146635</v>
+        <v>6.9736352260400682</v>
       </c>
     </row>
     <row r="31" spans="2:148" x14ac:dyDescent="0.3">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="BC32" s="10">
         <f>BC30/BC31-1</f>
-        <v>0.21316799690072741</v>
+        <v>0.16615973679599794</v>
       </c>
     </row>
     <row r="33" spans="54:55" x14ac:dyDescent="0.3">
